--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-244.097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.38136e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-76.828</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3924209983879824</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8910132017726454</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.614097729271899</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.306355301069031</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.65069156023822</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.14651427036735</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.777x + -6742.022</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>489.9742321541311</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>148118181.4788225</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.478231451742328e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8172474898596364</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-222.042</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.33907e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.80800000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5544682007665085</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.371329812182093</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.200639383766575</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.15825014107626</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.43425584999352</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.522x + -6812.803</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>480.2581810792708</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38935196.01490787</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.174355328937243e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8501281648784971</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-213.101</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.31461e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.137</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3419299628915256</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7032330073002038</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.560724885946134</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.488244405021416</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.41374222147842</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.72503267955744</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.378x + -7195.355</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>475.2972455033754</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>53640759.67525764</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.094773477069725e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8597889939004243</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-210.652</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.29532e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.36499999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2689838213703519</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5947670443258029</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.358287551024505</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.172710327564091</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.65114934197274</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.74488277369484</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.440x + -7129.177</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>470.9425137897255</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>44322862.68661626</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.045463250749225e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8660217394259915</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-207.506</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.28319e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.559</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1959637013551754</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6451804356809925</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.561364031254846</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.427714661989078</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.9277282170277</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.77791914159805</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.546x + -7093.683</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>466.432824560886</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>82130829.68119729</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.008757036480951e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8709474405750814</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-202.2909999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.27434e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.73999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5853508196965488</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.148258223508681</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.704540254966236</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.677197328111044</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.37355494812692</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.00770599639398</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.328x + -7453.785</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>461.8549488648044</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>56724908.32590564</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.76414534436509e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8755254932747133</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-201.451</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.26567e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.90300000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1620191109249551</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7927896207236551</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.582693475529581</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.512423912947165</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.18832148142454</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.94466451637027</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.105x + -7223.820</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>457.3615626041556</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>67801734.22047524</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.486780199241122e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8795528532825296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-198.793</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.25913e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-79.035</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1934440461196696</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9217267792799397</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.548172736611009</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.540775212139333</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.9344835537499</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.07607965060043</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.579x + -7406.363</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>453.2546206910977</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>503463074.8002728</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>9.275650692967625e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8827012141856697</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-196.66</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.25449e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.17</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5898868227231487</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9754121063680682</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.645764916656965</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.538981844753542</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.83726287810773</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.10565377072155</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.690x + -7384.208</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>449.4920261038993</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>367980904.6520852</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9.080503930994159e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8857282762463824</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-191.855</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.25006e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.30800000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.916902483679086</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.211021110451384</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.836011087939798</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.514841850400109</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.25621549355462</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.25781826491523</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.289x + -7641.013</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>445.8780580103834</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>141980293.9109289</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.895668155853722e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8886539260912504</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-193.032</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.24651e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-79.402</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5515187304837327</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.11457692261262</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.891092280276125</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.42082606058055</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.42518727881927</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.19457242780233</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 15.034x + -7422.647</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>442.3503984287934</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>112240319.493892</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.764206311982184e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8907696604704239</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-192.61</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.24329e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-79.49299999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3421948417589228</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9068870139793079</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.595254980404627</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.642209985595446</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22.52980404655059</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.18119739029416</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 14.981x + -7320.492</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>438.9069988842543</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>26001814.29875525</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.634925066014833e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8928959349140891</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-189.516</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.24097e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-79.61</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4658419382573964</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.883764495243796</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.60875843712789</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.594318049850169</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22.87069040942833</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.23643882630302</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 15.202x + -7367.310</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>435.5607166733957</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>68972214.1317673</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.508675645135113e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8950116281357834</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-189.105</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.24007e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.70699999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6564991690311296</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.565212807252517</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.310630091720536</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21.28672910471354</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.18873829179076</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 15.011x + -7193.466</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>432.1663647990239</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>355937089.6774742</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.401976279531202e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8968687594459273</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-187.767</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.23705e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.794</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2367392183175776</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9360960970092798</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.537793554309302</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.42255822182277</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22.30368955893963</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.2659016490831</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 15.322x + -7289.453</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>428.8040168914721</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>352665882.4857401</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8.296606311151344e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8986614520891326</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-187.425</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.23491e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.873</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1407556048805033</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7678014904433822</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.509005065534174</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.401990178739131</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21.97836461856139</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.27059090147748</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 15.342x + -7233.478</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>425.5181398561159</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>233348024.7402682</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.20844195289727e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9001907248450632</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-185.425</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.23312e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.964</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4960474678057184</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.002676634913937</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.844652241094084</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.773682377630725</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23.58888379740582</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.37729202165276</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 15.795x + -7399.724</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>422.2054309710713</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>173599336.1105402</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.111308803992081e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9019044205140203</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-186.873</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.23191e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-80.042</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1480482520921864</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.589249828434978</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.525893564501388</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.378652054244133</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22.34097047071391</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.25518816750865</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 15.278x + -7065.125</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>418.8913705290404</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>343891492.0842941</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.030844396002918e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9033714295641402</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-183.537</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.23159e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-80.127</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.379394562511104</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.081908449901843</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.694891183887842</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.665309263989076</v>
+      </c>
+      <c r="J20" t="n">
+        <v>23.44104404501469</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.41945351399555</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 15.981x + -7358.892</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>415.6398467546637</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>170711867.1082714</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.949215883028286e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9048873269211634</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-181.081</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.2307e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-80.227</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3409916298120794</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.12801311177894</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.663242745868579</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.790401580927847</v>
+      </c>
+      <c r="J21" t="n">
+        <v>23.28617940161484</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.43873896347283</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 16.068x + -7330.866</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>412.3606945871971</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>225638062.5626982</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.856700057113214e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9066104531347747</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-184.1990000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.23035e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-80.279</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.459496532458217</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.371256892159129</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.371632645822643</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22.79776784187481</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.27015346145507</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 15.340x + -6898.664</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>409.0709526386851</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>223706718.6679012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.80187494533801e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9076586219078739</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-391.198</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.10809e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72.67100000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3760607688977225</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5960263478065286</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.219805852761114</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.739733406768973</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.33663405942446</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.70459489039814</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.811x + -5664.476</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>484.9861151643555</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>332736872.0083891</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.29287172787754e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-296.4540000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.27465e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.34099999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3825606324296922</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.708897980451684</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.326946508238823</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.011795601829562</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.26082319176915</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.27422222106367</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.973x + -6235.017</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>521.3350682481924</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>400990891.9343027</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.677452522839929e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7256973211863861</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-270.971</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.26496e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.214</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06422594773600597</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5193973706787749</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.506615492334164</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.166445366476919</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.82290636303078</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.67273293376704</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.724x + -6457.223</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>517.3713649115799</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>338453846.786369</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.817158349230833e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7823188836726278</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-256.049</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.24367e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.712</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.119776886174554</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6565780103354363</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.432384821598352</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.277327044843894</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15.9592478865652</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.95536822507026</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.328x + -6711.920</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>513.1693295433734</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>71587039.11022817</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.551584797607573e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8050175307555576</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-246.5940000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.22243e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.059</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2260882118717157</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7393817500528544</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.57151861350703</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.163097749616126</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15.98088238782829</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.19587264337859</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.898x + -6971.728</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>508.7904941824024</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>53603483.59283476</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.403257078285212e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.819241634951197</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-239.462</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.20916e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.36499999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4169296705717941</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5676502412179942</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.424936145993078</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.184301441729694</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.05153095504486</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.27155152418317</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 12.090x + -6978.951</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>504.1404758598058</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>127015839.6190417</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.2989293958207e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8303017056326936</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-231.125</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.19867e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.604</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5279483020288382</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.209691643272182</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.973219766587984</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.487239703336152</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.43937855717516</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.56297724600542</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.887x + -7388.883</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>499.4335336193562</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24540362.74458681</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.223309426751137e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8389065445825524</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-228.739</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.18922e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.831</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2923016671155175</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9120185383793875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.628110465360352</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.380228442089888</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.57181762477026</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.51228589144141</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 12.741x + -7186.108</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>494.6814522457348</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>240916987.3990885</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.162745934544996e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.846174600581583</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-224.625</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.1818e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.01000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.384175237538015</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9602037977760616</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.673158636056737</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.084246318302073</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.0246516925667</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.64535672007067</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.132x + -7332.145</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>489.836180994921</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>410904260.3103519</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.116260850621299e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8520377104751431</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-221.218</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.17697e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.20699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4070840462417472</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.01608500206003</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.765796502429194</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.586652876146154</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19.88638200211895</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.7085873613081</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 13.326x + -7347.821</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>485.1460599920371</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>60299381.14163633</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.073682635026227e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8576846166664608</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-288.5219999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.34957e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-76.021</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13108792360626</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7004788898026604</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.236659109750848</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.998474552184525</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.35847398918895</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.34137867276681</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.092x + -5851.073</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>490.6367201800968</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>444957475.7575544</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.789976648279128e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7876958551000325</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-250.4160000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.32251e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1334385730557313</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6846546224824683</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.329431169532908</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.058497222916822</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.28721553629523</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.00298876246667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.437x + -6273.528</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>480.9967073330358</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>98211573.19599701</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.292418458022157e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8352058649312752</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-233.221</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.29211e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-77.78</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7045473468512315</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.145112988204874</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.772769972013858</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.370752173596686</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.4291762377234</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.49559100147437</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.694x + -6896.835</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>476.5104644538858</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>174464456.9436574</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.167616733782872e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8493114793289552</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-226.752</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.26899e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.095</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3799081480786351</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8078241662232671</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.377606246016697</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.117706638016172</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17.62211819010094</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.5016101024145</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.711x + -6797.388</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>472.7525593398541</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>118491567.6754503</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.097665810904654e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8577348042543627</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-221.253</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.25014e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.306</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8850650598072066</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.141731747056997</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.826287521292426</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.343698509802317</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.45108375475308</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.73307133933369</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.403x + -7126.489</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>468.9819122443698</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>112812922.6847093</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.051812760341511e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8634700582968291</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-216.3349999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.23713e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.51300000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7153038373974264</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.086511902130768</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.45265967152724</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.352426362564199</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.58237865560925</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.80503641341028</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.634x + -7171.224</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>465.0790243736301</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>111156231.6956024</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.013681429750216e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8685320003717431</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-212.8200000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.22673e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.712</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3100730686201351</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6699868548954904</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.450439832010598</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.259604964412067</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.18796585542277</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.79298279271276</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.595x + -7055.838</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>461.1516122042609</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>66260437.21048671</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.79331295351269e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8733319569118753</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-210.386</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.21853e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.857</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3943259313555657</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8740324571671987</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.483373369666582</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.341574975554589</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.49934147399136</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.86617075478213</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.836x + -7112.722</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>457.3864809506157</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>55553887.17777497</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>9.541075920291812e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.876963732069677</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-205.914</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.21175e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.991</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.66467338441554</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.205555272375719</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.866087991863654</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.435619051090081</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.21415709950004</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.04721851291664</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.472x + -7403.042</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>453.7330725039115</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>27254715.81268415</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9.329199084660932e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8800895374504167</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-207.3650000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.20735e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.10899999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1425720595855672</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8095302163976215</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.502399980038932</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.514397898327171</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.47793135831148</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.90117617036917</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 13.955x + -7029.461</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>450.2221643621617</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>63839364.51118754</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.158146631407134e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8827075870709763</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-202.934</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.20347e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-79.223</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6876712420412286</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.336113454959132</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.096723645604279</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.740901971391303</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.78819654744828</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.09682199415462</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 14.657x + -7356.216</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>446.8388964258468</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>236340210.8547626</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.996273767565365e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8852391797187512</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-200.639</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.20011e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-79.34099999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5456993096448471</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.13902987790713</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.702008353412342</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.48828933990042</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21.63682406280757</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.11823548043371</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 14.738x + -7329.036</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>443.5286139056063</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>104506479.3569433</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.846161540240556e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8876430945055536</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-198.266</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.19676e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-79.458</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5761079211704008</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.186960581649092</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.765980417693056</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.466087752953278</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.48228935430566</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.15113165755315</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 14.864x + -7328.840</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>440.2728386421616</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>48907273.27580757</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.702026283103438e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8899835589731141</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-201.864</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.19397e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.497</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.03930176500610308</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9362346332199328</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.470991863678789</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.362434346840123</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20.85213752420258</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.02377315489622</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 14.386x + -7005.441</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>436.9733621935648</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>37707447.05188376</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.626656148130543e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8912124570067083</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-196.441</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.19329e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.631</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6272792231972879</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9542797956554196</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.617131045771197</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.578248841991928</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21.37610644363616</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.19642498284472</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 15.042x + -7291.197</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>433.802254192731</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>48255195.06780083</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8.488422569119952e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8935906829007343</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-198.597</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.18997e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.693</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2475995699591194</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7046117909454926</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.366942869660273</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.269372345747574</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20.92689408291118</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.09150478381427</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 14.637x + -7010.914</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>430.589869034477</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>16593249.91813339</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.396386542920469e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8951239476083211</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-196.943</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.18886e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.794</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4199580397912129</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.330593823012697</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.216074211779245</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.18607599866911</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.05765811255874</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 14.510x + -6876.684</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>427.3854692308652</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>703133306.1587847</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.297869985299549e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8968476481013549</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-193.72</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.18725e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.902</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05856886699174287</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6852906709247946</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.324654474920868</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.161327634690301</v>
+      </c>
+      <c r="J19" t="n">
+        <v>21.15584780840677</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.15734959276618</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 14.888x + -7012.962</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>424.2195163582124</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>174618713.9645715</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.189301531234026e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.898756777894239</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-193.475</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.18796e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.967</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1827045578692102</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6405631131214343</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.576576035289089</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.42376620260316</v>
+      </c>
+      <c r="J20" t="n">
+        <v>21.64132518953993</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.20525123828185</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 15.077x + -7049.524</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>421.0071287354223</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>173122596.5523554</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8.120594659232375e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9000478760096424</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-192.172</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.18724e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-80.048</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2796324987421598</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8168759075816147</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.505320676618938</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.406129102809667</v>
+      </c>
+      <c r="J21" t="n">
+        <v>21.80420633611146</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.2322946739904</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 15.185x + -7043.294</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>417.8126408326631</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>343337304.2052764</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8.040902748043091e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9015033507399853</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-188.014</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.18656e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-80.14700000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4757256036866235</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.096372378941198</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.511833305970431</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.505537954186257</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22.59009422143666</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.38932829967922</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 15.847x + -7317.219</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>414.5699333941683</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>170322252.8409989</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.943590377711847e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9033020411966273</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-372.9979999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.30617e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72.37</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.305229528160217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8253259981307368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.384169276939502</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.1734979514652</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.67308331595372</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.77194845816865</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.885x + -5573.694</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>479.2253385644894</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>472354131.9910227</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.352861052745718e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-296.955</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.45063e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74.81399999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1071602219277513</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.401740825963118</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.238570543361571</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.88900320002873</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.40087124205822</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.02418309048512</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.553x + -5894.239</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>511.49299941495</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>902520402.7178111</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.526782239979953e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6919302999864283</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-269.418</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.43561e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-75.70399999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2351618820208391</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9154875863525624</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.238688259116721</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.112405078300682</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.84794507091336</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.57038930128259</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.521x + -6293.620</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>511.259118049216</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>367048545.7249072</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.181476508861705e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7613140111214566</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-253.001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.40693e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.26600000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08108969542901653</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7533157998888476</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.666809488322929</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.286957500059363</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.98979468907687</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.88794457234106</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.178x + -6581.251</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>507.8293741020886</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>304339646.6292965</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.78223714246108e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.79020552261438</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-242.379</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.38016e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.676</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4691174207770005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9113640926323461</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.706397667624951</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.355141898100458</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.55808468769415</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.16016319501142</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.810x + -6871.508</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>503.5583085184324</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>31448815.66216073</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.565254805349706e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8085861289201479</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-234.2009999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.36161e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.036</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3256704509302275</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9945306649274145</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.515106000077675</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.186167042026732</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.03955666462918</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.30933337209662</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 12.188x + -6990.027</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>498.6612136504206</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>271746175.66655</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.421163704164713e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8223049159105247</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-227.5229999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.34615e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.586105722921163</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8259174716164517</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.433450832553683</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.22960281966186</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17.30733813309292</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.41296251207909</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.464x + -7046.551</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>493.5944305799873</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>207468445.7795521</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.317363148607506e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8331295148860398</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-222.327</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.33202e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.616</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3528677494585213</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7460709670908044</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.558113684113225</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.269430226166837</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.41359769329891</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.4649106739612</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 12.607x + -7016.857</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>488.5616172285689</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>273495237.9056231</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.234759630935135e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8423148227569807</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-218.6819999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.31557e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.833</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.344359586258705</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9018746507369042</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.543571437864111</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.042470154786654</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17.9100196265023</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.60893138353242</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.023x + -7168.371</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>483.6703421743699</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>38899764.29307637</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.171538292361146e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8496277698707549</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-215.037</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.30722e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.05500000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2066984345779428</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7280502579867337</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.55056713981142</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.211320619324486</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.46445037567896</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.59917131842867</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.994x + -7046.443</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>479.1177921100242</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>134952739.5320344</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.121123047400696e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8559192472240215</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-305.5329999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.58809e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-74.592</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3301024091499679</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8367008061126036</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.430308606711741</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.103371869625002</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.75328740451347</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.81631011434521</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.230x + -5459.126</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>495.8142821417966</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>156362982.2244543</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.939460051597208e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7230908482518855</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-263.838</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.53072e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.09</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3806347025851536</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.856073063515977</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.44672589866453</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.060983420269634</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.93987495509508</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.66449696472088</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.708x + -6046.520</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>489.3332543864511</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>22716617.17866769</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.723593905626079e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7996433236301838</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-244.96</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.48432e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.806</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.09832894851399479</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8096666569219945</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.422649477070008</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.185257300687062</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.74395477127287</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.9938808202409</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.416x + -6307.153</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>484.174340005828</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>78898726.29831912</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.445534303458247e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8242070913563007</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-232.9459999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.44464e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.283</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3643596888248495</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7706186277139501</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.61628120304449</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.309543787157372</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.89281130760495</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.2567288732417</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.052x + -6567.897</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>479.4093085140572</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>171103766.1913403</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.299772470422183e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8386997720779665</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-225.91</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.41536e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.63</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09160527067149264</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.499590684864099</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.237115638558158</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.080913409329291</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.97244244015152</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.36876273292559</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.345x + -6629.071</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>474.5617476358946</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>65175634.19993156</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.206148627871701e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8488725973355692</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-216.5250000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.39399e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.94799999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5685054548624868</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.021299630864505</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.542907336311795</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.323747345589888</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.18577346056051</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.65429685905549</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.159x + -7007.294</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>469.7630187700368</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>104170035.1149336</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.135032723436958e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8572078173344774</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-213.976</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.37618e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.17700000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.148797826965246</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.000193715681134</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.438205525959162</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.199232034490155</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.25034403102211</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.62865855973675</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.082x + -6852.534</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>465.0424294029989</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>108463446.6572052</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.083236618129556e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8636058093250398</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-210.085</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.36257e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.402</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1397488358035178</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.755138197938148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.494686820779296</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.150051514413872</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.49056759013806</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.70910225532666</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.328x + -6896.546</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>460.5687854783792</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>106565178.2821618</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.040844649526188e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.869109418292883</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-205.7130000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.35313e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.59699999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2602718641736783</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7047072204277379</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.522673123184286</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.102489221188576</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.93168678249232</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.79834206250902</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.612x + -6967.257</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>456.3086191296907</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>40386859.37707627</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.006394073931005e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8738246336810223</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-204.225</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.34448e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.744</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2014230840990293</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8403745690595604</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.389985924028697</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.356618685942855</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.05736392964297</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.81055176757511</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 13.652x + -6904.240</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>452.2078351562517</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>62697817.95367827</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.803227553144902e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8774668121334069</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-200.006</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.33791e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-78.896</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5543197696236071</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.020110270664494</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.504087092508719</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.374108811120671</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.4364350603683</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.9756923366898</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 14.214x + -7139.873</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>448.3115515227257</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>96016442.48212782</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9.569377701865932e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8808555663346426</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-199.599</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.33169e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-79.036</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.07056558954419857</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7946050012761117</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.348902652833653</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.208742077573862</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.96063557613817</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.88751051667424</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 13.908x + -6889.204</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>444.6650435858865</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>180879024.3102809</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>9.361365042195794e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8839315605615186</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-194.5389999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.32685e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-79.175</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6033970467645074</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9826136528965708</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.794629844238146</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.43300026544915</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.22966461485848</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.10551997027011</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 14.689x + -7245.118</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>441.1438797420638</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>26692653.95806248</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>9.169170173836528e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8868648255645546</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-194.054</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.32169e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.285</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2945994155730148</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8271544871707466</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.499336488060087</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.446928111911252</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21.4677964091038</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.05576800368037</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 14.504x + -7071.457</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>437.784385584846</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>53063169.06322414</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9.019821697617403e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8891495212336263</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-190.3729999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.3181e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.396</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4770217624174433</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.120168369559101</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.455633954601606</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.274729245990715</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21.30710425442786</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.17066780525838</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 14.940x + -7240.649</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>434.5817543191504</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>482158631.2871308</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8.881227119662631e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8913408360591843</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-191.122</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.31649e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.471</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1559035676611303</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8480736603321325</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.494076041095436</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.596383081130563</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21.84588691238783</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.13380830266429</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 14.797x + -7098.044</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>431.4658987977885</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>66454227.7795037</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.778198949022282e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8930375616049108</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-187.501</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.31129e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.586</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4257928777744838</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9171493087409457</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.689249606026482</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.466755017837257</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.7914060903328</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.25571142886017</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 15.280x + -7292.477</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>428.3829152722445</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>353225684.149655</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.644316165480016e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8951668052222892</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-187.153</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.30989e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.684</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2111668079154354</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8126515938433891</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.490046600137014</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.325984382326963</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22.04711285548316</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.1929289729532</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 15.028x + -7092.611</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>425.3353741601115</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>116867376.7142304</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.536167775033069e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8969892537466958</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-186.256</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.30699e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.76300000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5005092969562875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8139377058121606</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.626681106828833</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.289998404132656</v>
+      </c>
+      <c r="J20" t="n">
+        <v>22.20521660699501</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.22281452282172</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 15.147x + -7095.152</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>422.2906207194653</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>231628942.6914996</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8.443795545922185e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8985259004989633</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-185.118</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.30495e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.858</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.00811650823342331</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7718418572958412</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.485597179166969</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.54199421033908</v>
+      </c>
+      <c r="J21" t="n">
+        <v>22.93427862070832</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.19572113363522</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 15.039x + -6975.334</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>419.3044655653769</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>229870125.7516502</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8.342861206783969e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9002518912254268</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-182.796</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.30317e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.95699999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3884003365453135</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7801152234514965</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.421376201130203</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.324018478173127</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22.31528397773949</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.28564577899618</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 15.404x + -7100.616</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>416.3153368583119</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>369199774.5804985</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>8.240718858778662e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9020368808862339</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-374.218</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.35053e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72.215</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07494999410207356</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5224796477982206</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.007061474031461</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.845286531739781</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.24152671045876</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.58538992846334</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.684x + -5422.829</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>473.7338192961772</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3662580913.677582</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.362371856452821e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000002</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-283.105</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.51048e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.105</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1294939604485836</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5591128041388731</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.106089032672827</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.854707082003852</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.73065200533692</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.20194311112579</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.848x + -5935.182</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>505.2416117076925</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1013067522.250978</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.907913506570322e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7218054592484467</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-255.4689999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.48767e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.081</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2707300567918456</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3484621423115785</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.550362900643524</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.043126197502781</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.9781018147828</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.73115555062793</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.844x + -6306.032</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>501.9309252934821</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>462625513.1415778</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.896365003181546e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7837861139106181</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-237.8200000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.4517e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4278865188866369</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6777494026762336</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.511280251332855</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.421054742695428</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.8020621508026</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.10512346645012</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.677x + -6693.239</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>498.1829296978888</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>290644206.8760032</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.591777310518496e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8085333773744523</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-226.275</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.4222e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.078</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4222523958070771</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9227632086996448</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.471330521776808</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.277703540529941</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.01931446852708</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.38209844644207</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.380x + -7021.645</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>494.0539812384313</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>92908426.54140775</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.426486985183265e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8238595213477984</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-221.2859999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.39685e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.392</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3875755868357272</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9457263721267988</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.945491464372651</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.363142947218843</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.60235871732878</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.46358061360702</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 12.604x + -7046.791</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>489.4233714150621</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>227679531.9324244</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.316241109357098e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8350115586261411</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-212.8420000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.38041e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.69199999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6671738680270394</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8918938203421688</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.354037446110056</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.203811387639494</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.09449420288878</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.6395974237423</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.115x + -7248.826</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>484.6246491553262</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>160794777.1034012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.231416102251103e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.844397028578406</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-208.4019999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.36693e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.94</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3499211619454445</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6923854450650276</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.563167399719332</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.074825788515141</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.67577918250349</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.75641327648039</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.477x + -7355.659</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>479.7650701934186</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>134412634.0496769</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.16560288558556e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.852158727711832</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-205.607</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.35442e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.15600000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1576471462609564</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7758500399060214</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.221779496156935</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.210061607507137</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.78908597422313</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.71535107482742</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.347x + -7170.807</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>475.0659821543966</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>75374975.55866922</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.114184749502611e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8584902098275503</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-199.8399999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.34572e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.352</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6174313884504437</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.196623538959351</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.871864379854434</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.395632901970171</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.66021138085898</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.98735396082425</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.255x + -7612.880</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>470.5584005846731</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>162780846.5726622</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.072257515075533e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8639418305740996</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-255.231</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.51162e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-76.18899999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3954790235673624</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8986636399182683</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.457795934763493</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.225899420923451</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15.2969759082039</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.78155887837785</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.949x + -6274.936</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>484.884699817303</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>355113031.7250056</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.808766172188195e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7916546012767963</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-220.418</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.46847e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.459</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5426517475235575</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8023568618923603</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.654951819723135</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.532757409658499</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.80190002952353</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.52275984351037</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.771x + -6945.695</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>474.7035148491834</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>206070272.7912714</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.298060893215393e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8395822544043737</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-211.413</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.43147e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-77.929</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.09626587662243742</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5809360837645944</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.461483184914488</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.110971794860276</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.29143690963812</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.59049512193246</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.968x + -6902.712</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>470.0777566933614</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>113522863.573035</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.173991412747739e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8533364120133866</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-203.663</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.40309e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.21899999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5463298529664354</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9966130032339197</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.71676896098834</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.553522552966333</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.51388126886687</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.81503565292</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.667x + -7214.449</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>466.3156443603283</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>62791011.76172917</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.106332742237177e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8612522102451547</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-198.034</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.38424e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.45399999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.320733105169013</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.065937749813664</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.69329677443694</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.64859952839368</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.28982981625905</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.93631231606432</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.076x + -7358.138</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>462.6292425085679</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>101367344.4809037</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.057235159675903e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8674125484443523</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-196.684</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.36996e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.65300000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02308955365584387</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2962273406165908</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.230955514514277</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.133223712173573</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19.95224243670808</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.80957651988884</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.649x + -7022.076</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>458.8581701532798</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>42430884.49731868</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.02005034564565e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8722783261207379</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-192.038</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.35761e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.806</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.271176099736725</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8632295493782897</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.578816308790989</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.568733443599278</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.74756553282938</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.05776625480708</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.511x + -7434.344</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>455.0869893102939</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>74210787.16324848</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.922564139804294e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8759964846137275</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-189.362</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.34831e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.958</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7375631544367928</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.166167421999446</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.650315027091714</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.305217470755197</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.61770891371232</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.09417664486328</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.647x + -7428.082</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>451.5493399788623</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>145881031.8591446</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>9.670763581717393e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8795255559379543</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-189.543</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.34146e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.08499999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4843801294289575</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.32994268557688</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.118634061249154</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.00617605249601</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.00484263254724</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.318x + -7170.581</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>448.3053541255115</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>27559080.97169546</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9.463653600061264e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.882536788197224</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-187.516</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.33535e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.193</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.06022446530299828</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4887503189985041</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.536441576178775</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.267467342364317</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.25096327109982</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.05829791752852</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.513x + -7209.415</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>445.1064134618819</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>143682236.2221341</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.30002885933358e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.884943565494608</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-184.034</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.32944e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-79.298</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2970016313356598</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.005326027823049</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.706930591003404</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.499816020920369</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23.02256270212751</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.27178652094392</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 15.346x + -7605.863</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>442.0399033444564</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>355382726.0797141</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9.144436966195757e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8872742840777263</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-183.0409999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.32504e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-79.416</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2532910934620763</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.112229087297223</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.528161032653196</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.597229840480135</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23.45194191815173</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.21263108231373</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 15.106x + -7405.062</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>439.0231331823721</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>253139142.7484311</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.990603939861496e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8896628045424204</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-183.028</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.3227e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-79.515</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6378677810240075</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.302365557335614</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.231168559049447</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22.2081721504607</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.09831015066743</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 14.662x + -7101.120</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>436.0900456156388</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>110425024.3092927</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.868767868096841e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8916151497611586</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-180.176</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.31992e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.607</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.004435171210107106</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8094648509357272</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.452646407803397</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.212484525711077</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.4289478380131</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.21686815057282</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 15.123x + -7290.849</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>433.187297301179</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>44756321.40970081</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.754502068073215e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8934618427485918</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-179.3140000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.31527e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.66500000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5390021242613001</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.070161164165414</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.668888662435726</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.409355673089174</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22.91855394854259</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.35533008557465</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 15.699x + -7541.798</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>430.328627180213</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>204915776.1680939</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8.664470345149445e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8948725901518495</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-177.2739999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.31349e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.765</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3643890896918707</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8453801948027435</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.698536922345339</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.343762223860124</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22.80854492461772</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.37799283449269</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 15.798x + -7529.774</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>427.5118109095331</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>236039388.4358574</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.555866333473535e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8966884849992028</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-175.024</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.31111e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.85599999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5775117228490287</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.022711579728271</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.628840384171398</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.517901021395853</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23.58118865610425</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.44201250614353</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 16.083x + -7617.267</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>424.6600818163836</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>467146461.0758933</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.453533080133084e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.898406185788005</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-175.881</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.31054e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.937</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.09685203989231268</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5685338284950219</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.442970807435745</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.192420290822016</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22.781903876149</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.33631493433467</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 15.618x + -7309.896</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>421.7794216213097</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>177374146.0547042</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.36700635626022e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8999286810833996</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-173.083</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.30803e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.996</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7348494887905714</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.156915979215683</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.95047100214665</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.887146786916396</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25.58043844447385</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.55759977950409</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 16.624x + -7777.014</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>418.8648413205626</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>229731178.3723945</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8.29334772169683e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.901180577618217</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-173.056</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.308e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-80.07599999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3982373443570966</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.088019030154891</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.685246054501414</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.625350942684013</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25.20038396350387</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.47434297442163</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 16.231x + -7507.868</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>416.0055626305751</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>120526718.694884</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8.212145709939803e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9026517839142629</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-171.023</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.30646e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-80.157</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5415108053123554</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.153963007970476</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.690934445762615</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.597024038870879</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24.83299458204647</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.56979034950589</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 16.683x + -7676.419</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>413.0712188009529</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>121548027.0439025</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>8.129018748708925e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.904123777226483</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-371.366</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.48386e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72.426</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.464407036805686</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6227947881769539</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.412425566988911</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.087748790372248</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.989746360768549</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.7018265444289</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.808x + -5178.691</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>454.7140628599946</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>296787138.5262638</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.442896959231097e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-287.437</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.55766e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.372</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.36825653796398</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9830782953847407</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.738876564115999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.34347434991799</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.1345972705217</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.734x + -5595.680</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>493.7219846016717</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>684393800.2032897</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.145430711220483e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7682074996702765</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-254.654</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.49985e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.474</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2174740823336929</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.665381204577432</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.531696644955461</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.174559556798013</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.96356773191735</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.8710411289631</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.141x + -6219.262</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>487.0570230297017</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>83416286.49601777</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.559200790171495e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8135065963305714</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-235.508</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.44787e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.145</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4318945232710127</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9512198184338075</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.52583069807508</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.439315529110092</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.90156311660557</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.2661129986185</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.076x + -6630.670</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>481.4987956014188</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>97234133.54792821</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.341308952563464e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8341125685920484</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-224.22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.40734e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.616</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5233828772558503</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.015222101059186</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.529315879495205</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.172502424958999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.0237958747216</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.52379449953956</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.774x + -6913.118</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>475.6589047444313</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>40392632.62186754</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.215800879654981e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8473687714558438</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-220.336</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.3773e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.964</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08498440621873239</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5545245022986216</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.54542455599606</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.390616830179318</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.46871805133745</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.52758181703794</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 12.785x + -6779.459</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>469.5170387710796</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>237065273.760372</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.13258003917621e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8569422978983555</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-212.02</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.35741e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.289</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1254457280898007</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7588962091963971</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.430065130479381</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.416069223159731</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.57612246421361</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.71854653558464</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.357x + -6985.424</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>463.5401903201668</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>194730491.0327183</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.067916225075361e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8650359142213063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-205.276</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.34237e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.54600000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.763055379106334</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8076975056022773</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.539464313662918</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.182627006970885</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.22691353207595</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.92717248131648</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.044x + -7262.260</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>457.9519030044322</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>48138607.27177531</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.019854564218235e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8714067212329445</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-201.3249999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.33108e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.77500000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3509924758804119</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9763976557249112</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.61067014483494</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.698908343021163</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.66888514227622</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.98574501677405</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.250x + -7258.901</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>452.7277353084801</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>51712806.20927975</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9.815714045508991e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8767422580128512</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-198.921</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.32166e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.949</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3982951044651507</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8025505559272028</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.73252351030952</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.317778516365677</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.1485159166397</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.00640051918805</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.324x + -7197.159</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>447.9635293046174</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>68623519.53066643</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.532182013866964e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8808114597849536</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-318.979</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.06231e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.92700000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3845479297057577</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5853427330038721</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.368009598585035</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.999910024957944</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.00214520235519</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.31904019323876</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 10.053x + -6186.825</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6186.824596413466</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>519.5588140749594</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>318.979</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.846606468641e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7726976832521258</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-263.8910000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.01658e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.262</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8037512408050527</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.033109438989221</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.772339886195368</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.470926973875821</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.57290596688247</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.28703657916409</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 12.130x + -7254.536</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7254.536331230087</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>515.1447530719911</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>263.8910000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.320704692016398e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8206223692429329</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-249.354</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.01002e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-77.672</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1038561340040198</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7978692452520235</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.533344702110725</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.306458710094026</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.52437313992124</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.42140891304169</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 12.487x + -7341.728</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7341.728118451605</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>509.7921866305265</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>249.354</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.208039586293898e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8336700133681956</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-237.933</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.00951e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.985</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2701663118939374</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9648191692705834</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.824760286292498</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.421282501401598</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.42995625072856</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.69160508820447</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 13.274x + -7705.299</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7705.298839750636</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>500.2904901021955</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>237.933</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.124365288833633e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8444167437723781</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-232.605</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.03341e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.367</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1296755385574064</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8195420234838361</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.592554015208401</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.244106770824501</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.27020855510006</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.6495160290913</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 13.145x + -7311.638</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7311.638077076997</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>486.6667719982777</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>232.605</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.024358980873656e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8594018771637804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-225.703</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.04904e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.67</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3866251402718449</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7593663139502894</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.337668774811911</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.238099725959418</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.87034911768952</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.77472239040441</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 13.536x + -7322.592</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7322.592353732044</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>476.2120706421102</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>225.703</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.652224676637845e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8689490814493078</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-221.2890000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.0578e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.93000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1777446246158907</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7228030124591078</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.428752240155295</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.23411350238359</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.06487527526921</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.77259387230671</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 13.529x + -7129.048</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7129.047920876661</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>467.7221137386111</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>221.2890000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.230098307439331e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.875998154022779</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-217.24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.06198e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-79.127</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2310114130021612</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9108384694331664</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.476907687196027</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.408816668596422</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.22242904412619</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.89937489564757</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 13.949x + -7228.638</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7228.637771056801</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>460.9081317632145</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>217.24</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.916688351433397e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8813696414110527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-212.787</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.06765e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.301</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05317208811171149</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6035895388635084</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.381494455177385</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.138656845442183</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19.86553738430784</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.94808366500585</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 14.117x + -7197.512</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7197.511933054325</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>455.3187362866913</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>212.787</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.686734850159351e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.885505297278968</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-209.21</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.06819e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.45099999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.373491704239077</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9432675202739751</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.430791968920269</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.518442436930063</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.06314399125852</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.04956526492397</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 14.481x + -7299.500</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7299.499636574808</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>450.4767903568224</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>209.21</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.491878219584032e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8889358848696474</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>85.14651427036735</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.777x + -6742.022</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6742.022109887177</v>
       </c>
       <c r="Y2" t="n">
         <v>489.9742321541311</v>
       </c>
       <c r="Z2" t="n">
-        <v>148118181.4788225</v>
+        <v>244.097</v>
       </c>
       <c r="AA2" t="n">
         <v>1.478231451742328e-06</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>85.43425584999352</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.522x + -6812.803</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6812.802726634773</v>
       </c>
       <c r="Y3" t="n">
         <v>480.2581810792708</v>
       </c>
       <c r="Z3" t="n">
-        <v>38935196.01490787</v>
+        <v>222.042</v>
       </c>
       <c r="AA3" t="n">
         <v>1.174355328937243e-06</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>85.72503267955744</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.378x + -7195.355</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7195.355208348639</v>
       </c>
       <c r="Y4" t="n">
         <v>475.2972455033754</v>
       </c>
       <c r="Z4" t="n">
-        <v>53640759.67525764</v>
+        <v>213.101</v>
       </c>
       <c r="AA4" t="n">
         <v>1.094773477069725e-06</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>85.74488277369484</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.440x + -7129.177</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7129.177219382758</v>
       </c>
       <c r="Y5" t="n">
         <v>470.9425137897255</v>
       </c>
       <c r="Z5" t="n">
-        <v>44322862.68661626</v>
+        <v>210.652</v>
       </c>
       <c r="AA5" t="n">
         <v>1.045463250749225e-06</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>85.77791914159805</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.546x + -7093.683</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7093.682694217379</v>
       </c>
       <c r="Y6" t="n">
         <v>466.432824560886</v>
       </c>
       <c r="Z6" t="n">
-        <v>82130829.68119729</v>
+        <v>207.506</v>
       </c>
       <c r="AA6" t="n">
         <v>1.008757036480951e-06</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>86.00770599639398</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.328x + -7453.785</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7453.784650128228</v>
       </c>
       <c r="Y7" t="n">
         <v>461.8549488648044</v>
       </c>
       <c r="Z7" t="n">
-        <v>56724908.32590564</v>
+        <v>202.2909999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>9.76414534436509e-07</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>85.94466451637027</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.105x + -7223.820</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7223.820233961746</v>
       </c>
       <c r="Y8" t="n">
         <v>457.3615626041556</v>
       </c>
       <c r="Z8" t="n">
-        <v>67801734.22047524</v>
+        <v>201.451</v>
       </c>
       <c r="AA8" t="n">
         <v>9.486780199241122e-07</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>86.07607965060043</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.579x + -7406.363</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7406.362743820021</v>
       </c>
       <c r="Y9" t="n">
         <v>453.2546206910977</v>
       </c>
       <c r="Z9" t="n">
-        <v>503463074.8002728</v>
+        <v>198.793</v>
       </c>
       <c r="AA9" t="n">
         <v>9.275650692967625e-07</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>86.10565377072155</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.690x + -7384.208</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7384.207958212489</v>
       </c>
       <c r="Y10" t="n">
         <v>449.4920261038993</v>
       </c>
       <c r="Z10" t="n">
-        <v>367980904.6520852</v>
+        <v>196.66</v>
       </c>
       <c r="AA10" t="n">
         <v>9.080503930994159e-07</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>86.25781826491523</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.289x + -7641.013</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7641.013345132657</v>
       </c>
       <c r="Y11" t="n">
         <v>445.8780580103834</v>
       </c>
       <c r="Z11" t="n">
-        <v>141980293.9109289</v>
+        <v>191.855</v>
       </c>
       <c r="AA11" t="n">
         <v>8.895668155853722e-07</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>86.19457242780233</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 15.034x + -7422.647</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-7422.646926486967</v>
       </c>
       <c r="Y12" t="n">
         <v>442.3503984287934</v>
       </c>
       <c r="Z12" t="n">
-        <v>112240319.493892</v>
+        <v>193.032</v>
       </c>
       <c r="AA12" t="n">
         <v>8.764206311982184e-07</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>86.18119739029416</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 14.981x + -7320.492</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-7320.492460151338</v>
       </c>
       <c r="Y13" t="n">
         <v>438.9069988842543</v>
       </c>
       <c r="Z13" t="n">
-        <v>26001814.29875525</v>
+        <v>192.61</v>
       </c>
       <c r="AA13" t="n">
         <v>8.634925066014833e-07</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>86.23643882630302</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 15.202x + -7367.310</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7367.309836368556</v>
       </c>
       <c r="Y14" t="n">
         <v>435.5607166733957</v>
       </c>
       <c r="Z14" t="n">
-        <v>68972214.1317673</v>
+        <v>189.516</v>
       </c>
       <c r="AA14" t="n">
         <v>8.508675645135113e-07</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>86.18873829179076</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 15.011x + -7193.466</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-7193.465923212082</v>
       </c>
       <c r="Y15" t="n">
         <v>432.1663647990239</v>
       </c>
       <c r="Z15" t="n">
-        <v>355937089.6774742</v>
+        <v>189.105</v>
       </c>
       <c r="AA15" t="n">
         <v>8.401976279531202e-07</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>86.2659016490831</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 15.322x + -7289.453</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-7289.452757198575</v>
       </c>
       <c r="Y16" t="n">
         <v>428.8040168914721</v>
       </c>
       <c r="Z16" t="n">
-        <v>352665882.4857401</v>
+        <v>187.767</v>
       </c>
       <c r="AA16" t="n">
         <v>8.296606311151344e-07</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>86.27059090147748</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 15.342x + -7233.478</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7233.477705375245</v>
       </c>
       <c r="Y17" t="n">
         <v>425.5181398561159</v>
       </c>
       <c r="Z17" t="n">
-        <v>233348024.7402682</v>
+        <v>187.425</v>
       </c>
       <c r="AA17" t="n">
         <v>8.20844195289727e-07</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>86.37729202165276</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 15.795x + -7399.724</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7399.724136359128</v>
       </c>
       <c r="Y18" t="n">
         <v>422.2054309710713</v>
       </c>
       <c r="Z18" t="n">
-        <v>173599336.1105402</v>
+        <v>185.425</v>
       </c>
       <c r="AA18" t="n">
         <v>8.111308803992081e-07</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>86.25518816750865</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 15.278x + -7065.125</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7065.125182309032</v>
       </c>
       <c r="Y19" t="n">
         <v>418.8913705290404</v>
       </c>
       <c r="Z19" t="n">
-        <v>343891492.0842941</v>
+        <v>186.873</v>
       </c>
       <c r="AA19" t="n">
         <v>8.030844396002918e-07</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>86.41945351399555</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 15.981x + -7358.892</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7358.892142885788</v>
       </c>
       <c r="Y20" t="n">
         <v>415.6398467546637</v>
       </c>
       <c r="Z20" t="n">
-        <v>170711867.1082714</v>
+        <v>183.537</v>
       </c>
       <c r="AA20" t="n">
         <v>7.949215883028286e-07</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>86.43873896347283</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 16.068x + -7330.866</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7330.866382177048</v>
       </c>
       <c r="Y21" t="n">
         <v>412.3606945871971</v>
       </c>
       <c r="Z21" t="n">
-        <v>225638062.5626982</v>
+        <v>181.081</v>
       </c>
       <c r="AA21" t="n">
         <v>7.856700057113214e-07</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>86.27015346145507</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 15.340x + -6898.664</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-6898.664298580803</v>
       </c>
       <c r="Y22" t="n">
         <v>409.0709526386851</v>
       </c>
       <c r="Z22" t="n">
-        <v>223706718.6679012</v>
+        <v>184.1990000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>7.80187494533801e-07</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-252.2190000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.04393e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.526</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5128678408020836</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.010198460901405</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.753057614057082</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.654851914870114</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.11356296709194</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.37045796082725</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 12.349x + -7280.476</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7280.475695272173</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>499.1176390781113</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>252.2190000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.249454044055751e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8299942220424288</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-225.913</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.07706e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-78.378</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1955306492728645</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8346090242609679</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.620687598744095</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.362669443611765</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.03413791091354</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.70198419608978</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 13.306x + -7375.904</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7375.903936424929</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>486.2898482420558</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>225.913</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.035668630598142e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.859359573301552</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-218.407</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.07966e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.658</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4334773202270193</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.216060465862294</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.19418921396628</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.10699697142644</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.7228042362088</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 13.371x + -7260.903</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7260.903349333928</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>481.4264374623174</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>218.407</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.807443637112244e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8676408994231256</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-213.936</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.07754e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.816</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1128098140560156</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5480933134465793</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.45632799062722</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.392103392535487</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.34346435217874</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.85060828652833</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 13.784x + -7415.660</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7415.660134759206</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>477.3102502881576</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>213.936</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9.503341995736951e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8723129801885814</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-210.581</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.07555e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.95</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3814648350988993</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7400469682968751</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.518196759781987</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.239976347338744</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.1793928003085</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.97968856055924</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 14.228x + -7589.476</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7589.47571592912</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>472.9588709053863</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>210.581</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.261465598722945e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8761298590883635</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-206.0630000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.07626e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-79.09699999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7797265859284079</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9417643708241996</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.708120726229179</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.716087528872767</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.57531470783789</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.09102856914589</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 14.635x + -7732.434</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7732.434431159663</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>468.4717608769296</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>206.0630000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.03637099704054e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8798555448635064</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-205.4670000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.07525e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-79.20999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6056782124111291</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9975941515531509</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.648743558066118</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.460048320521651</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.77266558213071</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.08941493964015</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 14.629x + -7633.516</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7633.516383021247</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>464.1141487701912</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>205.4670000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.850825373548373e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8829553946364356</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-198.372</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.07573e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-79.35899999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.197156707757679</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.343889384146011</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.891830945225419</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.820965382163825</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.7919021481966</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.3369970745009</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 15.620x + -8116.589</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8116.589163396268</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>460.0229431340741</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>198.372</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.662062897082133e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.886201533607208</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-200.828</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.07423e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.43600000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4801313799470114</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.067847330544208</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.824302581011899</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.69832084277739</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.20842076285486</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.23085091490984</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 15.179x + -7777.134</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7777.134174220517</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>456.2402362992059</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>200.828</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.539360900901032e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8883164337014405</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-201.2020000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.07522e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.52800000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3219884691250597</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7404669856994633</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.458527584781532</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.508352093893085</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.9141269915061</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.1455908825501</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 14.843x + -7507.113</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7507.112775363232</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>452.6263035733331</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>201.2020000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.42081609816923e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8904541333673119</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-202.195</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.07495e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-79.599</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4060713520669976</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6227153238548443</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.420712858373282</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.302039866775125</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.69425925304807</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.10219382292112</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 14.677x + -7342.240</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-7342.240245234433</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>449.0300279010361</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>202.195</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.325347789270932e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8921685425401087</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-197.675</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.07495e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-79.709</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5441537152874398</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9344389408116007</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.536038053596743</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.197714762943662</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21.39979381547813</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.25619071657593</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 15.282x + -7606.439</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-7606.439003292698</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>445.5425135130176</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>197.675</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.20693032661026e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8943121180026801</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-196.662</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.07561e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-79.77200000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7747359672404535</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.17189043131714</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.94071100384978</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.912152116826619</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23.35274763797629</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.36223952402705</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 15.729x + -7787.122</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7787.121506335484</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>442.1132882423688</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>196.662</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.127781237429013e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8958032447841887</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-195.315</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.07588e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.873</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6376461958148864</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8843719676971835</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.686785722127975</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.642680109420358</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.15900321291861</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.34080378605297</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 15.637x + -7659.418</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-7659.417691555616</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>438.7846401522244</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>195.315</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.022724761816673e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8977678598770742</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-194.843</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.0782e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.95399999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2481860798644547</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7926315870408949</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.591118715946928</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.545663664073011</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22.39426097276289</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.28041387999662</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 15.382x + -7450.193</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-7450.193141842873</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>435.334903354623</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>194.843</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.947759096426171e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8992533863527454</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-194.53</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.0786e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-80.00700000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5489499351611101</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.151220398004392</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.760872953896504</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.499386584803543</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22.29640701652342</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.3823934739746</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 15.817x + -7618.619</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7618.619376268224</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>431.8980721291372</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>194.53</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.885532963749957e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.900456080681713</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-192.979</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.07895e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-80.09999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5426439490807828</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.897906125717846</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.621922968896409</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.834042995825286</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23.49761019033234</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.3717566834879</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 15.770x + -7518.766</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7518.765585391766</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>428.4997763259188</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>192.979</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.795747484222539e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9021921772586892</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-194.591</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.08034e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-80.15900000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1456429891133929</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7387318409051296</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.644947817427679</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.510226943894417</v>
+      </c>
+      <c r="J19" t="n">
+        <v>23.01736148891735</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.28548445354127</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 15.403x + -7255.863</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7255.863403884056</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>425.087672523999</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>194.591</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7.735203486760573e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9034251029183138</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-191.8320000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.08109e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-80.256</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3010772146332337</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8982335349571927</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.759301655848004</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.572200670504321</v>
+      </c>
+      <c r="J20" t="n">
+        <v>22.88572999399127</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.3838129704954</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 15.823x + -7405.167</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7405.167210656181</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>421.7213660033631</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>191.8320000000001</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.651207285496407e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9050834176348366</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-191.65</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.08281e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-80.313</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1157751344692449</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8083735790233221</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.570541387662018</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.35406224614756</v>
+      </c>
+      <c r="J21" t="n">
+        <v>22.44159439168356</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.38921301969647</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 15.847x + -7349.343</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7349.342759269707</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>418.3605202623948</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>191.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.594625391339403e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9062712972722259</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-192.124</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.0839e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-80.384</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.04192480855325642</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6313475509712926</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.347895192247431</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.255286379449523</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22.14836969215325</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.30979593016248</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 15.505x + -7104.663</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7104.662817970229</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>415.0494363389573</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>192.124</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.530284246436029e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9075943564179231</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>82.70459489039814</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.811x + -5664.476</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5664.475697975076</v>
       </c>
       <c r="Y2" t="n">
         <v>484.9861151643555</v>
       </c>
       <c r="Z2" t="n">
-        <v>332736872.0083891</v>
+        <v>391.198</v>
       </c>
       <c r="AA2" t="n">
         <v>1.29287172787754e-05</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>84.27422222106367</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.973x + -6235.017</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6235.016696184286</v>
       </c>
       <c r="Y3" t="n">
         <v>521.3350682481924</v>
       </c>
       <c r="Z3" t="n">
-        <v>400990891.9343027</v>
+        <v>296.4540000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>2.677452522839929e-06</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>84.67273293376704</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.724x + -6457.223</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6457.222985885509</v>
       </c>
       <c r="Y4" t="n">
         <v>517.3713649115799</v>
       </c>
       <c r="Z4" t="n">
-        <v>338453846.786369</v>
+        <v>270.971</v>
       </c>
       <c r="AA4" t="n">
         <v>1.817158349230833e-06</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>84.95536822507026</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.328x + -6711.920</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-6711.919872729918</v>
       </c>
       <c r="Y5" t="n">
         <v>513.1693295433734</v>
       </c>
       <c r="Z5" t="n">
-        <v>71587039.11022817</v>
+        <v>256.049</v>
       </c>
       <c r="AA5" t="n">
         <v>1.551584797607573e-06</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>85.19587264337859</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.898x + -6971.728</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-6971.727991215119</v>
       </c>
       <c r="Y6" t="n">
         <v>508.7904941824024</v>
       </c>
       <c r="Z6" t="n">
-        <v>53603483.59283476</v>
+        <v>246.5940000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.403257078285212e-06</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>85.27155152418317</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 12.090x + -6978.951</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6978.950978077645</v>
       </c>
       <c r="Y7" t="n">
         <v>504.1404758598058</v>
       </c>
       <c r="Z7" t="n">
-        <v>127015839.6190417</v>
+        <v>239.462</v>
       </c>
       <c r="AA7" t="n">
         <v>1.2989293958207e-06</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>85.56297724600542</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.887x + -7388.883</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7388.882746748612</v>
       </c>
       <c r="Y8" t="n">
         <v>499.4335336193562</v>
       </c>
       <c r="Z8" t="n">
-        <v>24540362.74458681</v>
+        <v>231.125</v>
       </c>
       <c r="AA8" t="n">
         <v>1.223309426751137e-06</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>85.51228589144141</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 12.741x + -7186.108</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7186.108315126336</v>
       </c>
       <c r="Y9" t="n">
         <v>494.6814522457348</v>
       </c>
       <c r="Z9" t="n">
-        <v>240916987.3990885</v>
+        <v>228.739</v>
       </c>
       <c r="AA9" t="n">
         <v>1.162745934544996e-06</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>85.64535672007067</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.132x + -7332.145</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7332.145161253643</v>
       </c>
       <c r="Y10" t="n">
         <v>489.836180994921</v>
       </c>
       <c r="Z10" t="n">
-        <v>410904260.3103519</v>
+        <v>224.625</v>
       </c>
       <c r="AA10" t="n">
         <v>1.116260850621299e-06</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>85.7085873613081</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 13.326x + -7347.821</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7347.820697820334</v>
       </c>
       <c r="Y11" t="n">
         <v>485.1460599920371</v>
       </c>
       <c r="Z11" t="n">
-        <v>60299381.14163633</v>
+        <v>221.218</v>
       </c>
       <c r="AA11" t="n">
         <v>1.073682635026227e-06</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>84.34137867276681</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.092x + -5851.073</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5851.072698290834</v>
       </c>
       <c r="Y2" t="n">
         <v>490.6367201800968</v>
       </c>
       <c r="Z2" t="n">
-        <v>444957475.7575544</v>
+        <v>288.5219999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.789976648279128e-06</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>85.00298876246667</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.437x + -6273.528</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6273.527778223771</v>
       </c>
       <c r="Y3" t="n">
         <v>480.9967073330358</v>
       </c>
       <c r="Z3" t="n">
-        <v>98211573.19599701</v>
+        <v>250.4160000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.292418458022157e-06</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>85.49559100147437</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.694x + -6896.835</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6896.834561365011</v>
       </c>
       <c r="Y4" t="n">
         <v>476.5104644538858</v>
       </c>
       <c r="Z4" t="n">
-        <v>174464456.9436574</v>
+        <v>233.221</v>
       </c>
       <c r="AA4" t="n">
         <v>1.167616733782872e-06</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>85.5016101024145</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.711x + -6797.388</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-6797.38766962644</v>
       </c>
       <c r="Y5" t="n">
         <v>472.7525593398541</v>
       </c>
       <c r="Z5" t="n">
-        <v>118491567.6754503</v>
+        <v>226.752</v>
       </c>
       <c r="AA5" t="n">
         <v>1.097665810904654e-06</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>85.73307133933369</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.403x + -7126.489</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7126.489023836115</v>
       </c>
       <c r="Y6" t="n">
         <v>468.9819122443698</v>
       </c>
       <c r="Z6" t="n">
-        <v>112812922.6847093</v>
+        <v>221.253</v>
       </c>
       <c r="AA6" t="n">
         <v>1.051812760341511e-06</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>85.80503641341028</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.634x + -7171.224</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7171.224210644265</v>
       </c>
       <c r="Y7" t="n">
         <v>465.0790243736301</v>
       </c>
       <c r="Z7" t="n">
-        <v>111156231.6956024</v>
+        <v>216.3349999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.013681429750216e-06</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>85.79298279271276</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.595x + -7055.838</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7055.838377605582</v>
       </c>
       <c r="Y8" t="n">
         <v>461.1516122042609</v>
       </c>
       <c r="Z8" t="n">
-        <v>66260437.21048671</v>
+        <v>212.8200000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>9.79331295351269e-07</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>85.86617075478213</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.836x + -7112.722</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7112.722165157036</v>
       </c>
       <c r="Y9" t="n">
         <v>457.3864809506157</v>
       </c>
       <c r="Z9" t="n">
-        <v>55553887.17777497</v>
+        <v>210.386</v>
       </c>
       <c r="AA9" t="n">
         <v>9.541075920291812e-07</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>86.04721851291664</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.472x + -7403.042</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7403.041572670372</v>
       </c>
       <c r="Y10" t="n">
         <v>453.7330725039115</v>
       </c>
       <c r="Z10" t="n">
-        <v>27254715.81268415</v>
+        <v>205.914</v>
       </c>
       <c r="AA10" t="n">
         <v>9.329199084660932e-07</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>85.90117617036917</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 13.955x + -7029.461</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7029.460609951821</v>
       </c>
       <c r="Y11" t="n">
         <v>450.2221643621617</v>
       </c>
       <c r="Z11" t="n">
-        <v>63839364.51118754</v>
+        <v>207.3650000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>9.158146631407134e-07</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>86.09682199415462</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 14.657x + -7356.216</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-7356.21618013666</v>
       </c>
       <c r="Y12" t="n">
         <v>446.8388964258468</v>
       </c>
       <c r="Z12" t="n">
-        <v>236340210.8547626</v>
+        <v>202.934</v>
       </c>
       <c r="AA12" t="n">
         <v>8.996273767565365e-07</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>86.11823548043371</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 14.738x + -7329.036</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-7329.036117939046</v>
       </c>
       <c r="Y13" t="n">
         <v>443.5286139056063</v>
       </c>
       <c r="Z13" t="n">
-        <v>104506479.3569433</v>
+        <v>200.639</v>
       </c>
       <c r="AA13" t="n">
         <v>8.846161540240556e-07</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>86.15113165755315</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 14.864x + -7328.840</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7328.840189038013</v>
       </c>
       <c r="Y14" t="n">
         <v>440.2728386421616</v>
       </c>
       <c r="Z14" t="n">
-        <v>48907273.27580757</v>
+        <v>198.266</v>
       </c>
       <c r="AA14" t="n">
         <v>8.702026283103438e-07</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>86.02377315489622</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 14.386x + -7005.441</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-7005.441102406066</v>
       </c>
       <c r="Y15" t="n">
         <v>436.9733621935648</v>
       </c>
       <c r="Z15" t="n">
-        <v>37707447.05188376</v>
+        <v>201.864</v>
       </c>
       <c r="AA15" t="n">
         <v>8.626656148130543e-07</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>86.19642498284472</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 15.042x + -7291.197</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-7291.197489787197</v>
       </c>
       <c r="Y16" t="n">
         <v>433.802254192731</v>
       </c>
       <c r="Z16" t="n">
-        <v>48255195.06780083</v>
+        <v>196.441</v>
       </c>
       <c r="AA16" t="n">
         <v>8.488422569119952e-07</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>86.09150478381427</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 14.637x + -7010.914</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7010.913950724082</v>
       </c>
       <c r="Y17" t="n">
         <v>430.589869034477</v>
       </c>
       <c r="Z17" t="n">
-        <v>16593249.91813339</v>
+        <v>198.597</v>
       </c>
       <c r="AA17" t="n">
         <v>8.396386542920469e-07</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>86.05765811255874</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 14.510x + -6876.684</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-6876.684018773698</v>
       </c>
       <c r="Y18" t="n">
         <v>427.3854692308652</v>
       </c>
       <c r="Z18" t="n">
-        <v>703133306.1587847</v>
+        <v>196.943</v>
       </c>
       <c r="AA18" t="n">
         <v>8.297869985299549e-07</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>86.15734959276618</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 14.888x + -7012.962</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7012.96178817961</v>
       </c>
       <c r="Y19" t="n">
         <v>424.2195163582124</v>
       </c>
       <c r="Z19" t="n">
-        <v>174618713.9645715</v>
+        <v>193.72</v>
       </c>
       <c r="AA19" t="n">
         <v>8.189301531234026e-07</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>86.20525123828185</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 15.077x + -7049.524</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7049.52408508412</v>
       </c>
       <c r="Y20" t="n">
         <v>421.0071287354223</v>
       </c>
       <c r="Z20" t="n">
-        <v>173122596.5523554</v>
+        <v>193.475</v>
       </c>
       <c r="AA20" t="n">
         <v>8.120594659232375e-07</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>86.2322946739904</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 15.185x + -7043.294</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7043.293606001984</v>
       </c>
       <c r="Y21" t="n">
         <v>417.8126408326631</v>
       </c>
       <c r="Z21" t="n">
-        <v>343337304.2052764</v>
+        <v>192.172</v>
       </c>
       <c r="AA21" t="n">
         <v>8.040902748043091e-07</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>86.38932829967922</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 15.847x + -7317.219</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7317.219125309516</v>
       </c>
       <c r="Y22" t="n">
         <v>414.5699333941683</v>
       </c>
       <c r="Z22" t="n">
-        <v>170322252.8409989</v>
+        <v>188.014</v>
       </c>
       <c r="AA22" t="n">
         <v>7.943590377711847e-07</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>82.77194845816865</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.885x + -5573.694</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5573.693806484659</v>
       </c>
       <c r="Y2" t="n">
         <v>479.2253385644894</v>
       </c>
       <c r="Z2" t="n">
-        <v>472354131.9910227</v>
+        <v>372.9979999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.352861052745718e-05</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>84.02418309048512</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.553x + -5894.239</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-5894.239021872533</v>
       </c>
       <c r="Y3" t="n">
         <v>511.49299941495</v>
       </c>
       <c r="Z3" t="n">
-        <v>902520402.7178111</v>
+        <v>296.955</v>
       </c>
       <c r="AA3" t="n">
         <v>3.526782239979953e-06</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>84.57038930128259</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.521x + -6293.620</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6293.619681130627</v>
       </c>
       <c r="Y4" t="n">
         <v>511.259118049216</v>
       </c>
       <c r="Z4" t="n">
-        <v>367048545.7249072</v>
+        <v>269.418</v>
       </c>
       <c r="AA4" t="n">
         <v>2.181476508861705e-06</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>84.88794457234106</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.178x + -6581.251</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-6581.25142678913</v>
       </c>
       <c r="Y5" t="n">
         <v>507.8293741020886</v>
       </c>
       <c r="Z5" t="n">
-        <v>304339646.6292965</v>
+        <v>253.001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.78223714246108e-06</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>85.16016319501142</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.810x + -6871.508</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-6871.507724383208</v>
       </c>
       <c r="Y6" t="n">
         <v>503.5583085184324</v>
       </c>
       <c r="Z6" t="n">
-        <v>31448815.66216073</v>
+        <v>242.379</v>
       </c>
       <c r="AA6" t="n">
         <v>1.565254805349706e-06</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>85.30933337209662</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 12.188x + -6990.027</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6990.026653880045</v>
       </c>
       <c r="Y7" t="n">
         <v>498.6612136504206</v>
       </c>
       <c r="Z7" t="n">
-        <v>271746175.66655</v>
+        <v>234.2009999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.421163704164713e-06</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>85.41296251207909</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.464x + -7046.551</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7046.55101699981</v>
       </c>
       <c r="Y8" t="n">
         <v>493.5944305799873</v>
       </c>
       <c r="Z8" t="n">
-        <v>207468445.7795521</v>
+        <v>227.5229999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.317363148607506e-06</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>85.4649106739612</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 12.607x + -7016.857</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7016.856535205619</v>
       </c>
       <c r="Y9" t="n">
         <v>488.5616172285689</v>
       </c>
       <c r="Z9" t="n">
-        <v>273495237.9056231</v>
+        <v>222.327</v>
       </c>
       <c r="AA9" t="n">
         <v>1.234759630935135e-06</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>85.60893138353242</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.023x + -7168.371</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7168.370743560709</v>
       </c>
       <c r="Y10" t="n">
         <v>483.6703421743699</v>
       </c>
       <c r="Z10" t="n">
-        <v>38899764.29307637</v>
+        <v>218.6819999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.171538292361146e-06</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>85.59917131842867</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.994x + -7046.443</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7046.44320841293</v>
       </c>
       <c r="Y11" t="n">
         <v>479.1177921100242</v>
       </c>
       <c r="Z11" t="n">
-        <v>134952739.5320344</v>
+        <v>215.037</v>
       </c>
       <c r="AA11" t="n">
         <v>1.121123047400696e-06</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>83.81631011434521</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.230x + -5459.126</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5459.126046942333</v>
       </c>
       <c r="Y2" t="n">
         <v>495.8142821417966</v>
       </c>
       <c r="Z2" t="n">
-        <v>156362982.2244543</v>
+        <v>305.5329999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>2.939460051597208e-06</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>84.66449696472088</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.708x + -6046.520</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6046.519547476223</v>
       </c>
       <c r="Y3" t="n">
         <v>489.3332543864511</v>
       </c>
       <c r="Z3" t="n">
-        <v>22716617.17866769</v>
+        <v>263.838</v>
       </c>
       <c r="AA3" t="n">
         <v>1.723593905626079e-06</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>84.9938808202409</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.416x + -6307.153</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6307.153016777313</v>
       </c>
       <c r="Y4" t="n">
         <v>484.174340005828</v>
       </c>
       <c r="Z4" t="n">
-        <v>78898726.29831912</v>
+        <v>244.96</v>
       </c>
       <c r="AA4" t="n">
         <v>1.445534303458247e-06</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>85.2567288732417</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.052x + -6567.897</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-6567.897026605417</v>
       </c>
       <c r="Y5" t="n">
         <v>479.4093085140572</v>
       </c>
       <c r="Z5" t="n">
-        <v>171103766.1913403</v>
+        <v>232.9459999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.299772470422183e-06</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>85.36876273292559</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.345x + -6629.071</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-6629.071089220419</v>
       </c>
       <c r="Y6" t="n">
         <v>474.5617476358946</v>
       </c>
       <c r="Z6" t="n">
-        <v>65175634.19993156</v>
+        <v>225.91</v>
       </c>
       <c r="AA6" t="n">
         <v>1.206148627871701e-06</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>85.65429685905549</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.159x + -7007.294</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7007.293960867753</v>
       </c>
       <c r="Y7" t="n">
         <v>469.7630187700368</v>
       </c>
       <c r="Z7" t="n">
-        <v>104170035.1149336</v>
+        <v>216.5250000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.135032723436958e-06</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>85.62865855973675</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.082x + -6852.534</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-6852.533653382613</v>
       </c>
       <c r="Y8" t="n">
         <v>465.0424294029989</v>
       </c>
       <c r="Z8" t="n">
-        <v>108463446.6572052</v>
+        <v>213.976</v>
       </c>
       <c r="AA8" t="n">
         <v>1.083236618129556e-06</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>85.70910225532666</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.328x + -6896.546</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-6896.546207187512</v>
       </c>
       <c r="Y9" t="n">
         <v>460.5687854783792</v>
       </c>
       <c r="Z9" t="n">
-        <v>106565178.2821618</v>
+        <v>210.085</v>
       </c>
       <c r="AA9" t="n">
         <v>1.040844649526188e-06</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>85.79834206250902</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.612x + -6967.257</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-6967.256924568538</v>
       </c>
       <c r="Y10" t="n">
         <v>456.3086191296907</v>
       </c>
       <c r="Z10" t="n">
-        <v>40386859.37707627</v>
+        <v>205.7130000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.006394073931005e-06</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>85.81055176757511</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 13.652x + -6904.240</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-6904.239530447566</v>
       </c>
       <c r="Y11" t="n">
         <v>452.2078351562517</v>
       </c>
       <c r="Z11" t="n">
-        <v>62697817.95367827</v>
+        <v>204.225</v>
       </c>
       <c r="AA11" t="n">
         <v>9.803227553144902e-07</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>85.9756923366898</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 14.214x + -7139.873</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-7139.873421238864</v>
       </c>
       <c r="Y12" t="n">
         <v>448.3115515227257</v>
       </c>
       <c r="Z12" t="n">
-        <v>96016442.48212782</v>
+        <v>200.006</v>
       </c>
       <c r="AA12" t="n">
         <v>9.569377701865932e-07</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>85.88751051667424</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 13.908x + -6889.204</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-6889.204435189553</v>
       </c>
       <c r="Y13" t="n">
         <v>444.6650435858865</v>
       </c>
       <c r="Z13" t="n">
-        <v>180879024.3102809</v>
+        <v>199.599</v>
       </c>
       <c r="AA13" t="n">
         <v>9.361365042195794e-07</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>86.10551997027011</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 14.689x + -7245.118</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7245.118436099759</v>
       </c>
       <c r="Y14" t="n">
         <v>441.1438797420638</v>
       </c>
       <c r="Z14" t="n">
-        <v>26692653.95806248</v>
+        <v>194.5389999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>9.169170173836528e-07</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>86.05576800368037</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 14.504x + -7071.457</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-7071.456782491423</v>
       </c>
       <c r="Y15" t="n">
         <v>437.784385584846</v>
       </c>
       <c r="Z15" t="n">
-        <v>53063169.06322414</v>
+        <v>194.054</v>
       </c>
       <c r="AA15" t="n">
         <v>9.019821697617403e-07</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>86.17066780525838</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 14.940x + -7240.649</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-7240.648976410118</v>
       </c>
       <c r="Y16" t="n">
         <v>434.5817543191504</v>
       </c>
       <c r="Z16" t="n">
-        <v>482158631.2871308</v>
+        <v>190.3729999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>8.881227119662631e-07</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>86.13380830266429</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 14.797x + -7098.044</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7098.044478056531</v>
       </c>
       <c r="Y17" t="n">
         <v>431.4658987977885</v>
       </c>
       <c r="Z17" t="n">
-        <v>66454227.7795037</v>
+        <v>191.122</v>
       </c>
       <c r="AA17" t="n">
         <v>8.778198949022282e-07</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>86.25571142886017</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 15.280x + -7292.477</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7292.476624573471</v>
       </c>
       <c r="Y18" t="n">
         <v>428.3829152722445</v>
       </c>
       <c r="Z18" t="n">
-        <v>353225684.149655</v>
+        <v>187.501</v>
       </c>
       <c r="AA18" t="n">
         <v>8.644316165480016e-07</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>86.1929289729532</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 15.028x + -7092.611</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7092.611485683071</v>
       </c>
       <c r="Y19" t="n">
         <v>425.3353741601115</v>
       </c>
       <c r="Z19" t="n">
-        <v>116867376.7142304</v>
+        <v>187.153</v>
       </c>
       <c r="AA19" t="n">
         <v>8.536167775033069e-07</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>86.22281452282172</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 15.147x + -7095.152</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7095.151652313633</v>
       </c>
       <c r="Y20" t="n">
         <v>422.2906207194653</v>
       </c>
       <c r="Z20" t="n">
-        <v>231628942.6914996</v>
+        <v>186.256</v>
       </c>
       <c r="AA20" t="n">
         <v>8.443795545922185e-07</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>86.19572113363522</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 15.039x + -6975.334</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-6975.334469223051</v>
       </c>
       <c r="Y21" t="n">
         <v>419.3044655653769</v>
       </c>
       <c r="Z21" t="n">
-        <v>229870125.7516502</v>
+        <v>185.118</v>
       </c>
       <c r="AA21" t="n">
         <v>8.342861206783969e-07</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>86.28564577899618</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 15.404x + -7100.616</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7100.616029708968</v>
       </c>
       <c r="Y22" t="n">
         <v>416.3153368583119</v>
       </c>
       <c r="Z22" t="n">
-        <v>369199774.5804985</v>
+        <v>182.796</v>
       </c>
       <c r="AA22" t="n">
         <v>8.240718858778662e-07</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>82.58538992846334</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.684x + -5422.829</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5422.829001986913</v>
       </c>
       <c r="Y2" t="n">
         <v>473.7338192961772</v>
       </c>
       <c r="Z2" t="n">
-        <v>3662580913.677582</v>
+        <v>374.218</v>
       </c>
       <c r="AA2" t="n">
         <v>1.362371856452821e-05</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>84.20194311112579</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.848x + -5935.182</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-5935.181640114986</v>
       </c>
       <c r="Y3" t="n">
         <v>505.2416117076925</v>
       </c>
       <c r="Z3" t="n">
-        <v>1013067522.250978</v>
+        <v>283.105</v>
       </c>
       <c r="AA3" t="n">
         <v>2.907913506570322e-06</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>84.73115555062793</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.844x + -6306.032</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6306.031847322581</v>
       </c>
       <c r="Y4" t="n">
         <v>501.9309252934821</v>
       </c>
       <c r="Z4" t="n">
-        <v>462625513.1415778</v>
+        <v>255.4689999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.896365003181546e-06</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>85.10512346645012</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.677x + -6693.239</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-6693.238552575581</v>
       </c>
       <c r="Y5" t="n">
         <v>498.1829296978888</v>
       </c>
       <c r="Z5" t="n">
-        <v>290644206.8760032</v>
+        <v>237.8200000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.591777310518496e-06</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>85.38209844644207</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.380x + -7021.645</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7021.644868862996</v>
       </c>
       <c r="Y6" t="n">
         <v>494.0539812384313</v>
       </c>
       <c r="Z6" t="n">
-        <v>92908426.54140775</v>
+        <v>226.275</v>
       </c>
       <c r="AA6" t="n">
         <v>1.426486985183265e-06</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>85.46358061360702</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 12.604x + -7046.791</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7046.79146399494</v>
       </c>
       <c r="Y7" t="n">
         <v>489.4233714150621</v>
       </c>
       <c r="Z7" t="n">
-        <v>227679531.9324244</v>
+        <v>221.2859999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.316241109357098e-06</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>85.6395974237423</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.115x + -7248.826</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7248.825986570318</v>
       </c>
       <c r="Y8" t="n">
         <v>484.6246491553262</v>
       </c>
       <c r="Z8" t="n">
-        <v>160794777.1034012</v>
+        <v>212.8420000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.231416102251103e-06</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>85.75641327648039</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.477x + -7355.659</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7355.659449026061</v>
       </c>
       <c r="Y9" t="n">
         <v>479.7650701934186</v>
       </c>
       <c r="Z9" t="n">
-        <v>134412634.0496769</v>
+        <v>208.4019999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.16560288558556e-06</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>85.71535107482742</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.347x + -7170.807</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7170.807106811348</v>
       </c>
       <c r="Y10" t="n">
         <v>475.0659821543966</v>
       </c>
       <c r="Z10" t="n">
-        <v>75374975.55866922</v>
+        <v>205.607</v>
       </c>
       <c r="AA10" t="n">
         <v>1.114184749502611e-06</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>85.98735396082425</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.255x + -7612.880</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7612.879650833882</v>
       </c>
       <c r="Y11" t="n">
         <v>470.5584005846731</v>
       </c>
       <c r="Z11" t="n">
-        <v>162780846.5726622</v>
+        <v>199.8399999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.072257515075533e-06</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>84.78155887837785</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.949x + -6274.936</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6274.935947885607</v>
       </c>
       <c r="Y2" t="n">
         <v>484.884699817303</v>
       </c>
       <c r="Z2" t="n">
-        <v>355113031.7250056</v>
+        <v>255.231</v>
       </c>
       <c r="AA2" t="n">
         <v>1.808766172188195e-06</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>85.52275984351037</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.771x + -6945.695</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6945.694822136638</v>
       </c>
       <c r="Y3" t="n">
         <v>474.7035148491834</v>
       </c>
       <c r="Z3" t="n">
-        <v>206070272.7912714</v>
+        <v>220.418</v>
       </c>
       <c r="AA3" t="n">
         <v>1.298060893215393e-06</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>85.59049512193246</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.968x + -6902.712</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6902.711823665977</v>
       </c>
       <c r="Y4" t="n">
         <v>470.0777566933614</v>
       </c>
       <c r="Z4" t="n">
-        <v>113522863.573035</v>
+        <v>211.413</v>
       </c>
       <c r="AA4" t="n">
         <v>1.173991412747739e-06</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>85.81503565292</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.667x + -7214.449</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7214.44922391076</v>
       </c>
       <c r="Y5" t="n">
         <v>466.3156443603283</v>
       </c>
       <c r="Z5" t="n">
-        <v>62791011.76172917</v>
+        <v>203.663</v>
       </c>
       <c r="AA5" t="n">
         <v>1.106332742237177e-06</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>85.93631231606432</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.076x + -7358.138</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7358.138420855429</v>
       </c>
       <c r="Y6" t="n">
         <v>462.6292425085679</v>
       </c>
       <c r="Z6" t="n">
-        <v>101367344.4809037</v>
+        <v>198.034</v>
       </c>
       <c r="AA6" t="n">
         <v>1.057235159675903e-06</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>85.80957651988884</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.649x + -7022.076</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7022.075921221984</v>
       </c>
       <c r="Y7" t="n">
         <v>458.8581701532798</v>
       </c>
       <c r="Z7" t="n">
-        <v>42430884.49731868</v>
+        <v>196.684</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02005034564565e-06</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>86.05776625480708</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.511x + -7434.344</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7434.344010347481</v>
       </c>
       <c r="Y8" t="n">
         <v>455.0869893102939</v>
       </c>
       <c r="Z8" t="n">
-        <v>74210787.16324848</v>
+        <v>192.038</v>
       </c>
       <c r="AA8" t="n">
         <v>9.922564139804294e-07</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>86.09417664486328</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.647x + -7428.082</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7428.082345821925</v>
       </c>
       <c r="Y9" t="n">
         <v>451.5493399788623</v>
       </c>
       <c r="Z9" t="n">
-        <v>145881031.8591446</v>
+        <v>189.362</v>
       </c>
       <c r="AA9" t="n">
         <v>9.670763581717393e-07</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>86.00484263254724</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.318x + -7170.581</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7170.580770642491</v>
       </c>
       <c r="Y10" t="n">
         <v>448.3053541255115</v>
       </c>
       <c r="Z10" t="n">
-        <v>27559080.97169546</v>
+        <v>189.543</v>
       </c>
       <c r="AA10" t="n">
         <v>9.463653600061264e-07</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>86.05829791752852</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.513x + -7209.415</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7209.415035910584</v>
       </c>
       <c r="Y11" t="n">
         <v>445.1064134618819</v>
       </c>
       <c r="Z11" t="n">
-        <v>143682236.2221341</v>
+        <v>187.516</v>
       </c>
       <c r="AA11" t="n">
         <v>9.30002885933358e-07</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>86.27178652094392</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 15.346x + -7605.863</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-7605.863129560093</v>
       </c>
       <c r="Y12" t="n">
         <v>442.0399033444564</v>
       </c>
       <c r="Z12" t="n">
-        <v>355382726.0797141</v>
+        <v>184.034</v>
       </c>
       <c r="AA12" t="n">
         <v>9.144436966195757e-07</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>86.21263108231373</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 15.106x + -7405.062</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-7405.061580935761</v>
       </c>
       <c r="Y13" t="n">
         <v>439.0231331823721</v>
       </c>
       <c r="Z13" t="n">
-        <v>253139142.7484311</v>
+        <v>183.0409999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>8.990603939861496e-07</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>86.09831015066743</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 14.662x + -7101.120</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7101.120272662076</v>
       </c>
       <c r="Y14" t="n">
         <v>436.0900456156388</v>
       </c>
       <c r="Z14" t="n">
-        <v>110425024.3092927</v>
+        <v>183.028</v>
       </c>
       <c r="AA14" t="n">
         <v>8.868767868096841e-07</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>86.21686815057282</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 15.123x + -7290.849</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-7290.849198095433</v>
       </c>
       <c r="Y15" t="n">
         <v>433.187297301179</v>
       </c>
       <c r="Z15" t="n">
-        <v>44756321.40970081</v>
+        <v>180.176</v>
       </c>
       <c r="AA15" t="n">
         <v>8.754502068073215e-07</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>86.35533008557465</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 15.699x + -7541.798</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-7541.798441316817</v>
       </c>
       <c r="Y16" t="n">
         <v>430.328627180213</v>
       </c>
       <c r="Z16" t="n">
-        <v>204915776.1680939</v>
+        <v>179.3140000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>8.664470345149445e-07</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>86.37799283449269</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 15.798x + -7529.774</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7529.773770926233</v>
       </c>
       <c r="Y17" t="n">
         <v>427.5118109095331</v>
       </c>
       <c r="Z17" t="n">
-        <v>236039388.4358574</v>
+        <v>177.2739999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>8.555866333473535e-07</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>86.44201250614353</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 16.083x + -7617.267</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7617.267294575604</v>
       </c>
       <c r="Y18" t="n">
         <v>424.6600818163836</v>
       </c>
       <c r="Z18" t="n">
-        <v>467146461.0758933</v>
+        <v>175.024</v>
       </c>
       <c r="AA18" t="n">
         <v>8.453533080133084e-07</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>86.33631493433467</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 15.618x + -7309.896</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7309.895856728192</v>
       </c>
       <c r="Y19" t="n">
         <v>421.7794216213097</v>
       </c>
       <c r="Z19" t="n">
-        <v>177374146.0547042</v>
+        <v>175.881</v>
       </c>
       <c r="AA19" t="n">
         <v>8.36700635626022e-07</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>86.55759977950409</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 16.624x + -7777.014</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7777.014113823913</v>
       </c>
       <c r="Y20" t="n">
         <v>418.8648413205626</v>
       </c>
       <c r="Z20" t="n">
-        <v>229731178.3723945</v>
+        <v>173.083</v>
       </c>
       <c r="AA20" t="n">
         <v>8.29334772169683e-07</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>86.47434297442163</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 16.231x + -7507.868</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7507.868026603772</v>
       </c>
       <c r="Y21" t="n">
         <v>416.0055626305751</v>
       </c>
       <c r="Z21" t="n">
-        <v>120526718.694884</v>
+        <v>173.056</v>
       </c>
       <c r="AA21" t="n">
         <v>8.212145709939803e-07</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>86.56979034950589</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 16.683x + -7676.419</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7676.419263588273</v>
       </c>
       <c r="Y22" t="n">
         <v>413.0712188009529</v>
       </c>
       <c r="Z22" t="n">
-        <v>121548027.0439025</v>
+        <v>171.023</v>
       </c>
       <c r="AA22" t="n">
         <v>8.129018748708925e-07</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>82.7018265444289</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.808x + -5178.691</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5178.691403244354</v>
       </c>
       <c r="Y2" t="n">
         <v>454.7140628599946</v>
       </c>
       <c r="Z2" t="n">
-        <v>296787138.5262638</v>
+        <v>371.366</v>
       </c>
       <c r="AA2" t="n">
         <v>1.442896959231097e-05</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>84.1345972705217</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.734x + -5595.680</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-5595.680165755084</v>
       </c>
       <c r="Y3" t="n">
         <v>493.7219846016717</v>
       </c>
       <c r="Z3" t="n">
-        <v>684393800.2032897</v>
+        <v>287.437</v>
       </c>
       <c r="AA3" t="n">
         <v>2.145430711220483e-06</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>84.8710411289631</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.141x + -6219.262</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6219.262191740373</v>
       </c>
       <c r="Y4" t="n">
         <v>487.0570230297017</v>
       </c>
       <c r="Z4" t="n">
-        <v>83416286.49601777</v>
+        <v>254.654</v>
       </c>
       <c r="AA4" t="n">
         <v>1.559200790171495e-06</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>85.2661129986185</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.076x + -6630.670</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-6630.67046464207</v>
       </c>
       <c r="Y5" t="n">
         <v>481.4987956014188</v>
       </c>
       <c r="Z5" t="n">
-        <v>97234133.54792821</v>
+        <v>235.508</v>
       </c>
       <c r="AA5" t="n">
         <v>1.341308952563464e-06</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>85.52379449953956</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.774x + -6913.118</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-6913.117957816235</v>
       </c>
       <c r="Y6" t="n">
         <v>475.6589047444313</v>
       </c>
       <c r="Z6" t="n">
-        <v>40392632.62186754</v>
+        <v>224.22</v>
       </c>
       <c r="AA6" t="n">
         <v>1.215800879654981e-06</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>85.52758181703794</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 12.785x + -6779.459</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6779.458745065738</v>
       </c>
       <c r="Y7" t="n">
         <v>469.5170387710796</v>
       </c>
       <c r="Z7" t="n">
-        <v>237065273.760372</v>
+        <v>220.336</v>
       </c>
       <c r="AA7" t="n">
         <v>1.13258003917621e-06</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>85.71854653558464</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.357x + -6985.424</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-6985.424340662788</v>
       </c>
       <c r="Y8" t="n">
         <v>463.5401903201668</v>
       </c>
       <c r="Z8" t="n">
-        <v>194730491.0327183</v>
+        <v>212.02</v>
       </c>
       <c r="AA8" t="n">
         <v>1.067916225075361e-06</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>85.92717248131648</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.044x + -7262.260</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7262.25964341097</v>
       </c>
       <c r="Y9" t="n">
         <v>457.9519030044322</v>
       </c>
       <c r="Z9" t="n">
-        <v>48138607.27177531</v>
+        <v>205.276</v>
       </c>
       <c r="AA9" t="n">
         <v>1.019854564218235e-06</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>85.98574501677405</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.250x + -7258.901</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7258.901441500197</v>
       </c>
       <c r="Y10" t="n">
         <v>452.7277353084801</v>
       </c>
       <c r="Z10" t="n">
-        <v>51712806.20927975</v>
+        <v>201.3249999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>9.815714045508991e-07</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>86.00640051918805</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.324x + -7197.159</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7197.159314864291</v>
       </c>
       <c r="Y11" t="n">
         <v>447.9635293046174</v>
       </c>
       <c r="Z11" t="n">
-        <v>68623519.53066643</v>
+        <v>198.921</v>
       </c>
       <c r="AA11" t="n">
         <v>9.532182013866964e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>84.31904019323876</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.053x + -6186.825</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.05250869740089</v>
       </c>
       <c r="X2" t="n">
         <v>-6186.824596413466</v>
@@ -600,7 +598,7 @@
         <v>519.5588140749594</v>
       </c>
       <c r="Z2" t="n">
-        <v>318.979</v>
+        <v>413292553.9670471</v>
       </c>
       <c r="AA2" t="n">
         <v>1.846606468641e-06</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>85.28703657916409</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.130x + -7254.536</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.12962880506918</v>
       </c>
       <c r="X3" t="n">
         <v>-7254.536331230087</v>
@@ -652,7 +648,7 @@
         <v>515.1447530719911</v>
       </c>
       <c r="Z3" t="n">
-        <v>263.8910000000001</v>
+        <v>76340363.52911051</v>
       </c>
       <c r="AA3" t="n">
         <v>1.320704692016398e-06</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>85.42140891304169</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.487x + -7341.728</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.48719656247537</v>
       </c>
       <c r="X4" t="n">
         <v>-7341.728118451605</v>
@@ -704,7 +698,7 @@
         <v>509.7921866305265</v>
       </c>
       <c r="Z4" t="n">
-        <v>249.354</v>
+        <v>36670084.60525571</v>
       </c>
       <c r="AA4" t="n">
         <v>1.208039586293898e-06</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>85.69160508820447</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.274x + -7705.299</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.27356221133092</v>
       </c>
       <c r="X5" t="n">
         <v>-7705.298839750636</v>
@@ -756,7 +748,7 @@
         <v>500.2904901021955</v>
       </c>
       <c r="Z5" t="n">
-        <v>237.933</v>
+        <v>382593169.5692241</v>
       </c>
       <c r="AA5" t="n">
         <v>1.124365288833633e-06</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>85.6495160290913</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.145x + -7311.638</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.1446584816687</v>
       </c>
       <c r="X6" t="n">
         <v>-7311.638077076997</v>
@@ -808,7 +798,7 @@
         <v>486.6667719982777</v>
       </c>
       <c r="Z6" t="n">
-        <v>232.605</v>
+        <v>125436262.6919927</v>
       </c>
       <c r="AA6" t="n">
         <v>1.024358980873656e-06</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>85.77472239040441</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.536x + -7322.592</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.53564966542519</v>
       </c>
       <c r="X7" t="n">
         <v>-7322.592353732044</v>
@@ -860,7 +848,7 @@
         <v>476.2120706421102</v>
       </c>
       <c r="Z7" t="n">
-        <v>225.703</v>
+        <v>89002016.8540733</v>
       </c>
       <c r="AA7" t="n">
         <v>9.652224676637845e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>85.77259387230671</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.529x + -7129.048</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.52880962644852</v>
       </c>
       <c r="X8" t="n">
         <v>-7129.047920876661</v>
@@ -912,7 +898,7 @@
         <v>467.7221137386111</v>
       </c>
       <c r="Z8" t="n">
-        <v>221.2890000000001</v>
+        <v>55643978.7912456</v>
       </c>
       <c r="AA8" t="n">
         <v>9.230098307439331e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>85.89937489564757</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.949x + -7228.638</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.94858544649129</v>
       </c>
       <c r="X9" t="n">
         <v>-7228.637771056801</v>
@@ -964,7 +948,7 @@
         <v>460.9081317632145</v>
       </c>
       <c r="Z9" t="n">
-        <v>217.24</v>
+        <v>27752247.97604188</v>
       </c>
       <c r="AA9" t="n">
         <v>8.916688351433397e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>85.94808366500585</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.117x + -7197.512</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.11683428752971</v>
       </c>
       <c r="X10" t="n">
         <v>-7197.511933054325</v>
@@ -1016,7 +998,7 @@
         <v>455.3187362866913</v>
       </c>
       <c r="Z10" t="n">
-        <v>212.787</v>
+        <v>130385447.7159736</v>
       </c>
       <c r="AA10" t="n">
         <v>8.686734850159351e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>86.04956526492397</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.481x + -7299.500</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.48067438528013</v>
       </c>
       <c r="X11" t="n">
         <v>-7299.499636574808</v>
@@ -1068,7 +1048,7 @@
         <v>450.4767903568224</v>
       </c>
       <c r="Z11" t="n">
-        <v>209.21</v>
+        <v>57381590.60732438</v>
       </c>
       <c r="AA11" t="n">
         <v>8.491878219584032e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>85.14651427036735</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.777x + -6742.022</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.7768284397507</v>
       </c>
       <c r="X2" t="n">
         <v>-6742.022109887177</v>
@@ -1266,7 +1244,7 @@
         <v>489.9742321541311</v>
       </c>
       <c r="Z2" t="n">
-        <v>244.097</v>
+        <v>148118181.4788225</v>
       </c>
       <c r="AA2" t="n">
         <v>1.478231451742328e-06</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>85.43425584999352</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.522x + -6812.803</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.52248243356156</v>
       </c>
       <c r="X3" t="n">
         <v>-6812.802726634773</v>
@@ -1318,7 +1294,7 @@
         <v>480.2581810792708</v>
       </c>
       <c r="Z3" t="n">
-        <v>222.042</v>
+        <v>38935196.01490787</v>
       </c>
       <c r="AA3" t="n">
         <v>1.174355328937243e-06</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>85.72503267955744</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.378x + -7195.355</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.3777439907933</v>
       </c>
       <c r="X4" t="n">
         <v>-7195.355208348639</v>
@@ -1370,7 +1344,7 @@
         <v>475.2972455033754</v>
       </c>
       <c r="Z4" t="n">
-        <v>213.101</v>
+        <v>53640759.67525764</v>
       </c>
       <c r="AA4" t="n">
         <v>1.094773477069725e-06</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>85.74488277369484</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.440x + -7129.177</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.44038275558935</v>
       </c>
       <c r="X5" t="n">
         <v>-7129.177219382758</v>
@@ -1422,7 +1394,7 @@
         <v>470.9425137897255</v>
       </c>
       <c r="Z5" t="n">
-        <v>210.652</v>
+        <v>44322862.68661626</v>
       </c>
       <c r="AA5" t="n">
         <v>1.045463250749225e-06</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>85.77791914159805</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.546x + -7093.683</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.5459354280871</v>
       </c>
       <c r="X6" t="n">
         <v>-7093.682694217379</v>
@@ -1474,7 +1444,7 @@
         <v>466.432824560886</v>
       </c>
       <c r="Z6" t="n">
-        <v>207.506</v>
+        <v>82130829.68119729</v>
       </c>
       <c r="AA6" t="n">
         <v>1.008757036480951e-06</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>86.00770599639398</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.328x + -7453.785</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.32835946341241</v>
       </c>
       <c r="X7" t="n">
         <v>-7453.784650128228</v>
@@ -1526,7 +1494,7 @@
         <v>461.8549488648044</v>
       </c>
       <c r="Z7" t="n">
-        <v>202.2909999999999</v>
+        <v>56724908.32590564</v>
       </c>
       <c r="AA7" t="n">
         <v>9.76414534436509e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>85.94466451637027</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.105x + -7223.820</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.10489225944609</v>
       </c>
       <c r="X8" t="n">
         <v>-7223.820233961746</v>
@@ -1578,7 +1544,7 @@
         <v>457.3615626041556</v>
       </c>
       <c r="Z8" t="n">
-        <v>201.451</v>
+        <v>67801734.22047524</v>
       </c>
       <c r="AA8" t="n">
         <v>9.486780199241122e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>86.07607965060043</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.579x + -7406.363</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.57883173067389</v>
       </c>
       <c r="X9" t="n">
         <v>-7406.362743820021</v>
@@ -1630,7 +1594,7 @@
         <v>453.2546206910977</v>
       </c>
       <c r="Z9" t="n">
-        <v>198.793</v>
+        <v>503463074.8002728</v>
       </c>
       <c r="AA9" t="n">
         <v>9.275650692967625e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>86.10565377072155</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.690x + -7384.208</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.68989071328384</v>
       </c>
       <c r="X10" t="n">
         <v>-7384.207958212489</v>
@@ -1682,7 +1644,7 @@
         <v>449.4920261038993</v>
       </c>
       <c r="Z10" t="n">
-        <v>196.66</v>
+        <v>367980904.6520852</v>
       </c>
       <c r="AA10" t="n">
         <v>9.080503930994159e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>86.25781826491523</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.289x + -7641.013</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.28901824021155</v>
       </c>
       <c r="X11" t="n">
         <v>-7641.013345132657</v>
@@ -1734,7 +1694,7 @@
         <v>445.8780580103834</v>
       </c>
       <c r="Z11" t="n">
-        <v>191.855</v>
+        <v>141980293.9109289</v>
       </c>
       <c r="AA11" t="n">
         <v>8.895668155853722e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>86.19457242780233</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 15.034x + -7422.647</t>
-        </is>
+      <c r="W12" t="n">
+        <v>15.03418603426702</v>
       </c>
       <c r="X12" t="n">
         <v>-7422.646926486967</v>
@@ -1786,7 +1744,7 @@
         <v>442.3503984287934</v>
       </c>
       <c r="Z12" t="n">
-        <v>193.032</v>
+        <v>112240319.493892</v>
       </c>
       <c r="AA12" t="n">
         <v>8.764206311982184e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>86.18119739029416</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 14.981x + -7320.492</t>
-        </is>
+      <c r="W13" t="n">
+        <v>14.98137460725235</v>
       </c>
       <c r="X13" t="n">
         <v>-7320.492460151338</v>
@@ -1838,7 +1794,7 @@
         <v>438.9069988842543</v>
       </c>
       <c r="Z13" t="n">
-        <v>192.61</v>
+        <v>26001814.29875525</v>
       </c>
       <c r="AA13" t="n">
         <v>8.634925066014833e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>86.23643882630302</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 15.202x + -7367.310</t>
-        </is>
+      <c r="W14" t="n">
+        <v>15.20191862512941</v>
       </c>
       <c r="X14" t="n">
         <v>-7367.309836368556</v>
@@ -1890,7 +1844,7 @@
         <v>435.5607166733957</v>
       </c>
       <c r="Z14" t="n">
-        <v>189.516</v>
+        <v>68972214.1317673</v>
       </c>
       <c r="AA14" t="n">
         <v>8.508675645135113e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>86.18873829179076</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 15.011x + -7193.466</t>
-        </is>
+      <c r="W15" t="n">
+        <v>15.01110439671592</v>
       </c>
       <c r="X15" t="n">
         <v>-7193.465923212082</v>
@@ -1942,7 +1894,7 @@
         <v>432.1663647990239</v>
       </c>
       <c r="Z15" t="n">
-        <v>189.105</v>
+        <v>355937089.6774742</v>
       </c>
       <c r="AA15" t="n">
         <v>8.401976279531202e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>86.2659016490831</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 15.322x + -7289.453</t>
-        </is>
+      <c r="W16" t="n">
+        <v>15.32220933072214</v>
       </c>
       <c r="X16" t="n">
         <v>-7289.452757198575</v>
@@ -1994,7 +1944,7 @@
         <v>428.8040168914721</v>
       </c>
       <c r="Z16" t="n">
-        <v>187.767</v>
+        <v>352665882.4857401</v>
       </c>
       <c r="AA16" t="n">
         <v>8.296606311151344e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>86.27059090147748</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 15.342x + -7233.478</t>
-        </is>
+      <c r="W17" t="n">
+        <v>15.34152966587589</v>
       </c>
       <c r="X17" t="n">
         <v>-7233.477705375245</v>
@@ -2046,7 +1994,7 @@
         <v>425.5181398561159</v>
       </c>
       <c r="Z17" t="n">
-        <v>187.425</v>
+        <v>233348024.7402682</v>
       </c>
       <c r="AA17" t="n">
         <v>8.20844195289727e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>86.37729202165276</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 15.795x + -7399.724</t>
-        </is>
+      <c r="W18" t="n">
+        <v>15.79465059968024</v>
       </c>
       <c r="X18" t="n">
         <v>-7399.724136359128</v>
@@ -2098,7 +2044,7 @@
         <v>422.2054309710713</v>
       </c>
       <c r="Z18" t="n">
-        <v>185.425</v>
+        <v>173599336.1105402</v>
       </c>
       <c r="AA18" t="n">
         <v>8.111308803992081e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>86.25518816750865</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 15.278x + -7065.125</t>
-        </is>
+      <c r="W19" t="n">
+        <v>15.27824967962557</v>
       </c>
       <c r="X19" t="n">
         <v>-7065.125182309032</v>
@@ -2150,7 +2094,7 @@
         <v>418.8913705290404</v>
       </c>
       <c r="Z19" t="n">
-        <v>186.873</v>
+        <v>343891492.0842941</v>
       </c>
       <c r="AA19" t="n">
         <v>8.030844396002918e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>86.41945351399555</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 15.981x + -7358.892</t>
-        </is>
+      <c r="W20" t="n">
+        <v>15.98112878927881</v>
       </c>
       <c r="X20" t="n">
         <v>-7358.892142885788</v>
@@ -2202,7 +2144,7 @@
         <v>415.6398467546637</v>
       </c>
       <c r="Z20" t="n">
-        <v>183.537</v>
+        <v>170711867.1082714</v>
       </c>
       <c r="AA20" t="n">
         <v>7.949215883028286e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>86.43873896347283</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 16.068x + -7330.866</t>
-        </is>
+      <c r="W21" t="n">
+        <v>16.06789720132253</v>
       </c>
       <c r="X21" t="n">
         <v>-7330.866382177048</v>
@@ -2254,7 +2194,7 @@
         <v>412.3606945871971</v>
       </c>
       <c r="Z21" t="n">
-        <v>181.081</v>
+        <v>225638062.5626982</v>
       </c>
       <c r="AA21" t="n">
         <v>7.856700057113214e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>86.27015346145507</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 15.340x + -6898.664</t>
-        </is>
+      <c r="W22" t="n">
+        <v>15.33972530396093</v>
       </c>
       <c r="X22" t="n">
         <v>-6898.664298580803</v>
@@ -2306,7 +2244,7 @@
         <v>409.0709526386851</v>
       </c>
       <c r="Z22" t="n">
-        <v>184.1990000000001</v>
+        <v>223706718.6679012</v>
       </c>
       <c r="AA22" t="n">
         <v>7.80187494533801e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.37045796082725</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.349x + -7280.476</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.34917721138359</v>
       </c>
       <c r="X2" t="n">
         <v>-7280.475695272173</v>
@@ -2504,7 +2440,7 @@
         <v>499.1176390781113</v>
       </c>
       <c r="Z2" t="n">
-        <v>252.2190000000001</v>
+        <v>243775353.7656611</v>
       </c>
       <c r="AA2" t="n">
         <v>1.249454044055751e-06</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>85.70198419608978</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.306x + -7375.904</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.30573701345608</v>
       </c>
       <c r="X3" t="n">
         <v>-7375.903936424929</v>
@@ -2556,7 +2490,7 @@
         <v>486.2898482420558</v>
       </c>
       <c r="Z3" t="n">
-        <v>225.913</v>
+        <v>200647960.2769898</v>
       </c>
       <c r="AA3" t="n">
         <v>1.035668630598142e-06</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>85.7228042362088</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.371x + -7260.903</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.37074816836922</v>
       </c>
       <c r="X4" t="n">
         <v>-7260.903349333928</v>
@@ -2608,7 +2540,7 @@
         <v>481.4264374623174</v>
       </c>
       <c r="Z4" t="n">
-        <v>218.407</v>
+        <v>70490596.89608534</v>
       </c>
       <c r="AA4" t="n">
         <v>9.807443637112244e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>85.85060828652833</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.784x + -7415.660</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.78408724670077</v>
       </c>
       <c r="X5" t="n">
         <v>-7415.660134759206</v>
@@ -2660,7 +2590,7 @@
         <v>477.3102502881576</v>
       </c>
       <c r="Z5" t="n">
-        <v>213.936</v>
+        <v>49194235.607234</v>
       </c>
       <c r="AA5" t="n">
         <v>9.503341995736951e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>85.97968856055924</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.228x + -7589.476</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.22818046103546</v>
       </c>
       <c r="X6" t="n">
         <v>-7589.47571592912</v>
@@ -2712,7 +2640,7 @@
         <v>472.9588709053863</v>
       </c>
       <c r="Z6" t="n">
-        <v>210.581</v>
+        <v>66754175.71743279</v>
       </c>
       <c r="AA6" t="n">
         <v>9.261465598722945e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>86.09102856914589</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.635x + -7732.434</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.63475933658059</v>
       </c>
       <c r="X7" t="n">
         <v>-7732.434431159663</v>
@@ -2764,7 +2690,7 @@
         <v>468.4717608769296</v>
       </c>
       <c r="Z7" t="n">
-        <v>206.0630000000001</v>
+        <v>40467841.915176</v>
       </c>
       <c r="AA7" t="n">
         <v>9.03637099704054e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>86.08941493964015</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.629x + -7633.516</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.62870179468062</v>
       </c>
       <c r="X8" t="n">
         <v>-7633.516383021247</v>
@@ -2816,7 +2740,7 @@
         <v>464.1141487701912</v>
       </c>
       <c r="Z8" t="n">
-        <v>205.4670000000001</v>
+        <v>47936162.10497496</v>
       </c>
       <c r="AA8" t="n">
         <v>8.850825373548373e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>86.3369970745009</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.620x + -8116.589</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.62043466018733</v>
       </c>
       <c r="X9" t="n">
         <v>-8116.589163396268</v>
@@ -2868,7 +2790,7 @@
         <v>460.0229431340741</v>
       </c>
       <c r="Z9" t="n">
-        <v>198.372</v>
+        <v>89417581.47126876</v>
       </c>
       <c r="AA9" t="n">
         <v>8.662062897082133e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>86.23085091490984</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.179x + -7777.134</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.17931617679168</v>
       </c>
       <c r="X10" t="n">
         <v>-7777.134174220517</v>
@@ -2920,7 +2840,7 @@
         <v>456.2402362992059</v>
       </c>
       <c r="Z10" t="n">
-        <v>200.828</v>
+        <v>486361881.5455183</v>
       </c>
       <c r="AA10" t="n">
         <v>8.539360900901032e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>86.1455908825501</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.843x + -7507.113</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.84256607047867</v>
       </c>
       <c r="X11" t="n">
         <v>-7507.112775363232</v>
@@ -2972,7 +2890,7 @@
         <v>452.6263035733331</v>
       </c>
       <c r="Z11" t="n">
-        <v>201.2020000000001</v>
+        <v>47796829.53332189</v>
       </c>
       <c r="AA11" t="n">
         <v>8.42081609816923e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>86.10219382292112</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 14.677x + -7342.240</t>
-        </is>
+      <c r="W12" t="n">
+        <v>14.67681073983312</v>
       </c>
       <c r="X12" t="n">
         <v>-7342.240245234433</v>
@@ -3024,7 +2940,7 @@
         <v>449.0300279010361</v>
       </c>
       <c r="Z12" t="n">
-        <v>202.195</v>
+        <v>86506340.2766064</v>
       </c>
       <c r="AA12" t="n">
         <v>8.325347789270932e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>86.25619071657593</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 15.282x + -7606.439</t>
-        </is>
+      <c r="W13" t="n">
+        <v>15.2823526925668</v>
       </c>
       <c r="X13" t="n">
         <v>-7606.439003292698</v>
@@ -3076,7 +2990,7 @@
         <v>445.5425135130176</v>
       </c>
       <c r="Z13" t="n">
-        <v>197.675</v>
+        <v>495200450.8970287</v>
       </c>
       <c r="AA13" t="n">
         <v>8.20693032661026e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>86.36223952402705</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 15.729x + -7787.122</t>
-        </is>
+      <c r="W14" t="n">
+        <v>15.72911987119276</v>
       </c>
       <c r="X14" t="n">
         <v>-7787.121506335484</v>
@@ -3128,7 +3040,7 @@
         <v>442.1132882423688</v>
       </c>
       <c r="Z14" t="n">
-        <v>196.662</v>
+        <v>41647265.46886921</v>
       </c>
       <c r="AA14" t="n">
         <v>8.127781237429013e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>86.34080378605297</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 15.637x + -7659.418</t>
-        </is>
+      <c r="W15" t="n">
+        <v>15.63672915093479</v>
       </c>
       <c r="X15" t="n">
         <v>-7659.417691555616</v>
@@ -3180,7 +3090,7 @@
         <v>438.7846401522244</v>
       </c>
       <c r="Z15" t="n">
-        <v>195.315</v>
+        <v>241283099.4159756</v>
       </c>
       <c r="AA15" t="n">
         <v>8.022724761816673e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>86.28041387999662</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 15.382x + -7450.193</t>
-        </is>
+      <c r="W16" t="n">
+        <v>15.38215930717319</v>
       </c>
       <c r="X16" t="n">
         <v>-7450.193141842873</v>
@@ -3232,7 +3140,7 @@
         <v>435.334903354623</v>
       </c>
       <c r="Z16" t="n">
-        <v>194.843</v>
+        <v>478121641.4895244</v>
       </c>
       <c r="AA16" t="n">
         <v>7.947759096426171e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>86.3823934739746</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 15.817x + -7618.619</t>
-        </is>
+      <c r="W17" t="n">
+        <v>15.81698322664535</v>
       </c>
       <c r="X17" t="n">
         <v>-7618.619376268224</v>
@@ -3284,7 +3190,7 @@
         <v>431.8980721291372</v>
       </c>
       <c r="Z17" t="n">
-        <v>194.53</v>
+        <v>355786911.2603794</v>
       </c>
       <c r="AA17" t="n">
         <v>7.885532963749957e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>86.3717566834879</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 15.770x + -7518.766</t>
-        </is>
+      <c r="W18" t="n">
+        <v>15.77048949639992</v>
       </c>
       <c r="X18" t="n">
         <v>-7518.765585391766</v>
@@ -3336,7 +3240,7 @@
         <v>428.4997763259188</v>
       </c>
       <c r="Z18" t="n">
-        <v>192.979</v>
+        <v>176168883.5768803</v>
       </c>
       <c r="AA18" t="n">
         <v>7.795747484222539e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>86.28548445354127</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 15.403x + -7255.863</t>
-        </is>
+      <c r="W19" t="n">
+        <v>15.40321610280369</v>
       </c>
       <c r="X19" t="n">
         <v>-7255.863403884056</v>
@@ -3388,7 +3290,7 @@
         <v>425.087672523999</v>
       </c>
       <c r="Z19" t="n">
-        <v>194.591</v>
+        <v>349205414.8950536</v>
       </c>
       <c r="AA19" t="n">
         <v>7.735203486760573e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>86.3838129704954</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 15.823x + -7405.167</t>
-        </is>
+      <c r="W20" t="n">
+        <v>15.82320854714007</v>
       </c>
       <c r="X20" t="n">
         <v>-7405.167210656181</v>
@@ -3440,7 +3340,7 @@
         <v>421.7213660033631</v>
       </c>
       <c r="Z20" t="n">
-        <v>191.8320000000001</v>
+        <v>173240697.9551121</v>
       </c>
       <c r="AA20" t="n">
         <v>7.651207285496407e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>86.38921301969647</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 15.847x + -7349.343</t>
-        </is>
+      <c r="W21" t="n">
+        <v>15.84693558220773</v>
       </c>
       <c r="X21" t="n">
         <v>-7349.342759269707</v>
@@ -3492,7 +3390,7 @@
         <v>418.3605202623948</v>
       </c>
       <c r="Z21" t="n">
-        <v>191.65</v>
+        <v>114614647.8682878</v>
       </c>
       <c r="AA21" t="n">
         <v>7.594625391339403e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>86.30979593016248</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 15.505x + -7104.663</t>
-        </is>
+      <c r="W22" t="n">
+        <v>15.50497817787444</v>
       </c>
       <c r="X22" t="n">
         <v>-7104.662817970229</v>
@@ -3544,7 +3440,7 @@
         <v>415.0494363389573</v>
       </c>
       <c r="Z22" t="n">
-        <v>192.124</v>
+        <v>140184727.2398659</v>
       </c>
       <c r="AA22" t="n">
         <v>7.530284246436029e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>82.70459489039814</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.811x + -5664.476</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.811191425346159</v>
       </c>
       <c r="X2" t="n">
         <v>-5664.475697975076</v>
@@ -3742,7 +3636,7 @@
         <v>484.9861151643555</v>
       </c>
       <c r="Z2" t="n">
-        <v>391.198</v>
+        <v>332736872.0083891</v>
       </c>
       <c r="AA2" t="n">
         <v>1.29287172787754e-05</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>84.27422222106367</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.973x + -6235.017</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.973303530021342</v>
       </c>
       <c r="X3" t="n">
         <v>-6235.016696184286</v>
@@ -3794,7 +3686,7 @@
         <v>521.3350682481924</v>
       </c>
       <c r="Z3" t="n">
-        <v>296.4540000000001</v>
+        <v>400990891.9343027</v>
       </c>
       <c r="AA3" t="n">
         <v>2.677452522839929e-06</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>84.67273293376704</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.724x + -6457.223</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.72418122338732</v>
       </c>
       <c r="X4" t="n">
         <v>-6457.222985885509</v>
@@ -3846,7 +3736,7 @@
         <v>517.3713649115799</v>
       </c>
       <c r="Z4" t="n">
-        <v>270.971</v>
+        <v>338453846.786369</v>
       </c>
       <c r="AA4" t="n">
         <v>1.817158349230833e-06</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>84.95536822507026</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.328x + -6711.920</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.32840873787003</v>
       </c>
       <c r="X5" t="n">
         <v>-6711.919872729918</v>
@@ -3898,7 +3786,7 @@
         <v>513.1693295433734</v>
       </c>
       <c r="Z5" t="n">
-        <v>256.049</v>
+        <v>71587039.11022817</v>
       </c>
       <c r="AA5" t="n">
         <v>1.551584797607573e-06</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>85.19587264337859</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.898x + -6971.728</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.89840326745445</v>
       </c>
       <c r="X6" t="n">
         <v>-6971.727991215119</v>
@@ -3950,7 +3836,7 @@
         <v>508.7904941824024</v>
       </c>
       <c r="Z6" t="n">
-        <v>246.5940000000001</v>
+        <v>53603483.59283476</v>
       </c>
       <c r="AA6" t="n">
         <v>1.403257078285212e-06</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>85.27155152418317</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.090x + -6978.951</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.08972580048006</v>
       </c>
       <c r="X7" t="n">
         <v>-6978.950978077645</v>
@@ -4002,7 +3886,7 @@
         <v>504.1404758598058</v>
       </c>
       <c r="Z7" t="n">
-        <v>239.462</v>
+        <v>127015839.6190417</v>
       </c>
       <c r="AA7" t="n">
         <v>1.2989293958207e-06</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>85.56297724600542</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.887x + -7388.883</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.88728986709451</v>
       </c>
       <c r="X8" t="n">
         <v>-7388.882746748612</v>
@@ -4054,7 +3936,7 @@
         <v>499.4335336193562</v>
       </c>
       <c r="Z8" t="n">
-        <v>231.125</v>
+        <v>24540362.74458681</v>
       </c>
       <c r="AA8" t="n">
         <v>1.223309426751137e-06</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>85.51228589144141</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.741x + -7186.108</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.74113342932064</v>
       </c>
       <c r="X9" t="n">
         <v>-7186.108315126336</v>
@@ -4106,7 +3986,7 @@
         <v>494.6814522457348</v>
       </c>
       <c r="Z9" t="n">
-        <v>228.739</v>
+        <v>240916987.3990885</v>
       </c>
       <c r="AA9" t="n">
         <v>1.162745934544996e-06</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>85.64535672007067</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.132x + -7332.145</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.1320550372761</v>
       </c>
       <c r="X10" t="n">
         <v>-7332.145161253643</v>
@@ -4158,7 +4036,7 @@
         <v>489.836180994921</v>
       </c>
       <c r="Z10" t="n">
-        <v>224.625</v>
+        <v>410904260.3103519</v>
       </c>
       <c r="AA10" t="n">
         <v>1.116260850621299e-06</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>85.7085873613081</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.326x + -7347.821</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.3262874016879</v>
       </c>
       <c r="X11" t="n">
         <v>-7347.820697820334</v>
@@ -4210,7 +4086,7 @@
         <v>485.1460599920371</v>
       </c>
       <c r="Z11" t="n">
-        <v>221.218</v>
+        <v>60299381.14163633</v>
       </c>
       <c r="AA11" t="n">
         <v>1.073682635026227e-06</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>84.34137867276681</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.092x + -5851.073</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.09245365316553</v>
       </c>
       <c r="X2" t="n">
         <v>-5851.072698290834</v>
@@ -4408,7 +4282,7 @@
         <v>490.6367201800968</v>
       </c>
       <c r="Z2" t="n">
-        <v>288.5219999999999</v>
+        <v>444957475.7575544</v>
       </c>
       <c r="AA2" t="n">
         <v>1.789976648279128e-06</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>85.00298876246667</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.437x + -6273.528</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.43692355308581</v>
       </c>
       <c r="X3" t="n">
         <v>-6273.527778223771</v>
@@ -4460,7 +4332,7 @@
         <v>480.9967073330358</v>
       </c>
       <c r="Z3" t="n">
-        <v>250.4160000000001</v>
+        <v>98211573.19599701</v>
       </c>
       <c r="AA3" t="n">
         <v>1.292418458022157e-06</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>85.49559100147437</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.694x + -6896.835</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.69371635068393</v>
       </c>
       <c r="X4" t="n">
         <v>-6896.834561365011</v>
@@ -4512,7 +4382,7 @@
         <v>476.5104644538858</v>
       </c>
       <c r="Z4" t="n">
-        <v>233.221</v>
+        <v>174464456.9436574</v>
       </c>
       <c r="AA4" t="n">
         <v>1.167616733782872e-06</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>85.5016101024145</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.711x + -6797.388</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.71077140345731</v>
       </c>
       <c r="X5" t="n">
         <v>-6797.38766962644</v>
@@ -4564,7 +4432,7 @@
         <v>472.7525593398541</v>
       </c>
       <c r="Z5" t="n">
-        <v>226.752</v>
+        <v>118491567.6754503</v>
       </c>
       <c r="AA5" t="n">
         <v>1.097665810904654e-06</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>85.73307133933369</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.403x + -7126.489</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.40304061897154</v>
       </c>
       <c r="X6" t="n">
         <v>-7126.489023836115</v>
@@ -4616,7 +4482,7 @@
         <v>468.9819122443698</v>
       </c>
       <c r="Z6" t="n">
-        <v>221.253</v>
+        <v>112812922.6847093</v>
       </c>
       <c r="AA6" t="n">
         <v>1.051812760341511e-06</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>85.80503641341028</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.634x + -7171.224</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.63381644306993</v>
       </c>
       <c r="X7" t="n">
         <v>-7171.224210644265</v>
@@ -4668,7 +4532,7 @@
         <v>465.0790243736301</v>
       </c>
       <c r="Z7" t="n">
-        <v>216.3349999999999</v>
+        <v>111156231.6956024</v>
       </c>
       <c r="AA7" t="n">
         <v>1.013681429750216e-06</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>85.79298279271276</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.595x + -7055.838</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.59461373565817</v>
       </c>
       <c r="X8" t="n">
         <v>-7055.838377605582</v>
@@ -4720,7 +4582,7 @@
         <v>461.1516122042609</v>
       </c>
       <c r="Z8" t="n">
-        <v>212.8200000000001</v>
+        <v>66260437.21048671</v>
       </c>
       <c r="AA8" t="n">
         <v>9.79331295351269e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>85.86617075478213</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.836x + -7112.722</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.83616121563415</v>
       </c>
       <c r="X9" t="n">
         <v>-7112.722165157036</v>
@@ -4772,7 +4632,7 @@
         <v>457.3864809506157</v>
       </c>
       <c r="Z9" t="n">
-        <v>210.386</v>
+        <v>55553887.17777497</v>
       </c>
       <c r="AA9" t="n">
         <v>9.541075920291812e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>86.04721851291664</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.472x + -7403.042</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.47204994659154</v>
       </c>
       <c r="X10" t="n">
         <v>-7403.041572670372</v>
@@ -4824,7 +4682,7 @@
         <v>453.7330725039115</v>
       </c>
       <c r="Z10" t="n">
-        <v>205.914</v>
+        <v>27254715.81268415</v>
       </c>
       <c r="AA10" t="n">
         <v>9.329199084660932e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>85.90117617036917</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.955x + -7029.461</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.95473628862328</v>
       </c>
       <c r="X11" t="n">
         <v>-7029.460609951821</v>
@@ -4876,7 +4732,7 @@
         <v>450.2221643621617</v>
       </c>
       <c r="Z11" t="n">
-        <v>207.3650000000001</v>
+        <v>63839364.51118754</v>
       </c>
       <c r="AA11" t="n">
         <v>9.158146631407134e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>86.09682199415462</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 14.657x + -7356.216</t>
-        </is>
+      <c r="W12" t="n">
+        <v>14.65654897842345</v>
       </c>
       <c r="X12" t="n">
         <v>-7356.21618013666</v>
@@ -4928,7 +4782,7 @@
         <v>446.8388964258468</v>
       </c>
       <c r="Z12" t="n">
-        <v>202.934</v>
+        <v>236340210.8547626</v>
       </c>
       <c r="AA12" t="n">
         <v>8.996273767565365e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>86.11823548043371</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 14.738x + -7329.036</t>
-        </is>
+      <c r="W13" t="n">
+        <v>14.73765081843047</v>
       </c>
       <c r="X13" t="n">
         <v>-7329.036117939046</v>
@@ -4980,7 +4832,7 @@
         <v>443.5286139056063</v>
       </c>
       <c r="Z13" t="n">
-        <v>200.639</v>
+        <v>104506479.3569433</v>
       </c>
       <c r="AA13" t="n">
         <v>8.846161540240556e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>86.15113165755315</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 14.864x + -7328.840</t>
-        </is>
+      <c r="W14" t="n">
+        <v>14.86399776831588</v>
       </c>
       <c r="X14" t="n">
         <v>-7328.840189038013</v>
@@ -5032,7 +4882,7 @@
         <v>440.2728386421616</v>
       </c>
       <c r="Z14" t="n">
-        <v>198.266</v>
+        <v>48907273.27580757</v>
       </c>
       <c r="AA14" t="n">
         <v>8.702026283103438e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>86.02377315489622</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 14.386x + -7005.441</t>
-        </is>
+      <c r="W15" t="n">
+        <v>14.38644502270059</v>
       </c>
       <c r="X15" t="n">
         <v>-7005.441102406066</v>
@@ -5084,7 +4932,7 @@
         <v>436.9733621935648</v>
       </c>
       <c r="Z15" t="n">
-        <v>201.864</v>
+        <v>37707447.05188376</v>
       </c>
       <c r="AA15" t="n">
         <v>8.626656148130543e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>86.19642498284472</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 15.042x + -7291.197</t>
-        </is>
+      <c r="W16" t="n">
+        <v>15.04153010215688</v>
       </c>
       <c r="X16" t="n">
         <v>-7291.197489787197</v>
@@ -5136,7 +4982,7 @@
         <v>433.802254192731</v>
       </c>
       <c r="Z16" t="n">
-        <v>196.441</v>
+        <v>48255195.06780083</v>
       </c>
       <c r="AA16" t="n">
         <v>8.488422569119952e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>86.09150478381427</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 14.637x + -7010.914</t>
-        </is>
+      <c r="W17" t="n">
+        <v>14.63654799396766</v>
       </c>
       <c r="X17" t="n">
         <v>-7010.913950724082</v>
@@ -5188,7 +5032,7 @@
         <v>430.589869034477</v>
       </c>
       <c r="Z17" t="n">
-        <v>198.597</v>
+        <v>16593249.91813339</v>
       </c>
       <c r="AA17" t="n">
         <v>8.396386542920469e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>86.05765811255874</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 14.510x + -6876.684</t>
-        </is>
+      <c r="W18" t="n">
+        <v>14.51049466468189</v>
       </c>
       <c r="X18" t="n">
         <v>-6876.684018773698</v>
@@ -5240,7 +5082,7 @@
         <v>427.3854692308652</v>
       </c>
       <c r="Z18" t="n">
-        <v>196.943</v>
+        <v>703133306.1587847</v>
       </c>
       <c r="AA18" t="n">
         <v>8.297869985299549e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>86.15734959276618</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 14.888x + -7012.962</t>
-        </is>
+      <c r="W19" t="n">
+        <v>14.88812220568255</v>
       </c>
       <c r="X19" t="n">
         <v>-7012.96178817961</v>
@@ -5292,7 +5132,7 @@
         <v>424.2195163582124</v>
       </c>
       <c r="Z19" t="n">
-        <v>193.72</v>
+        <v>174618713.9645715</v>
       </c>
       <c r="AA19" t="n">
         <v>8.189301531234026e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>86.20525123828185</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 15.077x + -7049.524</t>
-        </is>
+      <c r="W20" t="n">
+        <v>15.07661827029655</v>
       </c>
       <c r="X20" t="n">
         <v>-7049.52408508412</v>
@@ -5344,7 +5182,7 @@
         <v>421.0071287354223</v>
       </c>
       <c r="Z20" t="n">
-        <v>193.475</v>
+        <v>173122596.5523554</v>
       </c>
       <c r="AA20" t="n">
         <v>8.120594659232375e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>86.2322946739904</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 15.185x + -7043.294</t>
-        </is>
+      <c r="W21" t="n">
+        <v>15.18514959942751</v>
       </c>
       <c r="X21" t="n">
         <v>-7043.293606001984</v>
@@ -5396,7 +5232,7 @@
         <v>417.8126408326631</v>
       </c>
       <c r="Z21" t="n">
-        <v>192.172</v>
+        <v>343337304.2052764</v>
       </c>
       <c r="AA21" t="n">
         <v>8.040902748043091e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>86.38932829967922</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 15.847x + -7317.219</t>
-        </is>
+      <c r="W22" t="n">
+        <v>15.84744287846921</v>
       </c>
       <c r="X22" t="n">
         <v>-7317.219125309516</v>
@@ -5448,7 +5282,7 @@
         <v>414.5699333941683</v>
       </c>
       <c r="Z22" t="n">
-        <v>188.014</v>
+        <v>170322252.8409989</v>
       </c>
       <c r="AA22" t="n">
         <v>7.943590377711847e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>82.77194845816865</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.885x + -5573.694</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.884767934930937</v>
       </c>
       <c r="X2" t="n">
         <v>-5573.693806484659</v>
@@ -5646,7 +5478,7 @@
         <v>479.2253385644894</v>
       </c>
       <c r="Z2" t="n">
-        <v>372.9979999999999</v>
+        <v>472354131.9910227</v>
       </c>
       <c r="AA2" t="n">
         <v>1.352861052745718e-05</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>84.02418309048512</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.553x + -5894.239</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.553149794099227</v>
       </c>
       <c r="X3" t="n">
         <v>-5894.239021872533</v>
@@ -5698,7 +5528,7 @@
         <v>511.49299941495</v>
       </c>
       <c r="Z3" t="n">
-        <v>296.955</v>
+        <v>902520402.7178111</v>
       </c>
       <c r="AA3" t="n">
         <v>3.526782239979953e-06</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>84.57038930128259</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.521x + -6293.620</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.52085836601968</v>
       </c>
       <c r="X4" t="n">
         <v>-6293.619681130627</v>
@@ -5750,7 +5578,7 @@
         <v>511.259118049216</v>
       </c>
       <c r="Z4" t="n">
-        <v>269.418</v>
+        <v>367048545.7249072</v>
       </c>
       <c r="AA4" t="n">
         <v>2.181476508861705e-06</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>84.88794457234106</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.178x + -6581.251</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.17821653123506</v>
       </c>
       <c r="X5" t="n">
         <v>-6581.25142678913</v>
@@ -5802,7 +5628,7 @@
         <v>507.8293741020886</v>
       </c>
       <c r="Z5" t="n">
-        <v>253.001</v>
+        <v>304339646.6292965</v>
       </c>
       <c r="AA5" t="n">
         <v>1.78223714246108e-06</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>85.16016319501142</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.810x + -6871.508</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.8101997073542</v>
       </c>
       <c r="X6" t="n">
         <v>-6871.507724383208</v>
@@ -5854,7 +5678,7 @@
         <v>503.5583085184324</v>
       </c>
       <c r="Z6" t="n">
-        <v>242.379</v>
+        <v>31448815.66216073</v>
       </c>
       <c r="AA6" t="n">
         <v>1.565254805349706e-06</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>85.30933337209662</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.188x + -6990.027</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.18754652869191</v>
       </c>
       <c r="X7" t="n">
         <v>-6990.026653880045</v>
@@ -5906,7 +5728,7 @@
         <v>498.6612136504206</v>
       </c>
       <c r="Z7" t="n">
-        <v>234.2009999999999</v>
+        <v>271746175.66655</v>
       </c>
       <c r="AA7" t="n">
         <v>1.421163704164713e-06</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>85.41296251207909</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.464x + -7046.551</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.46410482946496</v>
       </c>
       <c r="X8" t="n">
         <v>-7046.55101699981</v>
@@ -5958,7 +5778,7 @@
         <v>493.5944305799873</v>
       </c>
       <c r="Z8" t="n">
-        <v>227.5229999999999</v>
+        <v>207468445.7795521</v>
       </c>
       <c r="AA8" t="n">
         <v>1.317363148607506e-06</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>85.4649106739612</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.607x + -7016.857</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.60748603523212</v>
       </c>
       <c r="X9" t="n">
         <v>-7016.856535205619</v>
@@ -6010,7 +5828,7 @@
         <v>488.5616172285689</v>
       </c>
       <c r="Z9" t="n">
-        <v>222.327</v>
+        <v>273495237.9056231</v>
       </c>
       <c r="AA9" t="n">
         <v>1.234759630935135e-06</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>85.60893138353242</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.023x + -7168.371</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.02269798875889</v>
       </c>
       <c r="X10" t="n">
         <v>-7168.370743560709</v>
@@ -6062,7 +5878,7 @@
         <v>483.6703421743699</v>
       </c>
       <c r="Z10" t="n">
-        <v>218.6819999999999</v>
+        <v>38899764.29307637</v>
       </c>
       <c r="AA10" t="n">
         <v>1.171538292361146e-06</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>85.59917131842867</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.994x + -7046.443</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.9937029969154</v>
       </c>
       <c r="X11" t="n">
         <v>-7046.44320841293</v>
@@ -6114,7 +5928,7 @@
         <v>479.1177921100242</v>
       </c>
       <c r="Z11" t="n">
-        <v>215.037</v>
+        <v>134952739.5320344</v>
       </c>
       <c r="AA11" t="n">
         <v>1.121123047400696e-06</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>83.81631011434521</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.230x + -5459.126</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.229626298103566</v>
       </c>
       <c r="X2" t="n">
         <v>-5459.126046942333</v>
@@ -6312,7 +6124,7 @@
         <v>495.8142821417966</v>
       </c>
       <c r="Z2" t="n">
-        <v>305.5329999999999</v>
+        <v>156362982.2244543</v>
       </c>
       <c r="AA2" t="n">
         <v>2.939460051597208e-06</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>84.66449696472088</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.708x + -6046.520</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.70753133669543</v>
       </c>
       <c r="X3" t="n">
         <v>-6046.519547476223</v>
@@ -6364,7 +6174,7 @@
         <v>489.3332543864511</v>
       </c>
       <c r="Z3" t="n">
-        <v>263.838</v>
+        <v>22716617.17866769</v>
       </c>
       <c r="AA3" t="n">
         <v>1.723593905626079e-06</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>84.9938808202409</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.416x + -6307.153</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.41600966374292</v>
       </c>
       <c r="X4" t="n">
         <v>-6307.153016777313</v>
@@ -6416,7 +6224,7 @@
         <v>484.174340005828</v>
       </c>
       <c r="Z4" t="n">
-        <v>244.96</v>
+        <v>78898726.29831912</v>
       </c>
       <c r="AA4" t="n">
         <v>1.445534303458247e-06</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>85.2567288732417</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.052x + -6567.897</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.05177323224869</v>
       </c>
       <c r="X5" t="n">
         <v>-6567.897026605417</v>
@@ -6468,7 +6274,7 @@
         <v>479.4093085140572</v>
       </c>
       <c r="Z5" t="n">
-        <v>232.9459999999999</v>
+        <v>171103766.1913403</v>
       </c>
       <c r="AA5" t="n">
         <v>1.299772470422183e-06</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>85.36876273292559</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.345x + -6629.071</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.34463715394038</v>
       </c>
       <c r="X6" t="n">
         <v>-6629.071089220419</v>
@@ -6520,7 +6324,7 @@
         <v>474.5617476358946</v>
       </c>
       <c r="Z6" t="n">
-        <v>225.91</v>
+        <v>65175634.19993156</v>
       </c>
       <c r="AA6" t="n">
         <v>1.206148627871701e-06</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>85.65429685905549</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.159x + -7007.294</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.15917499015366</v>
       </c>
       <c r="X7" t="n">
         <v>-7007.293960867753</v>
@@ -6572,7 +6374,7 @@
         <v>469.7630187700368</v>
       </c>
       <c r="Z7" t="n">
-        <v>216.5250000000001</v>
+        <v>104170035.1149336</v>
       </c>
       <c r="AA7" t="n">
         <v>1.135032723436958e-06</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>85.62865855973675</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.082x + -6852.534</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.08169760955599</v>
       </c>
       <c r="X8" t="n">
         <v>-6852.533653382613</v>
@@ -6624,7 +6424,7 @@
         <v>465.0424294029989</v>
       </c>
       <c r="Z8" t="n">
-        <v>213.976</v>
+        <v>108463446.6572052</v>
       </c>
       <c r="AA8" t="n">
         <v>1.083236618129556e-06</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>85.70910225532666</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.328x + -6896.546</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.32789250950225</v>
       </c>
       <c r="X9" t="n">
         <v>-6896.546207187512</v>
@@ -6676,7 +6474,7 @@
         <v>460.5687854783792</v>
       </c>
       <c r="Z9" t="n">
-        <v>210.085</v>
+        <v>106565178.2821618</v>
       </c>
       <c r="AA9" t="n">
         <v>1.040844649526188e-06</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>85.79834206250902</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.612x + -6967.257</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.61201628628344</v>
       </c>
       <c r="X10" t="n">
         <v>-6967.256924568538</v>
@@ -6728,7 +6524,7 @@
         <v>456.3086191296907</v>
       </c>
       <c r="Z10" t="n">
-        <v>205.7130000000001</v>
+        <v>40386859.37707627</v>
       </c>
       <c r="AA10" t="n">
         <v>1.006394073931005e-06</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>85.81055176757511</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.652x + -6904.240</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.65182944744899</v>
       </c>
       <c r="X11" t="n">
         <v>-6904.239530447566</v>
@@ -6780,7 +6574,7 @@
         <v>452.2078351562517</v>
       </c>
       <c r="Z11" t="n">
-        <v>204.225</v>
+        <v>62697817.95367827</v>
       </c>
       <c r="AA11" t="n">
         <v>9.803227553144902e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>85.9756923366898</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 14.214x + -7139.873</t>
-        </is>
+      <c r="W12" t="n">
+        <v>14.21400506685705</v>
       </c>
       <c r="X12" t="n">
         <v>-7139.873421238864</v>
@@ -6832,7 +6624,7 @@
         <v>448.3115515227257</v>
       </c>
       <c r="Z12" t="n">
-        <v>200.006</v>
+        <v>96016442.48212782</v>
       </c>
       <c r="AA12" t="n">
         <v>9.569377701865932e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>85.88751051667424</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 13.908x + -6889.204</t>
-        </is>
+      <c r="W13" t="n">
+        <v>13.90820635337586</v>
       </c>
       <c r="X13" t="n">
         <v>-6889.204435189553</v>
@@ -6884,7 +6674,7 @@
         <v>444.6650435858865</v>
       </c>
       <c r="Z13" t="n">
-        <v>199.599</v>
+        <v>180879024.3102809</v>
       </c>
       <c r="AA13" t="n">
         <v>9.361365042195794e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>86.10551997027011</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 14.689x + -7245.118</t>
-        </is>
+      <c r="W14" t="n">
+        <v>14.68938446323112</v>
       </c>
       <c r="X14" t="n">
         <v>-7245.118436099759</v>
@@ -6936,7 +6724,7 @@
         <v>441.1438797420638</v>
       </c>
       <c r="Z14" t="n">
-        <v>194.5389999999999</v>
+        <v>26692653.95806248</v>
       </c>
       <c r="AA14" t="n">
         <v>9.169170173836528e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>86.05576800368037</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 14.504x + -7071.457</t>
-        </is>
+      <c r="W15" t="n">
+        <v>14.50351911353975</v>
       </c>
       <c r="X15" t="n">
         <v>-7071.456782491423</v>
@@ -6988,7 +6774,7 @@
         <v>437.784385584846</v>
       </c>
       <c r="Z15" t="n">
-        <v>194.054</v>
+        <v>53063169.06322414</v>
       </c>
       <c r="AA15" t="n">
         <v>9.019821697617403e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>86.17066780525838</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 14.940x + -7240.649</t>
-        </is>
+      <c r="W16" t="n">
+        <v>14.94005762490695</v>
       </c>
       <c r="X16" t="n">
         <v>-7240.648976410118</v>
@@ -7040,7 +6824,7 @@
         <v>434.5817543191504</v>
       </c>
       <c r="Z16" t="n">
-        <v>190.3729999999999</v>
+        <v>482158631.2871308</v>
       </c>
       <c r="AA16" t="n">
         <v>8.881227119662631e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>86.13380830266429</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 14.797x + -7098.044</t>
-        </is>
+      <c r="W17" t="n">
+        <v>14.79719499513266</v>
       </c>
       <c r="X17" t="n">
         <v>-7098.044478056531</v>
@@ -7092,7 +6874,7 @@
         <v>431.4658987977885</v>
       </c>
       <c r="Z17" t="n">
-        <v>191.122</v>
+        <v>66454227.7795037</v>
       </c>
       <c r="AA17" t="n">
         <v>8.778198949022282e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>86.25571142886017</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 15.280x + -7292.477</t>
-        </is>
+      <c r="W18" t="n">
+        <v>15.28039089519118</v>
       </c>
       <c r="X18" t="n">
         <v>-7292.476624573471</v>
@@ -7144,7 +6924,7 @@
         <v>428.3829152722445</v>
       </c>
       <c r="Z18" t="n">
-        <v>187.501</v>
+        <v>353225684.149655</v>
       </c>
       <c r="AA18" t="n">
         <v>8.644316165480016e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>86.1929289729532</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 15.028x + -7092.611</t>
-        </is>
+      <c r="W19" t="n">
+        <v>15.02767687447183</v>
       </c>
       <c r="X19" t="n">
         <v>-7092.611485683071</v>
@@ -7196,7 +6974,7 @@
         <v>425.3353741601115</v>
       </c>
       <c r="Z19" t="n">
-        <v>187.153</v>
+        <v>116867376.7142304</v>
       </c>
       <c r="AA19" t="n">
         <v>8.536167775033069e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>86.22281452282172</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 15.147x + -7095.152</t>
-        </is>
+      <c r="W20" t="n">
+        <v>15.14692699141047</v>
       </c>
       <c r="X20" t="n">
         <v>-7095.151652313633</v>
@@ -7248,7 +7024,7 @@
         <v>422.2906207194653</v>
       </c>
       <c r="Z20" t="n">
-        <v>186.256</v>
+        <v>231628942.6914996</v>
       </c>
       <c r="AA20" t="n">
         <v>8.443795545922185e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>86.19572113363522</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 15.039x + -6975.334</t>
-        </is>
+      <c r="W21" t="n">
+        <v>15.03873899755497</v>
       </c>
       <c r="X21" t="n">
         <v>-6975.334469223051</v>
@@ -7300,7 +7074,7 @@
         <v>419.3044655653769</v>
       </c>
       <c r="Z21" t="n">
-        <v>185.118</v>
+        <v>229870125.7516502</v>
       </c>
       <c r="AA21" t="n">
         <v>8.342861206783969e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>86.28564577899618</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 15.404x + -7100.616</t>
-        </is>
+      <c r="W22" t="n">
+        <v>15.40388698850746</v>
       </c>
       <c r="X22" t="n">
         <v>-7100.616029708968</v>
@@ -7352,7 +7124,7 @@
         <v>416.3153368583119</v>
       </c>
       <c r="Z22" t="n">
-        <v>182.796</v>
+        <v>369199774.5804985</v>
       </c>
       <c r="AA22" t="n">
         <v>8.240718858778662e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>82.58538992846334</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.684x + -5422.829</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.684231716737626</v>
       </c>
       <c r="X2" t="n">
         <v>-5422.829001986913</v>
@@ -7550,7 +7320,7 @@
         <v>473.7338192961772</v>
       </c>
       <c r="Z2" t="n">
-        <v>374.218</v>
+        <v>3662580913.677582</v>
       </c>
       <c r="AA2" t="n">
         <v>1.362371856452821e-05</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>84.20194311112579</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.848x + -5935.182</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.848138519560406</v>
       </c>
       <c r="X3" t="n">
         <v>-5935.181640114986</v>
@@ -7602,7 +7370,7 @@
         <v>505.2416117076925</v>
       </c>
       <c r="Z3" t="n">
-        <v>283.105</v>
+        <v>1013067522.250978</v>
       </c>
       <c r="AA3" t="n">
         <v>2.907913506570322e-06</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>84.73115555062793</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.844x + -6306.032</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.84377867017155</v>
       </c>
       <c r="X4" t="n">
         <v>-6306.031847322581</v>
@@ -7654,7 +7420,7 @@
         <v>501.9309252934821</v>
       </c>
       <c r="Z4" t="n">
-        <v>255.4689999999999</v>
+        <v>462625513.1415778</v>
       </c>
       <c r="AA4" t="n">
         <v>1.896365003181546e-06</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>85.10512346645012</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.677x + -6693.239</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.67676420210202</v>
       </c>
       <c r="X5" t="n">
         <v>-6693.238552575581</v>
@@ -7706,7 +7470,7 @@
         <v>498.1829296978888</v>
       </c>
       <c r="Z5" t="n">
-        <v>237.8200000000001</v>
+        <v>290644206.8760032</v>
       </c>
       <c r="AA5" t="n">
         <v>1.591777310518496e-06</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>85.38209844644207</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.380x + -7021.645</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.38044189166691</v>
       </c>
       <c r="X6" t="n">
         <v>-7021.644868862996</v>
@@ -7758,7 +7520,7 @@
         <v>494.0539812384313</v>
       </c>
       <c r="Z6" t="n">
-        <v>226.275</v>
+        <v>92908426.54140775</v>
       </c>
       <c r="AA6" t="n">
         <v>1.426486985183265e-06</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>85.46358061360702</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.604x + -7046.791</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.60377408319593</v>
       </c>
       <c r="X7" t="n">
         <v>-7046.79146399494</v>
@@ -7810,7 +7570,7 @@
         <v>489.4233714150621</v>
       </c>
       <c r="Z7" t="n">
-        <v>221.2859999999999</v>
+        <v>227679531.9324244</v>
       </c>
       <c r="AA7" t="n">
         <v>1.316241109357098e-06</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>85.6395974237423</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.115x + -7248.826</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.11464296838327</v>
       </c>
       <c r="X8" t="n">
         <v>-7248.825986570318</v>
@@ -7862,7 +7620,7 @@
         <v>484.6246491553262</v>
       </c>
       <c r="Z8" t="n">
-        <v>212.8420000000001</v>
+        <v>160794777.1034012</v>
       </c>
       <c r="AA8" t="n">
         <v>1.231416102251103e-06</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>85.75641327648039</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.477x + -7355.659</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.47703686619924</v>
       </c>
       <c r="X9" t="n">
         <v>-7355.659449026061</v>
@@ -7914,7 +7670,7 @@
         <v>479.7650701934186</v>
       </c>
       <c r="Z9" t="n">
-        <v>208.4019999999999</v>
+        <v>134412634.0496769</v>
       </c>
       <c r="AA9" t="n">
         <v>1.16560288558556e-06</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>85.71535107482742</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.347x + -7170.807</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.34740299585458</v>
       </c>
       <c r="X10" t="n">
         <v>-7170.807106811348</v>
@@ -7966,7 +7720,7 @@
         <v>475.0659821543966</v>
       </c>
       <c r="Z10" t="n">
-        <v>205.607</v>
+        <v>75374975.55866922</v>
       </c>
       <c r="AA10" t="n">
         <v>1.114184749502611e-06</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>85.98735396082425</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.255x + -7612.880</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.25545003970677</v>
       </c>
       <c r="X11" t="n">
         <v>-7612.879650833882</v>
@@ -8018,7 +7770,7 @@
         <v>470.5584005846731</v>
       </c>
       <c r="Z11" t="n">
-        <v>199.8399999999999</v>
+        <v>162780846.5726622</v>
       </c>
       <c r="AA11" t="n">
         <v>1.072257515075533e-06</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>84.78155887837785</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.949x + -6274.936</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.94910537441375</v>
       </c>
       <c r="X2" t="n">
         <v>-6274.935947885607</v>
@@ -8216,7 +7966,7 @@
         <v>484.884699817303</v>
       </c>
       <c r="Z2" t="n">
-        <v>255.231</v>
+        <v>355113031.7250056</v>
       </c>
       <c r="AA2" t="n">
         <v>1.808766172188195e-06</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>85.52275984351037</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.771x + -6945.695</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.77106185435287</v>
       </c>
       <c r="X3" t="n">
         <v>-6945.694822136638</v>
@@ -8268,7 +8016,7 @@
         <v>474.7035148491834</v>
       </c>
       <c r="Z3" t="n">
-        <v>220.418</v>
+        <v>206070272.7912714</v>
       </c>
       <c r="AA3" t="n">
         <v>1.298060893215393e-06</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>85.59049512193246</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.968x + -6902.712</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.96803549334798</v>
       </c>
       <c r="X4" t="n">
         <v>-6902.711823665977</v>
@@ -8320,7 +8066,7 @@
         <v>470.0777566933614</v>
       </c>
       <c r="Z4" t="n">
-        <v>211.413</v>
+        <v>113522863.573035</v>
       </c>
       <c r="AA4" t="n">
         <v>1.173991412747739e-06</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>85.81503565292</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.667x + -7214.449</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.66650862869756</v>
       </c>
       <c r="X5" t="n">
         <v>-7214.44922391076</v>
@@ -8372,7 +8116,7 @@
         <v>466.3156443603283</v>
       </c>
       <c r="Z5" t="n">
-        <v>203.663</v>
+        <v>62791011.76172917</v>
       </c>
       <c r="AA5" t="n">
         <v>1.106332742237177e-06</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>85.93631231606432</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.076x + -7358.138</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.07580496942494</v>
       </c>
       <c r="X6" t="n">
         <v>-7358.138420855429</v>
@@ -8424,7 +8166,7 @@
         <v>462.6292425085679</v>
       </c>
       <c r="Z6" t="n">
-        <v>198.034</v>
+        <v>101367344.4809037</v>
       </c>
       <c r="AA6" t="n">
         <v>1.057235159675903e-06</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>85.80957651988884</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.649x + -7022.076</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.64864086890501</v>
       </c>
       <c r="X7" t="n">
         <v>-7022.075921221984</v>
@@ -8476,7 +8216,7 @@
         <v>458.8581701532798</v>
       </c>
       <c r="Z7" t="n">
-        <v>196.684</v>
+        <v>42430884.49731868</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02005034564565e-06</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>86.05776625480708</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.511x + -7434.344</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.51089397159833</v>
       </c>
       <c r="X8" t="n">
         <v>-7434.344010347481</v>
@@ -8528,7 +8266,7 @@
         <v>455.0869893102939</v>
       </c>
       <c r="Z8" t="n">
-        <v>192.038</v>
+        <v>74210787.16324848</v>
       </c>
       <c r="AA8" t="n">
         <v>9.922564139804294e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>86.09417664486328</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.647x + -7428.082</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.64659155253502</v>
       </c>
       <c r="X9" t="n">
         <v>-7428.082345821925</v>
@@ -8580,7 +8316,7 @@
         <v>451.5493399788623</v>
       </c>
       <c r="Z9" t="n">
-        <v>189.362</v>
+        <v>145881031.8591446</v>
       </c>
       <c r="AA9" t="n">
         <v>9.670763581717393e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>86.00484263254724</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.318x + -7170.581</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.3180568778303</v>
       </c>
       <c r="X10" t="n">
         <v>-7170.580770642491</v>
@@ -8632,7 +8366,7 @@
         <v>448.3053541255115</v>
       </c>
       <c r="Z10" t="n">
-        <v>189.543</v>
+        <v>27559080.97169546</v>
       </c>
       <c r="AA10" t="n">
         <v>9.463653600061264e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>86.05829791752852</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.513x + -7209.415</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.5128574133625</v>
       </c>
       <c r="X11" t="n">
         <v>-7209.415035910584</v>
@@ -8684,7 +8416,7 @@
         <v>445.1064134618819</v>
       </c>
       <c r="Z11" t="n">
-        <v>187.516</v>
+        <v>143682236.2221341</v>
       </c>
       <c r="AA11" t="n">
         <v>9.30002885933358e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>86.27178652094392</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 15.346x + -7605.863</t>
-        </is>
+      <c r="W12" t="n">
+        <v>15.34646353967342</v>
       </c>
       <c r="X12" t="n">
         <v>-7605.863129560093</v>
@@ -8736,7 +8466,7 @@
         <v>442.0399033444564</v>
       </c>
       <c r="Z12" t="n">
-        <v>184.034</v>
+        <v>355382726.0797141</v>
       </c>
       <c r="AA12" t="n">
         <v>9.144436966195757e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>86.21263108231373</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 15.106x + -7405.062</t>
-        </is>
+      <c r="W13" t="n">
+        <v>15.10608168303221</v>
       </c>
       <c r="X13" t="n">
         <v>-7405.061580935761</v>
@@ -8788,7 +8516,7 @@
         <v>439.0231331823721</v>
       </c>
       <c r="Z13" t="n">
-        <v>183.0409999999999</v>
+        <v>253139142.7484311</v>
       </c>
       <c r="AA13" t="n">
         <v>8.990603939861496e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>86.09831015066743</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 14.662x + -7101.120</t>
-        </is>
+      <c r="W14" t="n">
+        <v>14.66215651106469</v>
       </c>
       <c r="X14" t="n">
         <v>-7101.120272662076</v>
@@ -8840,7 +8566,7 @@
         <v>436.0900456156388</v>
       </c>
       <c r="Z14" t="n">
-        <v>183.028</v>
+        <v>110425024.3092927</v>
       </c>
       <c r="AA14" t="n">
         <v>8.868767868096841e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>86.21686815057282</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 15.123x + -7290.849</t>
-        </is>
+      <c r="W15" t="n">
+        <v>15.12304969400374</v>
       </c>
       <c r="X15" t="n">
         <v>-7290.849198095433</v>
@@ -8892,7 +8616,7 @@
         <v>433.187297301179</v>
       </c>
       <c r="Z15" t="n">
-        <v>180.176</v>
+        <v>44756321.40970081</v>
       </c>
       <c r="AA15" t="n">
         <v>8.754502068073215e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>86.35533008557465</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 15.699x + -7541.798</t>
-        </is>
+      <c r="W16" t="n">
+        <v>15.69922079080311</v>
       </c>
       <c r="X16" t="n">
         <v>-7541.798441316817</v>
@@ -8944,7 +8666,7 @@
         <v>430.328627180213</v>
       </c>
       <c r="Z16" t="n">
-        <v>179.3140000000001</v>
+        <v>204915776.1680939</v>
       </c>
       <c r="AA16" t="n">
         <v>8.664470345149445e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>86.37799283449269</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 15.798x + -7529.774</t>
-        </is>
+      <c r="W17" t="n">
+        <v>15.79771482541936</v>
       </c>
       <c r="X17" t="n">
         <v>-7529.773770926233</v>
@@ -8996,7 +8716,7 @@
         <v>427.5118109095331</v>
       </c>
       <c r="Z17" t="n">
-        <v>177.2739999999999</v>
+        <v>236039388.4358574</v>
       </c>
       <c r="AA17" t="n">
         <v>8.555866333473535e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>86.44201250614353</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 16.083x + -7617.267</t>
-        </is>
+      <c r="W18" t="n">
+        <v>16.08271867019238</v>
       </c>
       <c r="X18" t="n">
         <v>-7617.267294575604</v>
@@ -9048,7 +8766,7 @@
         <v>424.6600818163836</v>
       </c>
       <c r="Z18" t="n">
-        <v>175.024</v>
+        <v>467146461.0758933</v>
       </c>
       <c r="AA18" t="n">
         <v>8.453533080133084e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>86.33631493433467</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 15.618x + -7309.896</t>
-        </is>
+      <c r="W19" t="n">
+        <v>15.6175183565893</v>
       </c>
       <c r="X19" t="n">
         <v>-7309.895856728192</v>
@@ -9100,7 +8816,7 @@
         <v>421.7794216213097</v>
       </c>
       <c r="Z19" t="n">
-        <v>175.881</v>
+        <v>177374146.0547042</v>
       </c>
       <c r="AA19" t="n">
         <v>8.36700635626022e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>86.55759977950409</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 16.624x + -7777.014</t>
-        </is>
+      <c r="W20" t="n">
+        <v>16.62410470942704</v>
       </c>
       <c r="X20" t="n">
         <v>-7777.014113823913</v>
@@ -9152,7 +8866,7 @@
         <v>418.8648413205626</v>
       </c>
       <c r="Z20" t="n">
-        <v>173.083</v>
+        <v>229731178.3723945</v>
       </c>
       <c r="AA20" t="n">
         <v>8.29334772169683e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>86.47434297442163</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 16.231x + -7507.868</t>
-        </is>
+      <c r="W21" t="n">
+        <v>16.23057618194329</v>
       </c>
       <c r="X21" t="n">
         <v>-7507.868026603772</v>
@@ -9204,7 +8916,7 @@
         <v>416.0055626305751</v>
       </c>
       <c r="Z21" t="n">
-        <v>173.056</v>
+        <v>120526718.694884</v>
       </c>
       <c r="AA21" t="n">
         <v>8.212145709939803e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>86.56979034950589</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 16.683x + -7676.419</t>
-        </is>
+      <c r="W22" t="n">
+        <v>16.68332702673313</v>
       </c>
       <c r="X22" t="n">
         <v>-7676.419263588273</v>
@@ -9256,7 +8966,7 @@
         <v>413.0712188009529</v>
       </c>
       <c r="Z22" t="n">
-        <v>171.023</v>
+        <v>121548027.0439025</v>
       </c>
       <c r="AA22" t="n">
         <v>8.129018748708925e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>82.7018265444289</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.808x + -5178.691</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.808196206338663</v>
       </c>
       <c r="X2" t="n">
         <v>-5178.691403244354</v>
@@ -9454,7 +9162,7 @@
         <v>454.7140628599946</v>
       </c>
       <c r="Z2" t="n">
-        <v>371.366</v>
+        <v>296787138.5262638</v>
       </c>
       <c r="AA2" t="n">
         <v>1.442896959231097e-05</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>84.1345972705217</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.734x + -5595.680</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.734283207498484</v>
       </c>
       <c r="X3" t="n">
         <v>-5595.680165755084</v>
@@ -9506,7 +9212,7 @@
         <v>493.7219846016717</v>
       </c>
       <c r="Z3" t="n">
-        <v>287.437</v>
+        <v>684393800.2032897</v>
       </c>
       <c r="AA3" t="n">
         <v>2.145430711220483e-06</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>84.8710411289631</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.141x + -6219.262</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.14118006192885</v>
       </c>
       <c r="X4" t="n">
         <v>-6219.262191740373</v>
@@ -9558,7 +9262,7 @@
         <v>487.0570230297017</v>
       </c>
       <c r="Z4" t="n">
-        <v>254.654</v>
+        <v>83416286.49601777</v>
       </c>
       <c r="AA4" t="n">
         <v>1.559200790171495e-06</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>85.2661129986185</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.076x + -6630.670</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.07577321899202</v>
       </c>
       <c r="X5" t="n">
         <v>-6630.67046464207</v>
@@ -9610,7 +9312,7 @@
         <v>481.4987956014188</v>
       </c>
       <c r="Z5" t="n">
-        <v>235.508</v>
+        <v>97234133.54792821</v>
       </c>
       <c r="AA5" t="n">
         <v>1.341308952563464e-06</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>85.52379449953956</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.774x + -6913.118</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.77402588142602</v>
       </c>
       <c r="X6" t="n">
         <v>-6913.117957816235</v>
@@ -9662,7 +9362,7 @@
         <v>475.6589047444313</v>
       </c>
       <c r="Z6" t="n">
-        <v>224.22</v>
+        <v>40392632.62186754</v>
       </c>
       <c r="AA6" t="n">
         <v>1.215800879654981e-06</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>85.52758181703794</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.785x + -6779.459</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.78488725925079</v>
       </c>
       <c r="X7" t="n">
         <v>-6779.458745065738</v>
@@ -9714,7 +9412,7 @@
         <v>469.5170387710796</v>
       </c>
       <c r="Z7" t="n">
-        <v>220.336</v>
+        <v>237065273.760372</v>
       </c>
       <c r="AA7" t="n">
         <v>1.13258003917621e-06</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>85.71854653558464</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.357x + -6985.424</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.35740204621767</v>
       </c>
       <c r="X8" t="n">
         <v>-6985.424340662788</v>
@@ -9766,7 +9462,7 @@
         <v>463.5401903201668</v>
       </c>
       <c r="Z8" t="n">
-        <v>212.02</v>
+        <v>194730491.0327183</v>
       </c>
       <c r="AA8" t="n">
         <v>1.067916225075361e-06</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>85.92717248131648</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.044x + -7262.260</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.044111147868</v>
       </c>
       <c r="X9" t="n">
         <v>-7262.25964341097</v>
@@ -9818,7 +9512,7 @@
         <v>457.9519030044322</v>
       </c>
       <c r="Z9" t="n">
-        <v>205.276</v>
+        <v>48138607.27177531</v>
       </c>
       <c r="AA9" t="n">
         <v>1.019854564218235e-06</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>85.98574501677405</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.250x + -7258.901</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.24971761705974</v>
       </c>
       <c r="X10" t="n">
         <v>-7258.901441500197</v>
@@ -9870,7 +9562,7 @@
         <v>452.7277353084801</v>
       </c>
       <c r="Z10" t="n">
-        <v>201.3249999999999</v>
+        <v>51712806.20927975</v>
       </c>
       <c r="AA10" t="n">
         <v>9.815714045508991e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>86.00640051918805</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.324x + -7197.159</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.32366043472886</v>
       </c>
       <c r="X11" t="n">
         <v>-7197.159314864291</v>
@@ -9922,7 +9612,7 @@
         <v>447.9635293046174</v>
       </c>
       <c r="Z11" t="n">
-        <v>198.921</v>
+        <v>68623519.53066643</v>
       </c>
       <c r="AA11" t="n">
         <v>9.532182013866964e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-318.979</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-263.8910000000001</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-249.354</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-237.933</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-232.605</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-225.703</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-221.2890000000001</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-217.24</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-212.787</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-209.21</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-391.198</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-296.4540000000001</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-270.971</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-256.049</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-246.5940000000001</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-239.462</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-231.125</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-228.739</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-224.625</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-221.218</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-372.9979999999999</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-296.955</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-269.418</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-253.001</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-242.379</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-234.2009999999999</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-227.5229999999999</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-222.327</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-218.6819999999999</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-215.037</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-374.218</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-283.105</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-255.4689999999999</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-237.8200000000001</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-226.275</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-221.2859999999999</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-212.8420000000001</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-208.4019999999999</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-205.607</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-199.8399999999999</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-371.366</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-287.437</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-254.654</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-235.508</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-224.22</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-220.336</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-212.02</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-205.276</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-201.3249999999999</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-198.921</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-318.979</v>
+        <v>169.7359999999999</v>
       </c>
       <c r="D2" t="n">
         <v>4.06231e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-263.8910000000001</v>
+        <v>156.4959999999999</v>
       </c>
       <c r="D3" t="n">
         <v>4.01658e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-249.354</v>
+        <v>150.422</v>
       </c>
       <c r="D4" t="n">
         <v>4.01002e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-237.933</v>
+        <v>149.673</v>
       </c>
       <c r="D5" t="n">
         <v>4.00951e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-232.605</v>
+        <v>132.994</v>
       </c>
       <c r="D6" t="n">
         <v>4.03341e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-225.703</v>
+        <v>123.899</v>
       </c>
       <c r="D7" t="n">
         <v>4.04904e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-221.2890000000001</v>
+        <v>115.547</v>
       </c>
       <c r="D8" t="n">
         <v>4.0578e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-217.24</v>
+        <v>110.194</v>
       </c>
       <c r="D9" t="n">
         <v>4.06198e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-212.787</v>
+        <v>106.366</v>
       </c>
       <c r="D10" t="n">
         <v>4.06765e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-209.21</v>
+        <v>103.319</v>
       </c>
       <c r="D11" t="n">
         <v>4.06819e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-244.097</v>
+        <v>146.6200000000001</v>
       </c>
       <c r="D2" t="n">
         <v>4.38136e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-222.042</v>
+        <v>123.864</v>
       </c>
       <c r="D3" t="n">
         <v>4.33907e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-213.101</v>
+        <v>120.127</v>
       </c>
       <c r="D4" t="n">
         <v>4.31461e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-210.652</v>
+        <v>115.028</v>
       </c>
       <c r="D5" t="n">
         <v>4.29532e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-207.506</v>
+        <v>111.7569999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.28319e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-202.2909999999999</v>
+        <v>110.511</v>
       </c>
       <c r="D7" t="n">
         <v>4.27434e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-201.451</v>
+        <v>105.834</v>
       </c>
       <c r="D8" t="n">
         <v>4.26567e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-198.793</v>
+        <v>104.54</v>
       </c>
       <c r="D9" t="n">
         <v>4.25913e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-196.66</v>
+        <v>101.923</v>
       </c>
       <c r="D10" t="n">
         <v>4.25449e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-191.855</v>
+        <v>101.522</v>
       </c>
       <c r="D11" t="n">
         <v>4.25006e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-193.032</v>
+        <v>97.41800000000001</v>
       </c>
       <c r="D12" t="n">
         <v>4.24651e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-192.61</v>
+        <v>95.50299999999999</v>
       </c>
       <c r="D13" t="n">
         <v>4.24329e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-189.516</v>
+        <v>94.517</v>
       </c>
       <c r="D14" t="n">
         <v>4.24097e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-189.105</v>
+        <v>91.726</v>
       </c>
       <c r="D15" t="n">
         <v>4.24007e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-187.767</v>
+        <v>90.57299999999998</v>
       </c>
       <c r="D16" t="n">
         <v>4.23705e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-187.425</v>
+        <v>88.90000000000003</v>
       </c>
       <c r="D17" t="n">
         <v>4.23491e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-185.425</v>
+        <v>87.82900000000001</v>
       </c>
       <c r="D18" t="n">
         <v>4.23312e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-186.873</v>
+        <v>84.20699999999999</v>
       </c>
       <c r="D19" t="n">
         <v>4.23191e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-183.537</v>
+        <v>85.12200000000001</v>
       </c>
       <c r="D20" t="n">
         <v>4.23159e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-181.081</v>
+        <v>84.25</v>
       </c>
       <c r="D21" t="n">
         <v>4.2307e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-184.1990000000001</v>
+        <v>80.15899999999999</v>
       </c>
       <c r="D22" t="n">
         <v>4.23035e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-252.2190000000001</v>
+        <v>159.521</v>
       </c>
       <c r="D2" t="n">
         <v>4.04393e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-225.913</v>
+        <v>129.987</v>
       </c>
       <c r="D3" t="n">
         <v>4.07706e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-218.407</v>
+        <v>121.414</v>
       </c>
       <c r="D4" t="n">
         <v>4.07966e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-213.936</v>
+        <v>118.814</v>
       </c>
       <c r="D5" t="n">
         <v>4.07754e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-210.581</v>
+        <v>116.859</v>
       </c>
       <c r="D6" t="n">
         <v>4.07555e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-206.0630000000001</v>
+        <v>115.15</v>
       </c>
       <c r="D7" t="n">
         <v>4.07626e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-205.4670000000001</v>
+        <v>111.708</v>
       </c>
       <c r="D8" t="n">
         <v>4.07525e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-198.372</v>
+        <v>111.664</v>
       </c>
       <c r="D9" t="n">
         <v>4.07573e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-200.828</v>
+        <v>106.804</v>
       </c>
       <c r="D10" t="n">
         <v>4.07423e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-201.2020000000001</v>
+        <v>102.842</v>
       </c>
       <c r="D11" t="n">
         <v>4.07522e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-202.195</v>
+        <v>100.172</v>
       </c>
       <c r="D12" t="n">
         <v>4.07495e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-197.675</v>
+        <v>100.331</v>
       </c>
       <c r="D13" t="n">
         <v>4.07495e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-196.662</v>
+        <v>99.54599999999999</v>
       </c>
       <c r="D14" t="n">
         <v>4.07561e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-195.315</v>
+        <v>97.00899999999996</v>
       </c>
       <c r="D15" t="n">
         <v>4.07588e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-194.843</v>
+        <v>94.45400000000001</v>
       </c>
       <c r="D16" t="n">
         <v>4.0782e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-194.53</v>
+        <v>93.88200000000001</v>
       </c>
       <c r="D17" t="n">
         <v>4.0786e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-192.979</v>
+        <v>91.95400000000001</v>
       </c>
       <c r="D18" t="n">
         <v>4.07895e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-194.591</v>
+        <v>88.858</v>
       </c>
       <c r="D19" t="n">
         <v>4.08034e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-191.8320000000001</v>
+        <v>87.77999999999997</v>
       </c>
       <c r="D20" t="n">
         <v>4.08109e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-191.65</v>
+        <v>86.488</v>
       </c>
       <c r="D21" t="n">
         <v>4.08281e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-192.124</v>
+        <v>83.93599999999998</v>
       </c>
       <c r="D22" t="n">
         <v>4.0839e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-391.198</v>
+        <v>262.504</v>
       </c>
       <c r="D2" t="n">
         <v>4.10809e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-296.4540000000001</v>
+        <v>174.836</v>
       </c>
       <c r="D3" t="n">
         <v>4.27465e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-270.971</v>
+        <v>156.252</v>
       </c>
       <c r="D4" t="n">
         <v>4.26496e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-256.049</v>
+        <v>149.34</v>
       </c>
       <c r="D5" t="n">
         <v>4.24367e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-246.5940000000001</v>
+        <v>145.3699999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.22243e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-239.462</v>
+        <v>139.777</v>
       </c>
       <c r="D7" t="n">
         <v>4.20916e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-231.125</v>
+        <v>138.743</v>
       </c>
       <c r="D8" t="n">
         <v>4.19867e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-228.739</v>
+        <v>132.643</v>
       </c>
       <c r="D9" t="n">
         <v>4.18922e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-224.625</v>
+        <v>130.433</v>
       </c>
       <c r="D10" t="n">
         <v>4.1818e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-221.218</v>
+        <v>125.848</v>
       </c>
       <c r="D11" t="n">
         <v>4.17697e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-288.5219999999999</v>
+        <v>154.8630000000001</v>
       </c>
       <c r="D2" t="n">
         <v>4.34957e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-250.4160000000001</v>
+        <v>128.346</v>
       </c>
       <c r="D3" t="n">
         <v>4.32251e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-233.221</v>
+        <v>125.253</v>
       </c>
       <c r="D4" t="n">
         <v>4.29211e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-226.752</v>
+        <v>119.668</v>
       </c>
       <c r="D5" t="n">
         <v>4.26899e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-221.253</v>
+        <v>118.0219999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.25014e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-216.3349999999999</v>
+        <v>115.446</v>
       </c>
       <c r="D7" t="n">
         <v>4.23713e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-212.8200000000001</v>
+        <v>111.303</v>
       </c>
       <c r="D8" t="n">
         <v>4.22673e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-210.386</v>
+        <v>108.67</v>
       </c>
       <c r="D9" t="n">
         <v>4.21853e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-205.914</v>
+        <v>108.903</v>
       </c>
       <c r="D10" t="n">
         <v>4.21175e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-207.3650000000001</v>
+        <v>103.167</v>
       </c>
       <c r="D11" t="n">
         <v>4.20735e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-202.934</v>
+        <v>103.635</v>
       </c>
       <c r="D12" t="n">
         <v>4.20347e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-200.639</v>
+        <v>101.796</v>
       </c>
       <c r="D13" t="n">
         <v>4.20011e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-198.266</v>
+        <v>99.78700000000003</v>
       </c>
       <c r="D14" t="n">
         <v>4.19676e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-201.864</v>
+        <v>96.41400000000004</v>
       </c>
       <c r="D15" t="n">
         <v>4.19397e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-196.441</v>
+        <v>96.06</v>
       </c>
       <c r="D16" t="n">
         <v>4.19329e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-198.597</v>
+        <v>93.17400000000004</v>
       </c>
       <c r="D17" t="n">
         <v>4.18997e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-196.943</v>
+        <v>91.44099999999997</v>
       </c>
       <c r="D18" t="n">
         <v>4.18886e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-193.72</v>
+        <v>90.58600000000001</v>
       </c>
       <c r="D19" t="n">
         <v>4.18725e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-193.475</v>
+        <v>89.36499999999995</v>
       </c>
       <c r="D20" t="n">
         <v>4.18796e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-192.172</v>
+        <v>87.89699999999999</v>
       </c>
       <c r="D21" t="n">
         <v>4.18724e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-188.014</v>
+        <v>88.505</v>
       </c>
       <c r="D22" t="n">
         <v>4.18656e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-372.9979999999999</v>
+        <v>249.226</v>
       </c>
       <c r="D2" t="n">
         <v>4.30617e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-296.955</v>
+        <v>170.275</v>
       </c>
       <c r="D3" t="n">
         <v>4.45063e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-269.418</v>
+        <v>155.854</v>
       </c>
       <c r="D4" t="n">
         <v>4.43561e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-253.001</v>
+        <v>149.561</v>
       </c>
       <c r="D5" t="n">
         <v>4.40693e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-242.379</v>
+        <v>144.996</v>
       </c>
       <c r="D6" t="n">
         <v>4.38016e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-234.2009999999999</v>
+        <v>139.1750000000001</v>
       </c>
       <c r="D7" t="n">
         <v>4.36161e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-227.5229999999999</v>
+        <v>135.1300000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.34615e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-222.327</v>
+        <v>129.705</v>
       </c>
       <c r="D9" t="n">
         <v>4.33202e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-218.6819999999999</v>
+        <v>127.003</v>
       </c>
       <c r="D10" t="n">
         <v>4.31557e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-215.037</v>
+        <v>122.172</v>
       </c>
       <c r="D11" t="n">
         <v>4.30722e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-305.5329999999999</v>
+        <v>160.167</v>
       </c>
       <c r="D2" t="n">
         <v>4.58809e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-263.838</v>
+        <v>138.1</v>
       </c>
       <c r="D3" t="n">
         <v>4.53072e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-244.96</v>
+        <v>129.027</v>
       </c>
       <c r="D4" t="n">
         <v>4.48432e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-232.9459999999999</v>
+        <v>124.3340000000001</v>
       </c>
       <c r="D5" t="n">
         <v>4.44464e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-225.91</v>
+        <v>120.244</v>
       </c>
       <c r="D6" t="n">
         <v>4.41536e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-216.5250000000001</v>
+        <v>118.028</v>
       </c>
       <c r="D7" t="n">
         <v>4.39399e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-213.976</v>
+        <v>113.074</v>
       </c>
       <c r="D8" t="n">
         <v>4.37618e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-210.085</v>
+        <v>109.406</v>
       </c>
       <c r="D9" t="n">
         <v>4.36257e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-205.7130000000001</v>
+        <v>106.69</v>
       </c>
       <c r="D10" t="n">
         <v>4.35313e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-204.225</v>
+        <v>103.692</v>
       </c>
       <c r="D11" t="n">
         <v>4.34448e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-200.006</v>
+        <v>103.007</v>
       </c>
       <c r="D12" t="n">
         <v>4.33791e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-199.599</v>
+        <v>98.77200000000005</v>
       </c>
       <c r="D13" t="n">
         <v>4.33169e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-194.5389999999999</v>
+        <v>98.423</v>
       </c>
       <c r="D14" t="n">
         <v>4.32685e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-194.054</v>
+        <v>95.363</v>
       </c>
       <c r="D15" t="n">
         <v>4.32169e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-190.3729999999999</v>
+        <v>95.43600000000004</v>
       </c>
       <c r="D16" t="n">
         <v>4.3181e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-191.122</v>
+        <v>92.89800000000002</v>
       </c>
       <c r="D17" t="n">
         <v>4.31649e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-187.501</v>
+        <v>92.55700000000002</v>
       </c>
       <c r="D18" t="n">
         <v>4.31129e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-187.153</v>
+        <v>89.63600000000002</v>
       </c>
       <c r="D19" t="n">
         <v>4.30989e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-186.256</v>
+        <v>88.459</v>
       </c>
       <c r="D20" t="n">
         <v>4.30699e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-185.118</v>
+        <v>86.61900000000003</v>
       </c>
       <c r="D21" t="n">
         <v>4.30495e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-182.796</v>
+        <v>85.46499999999997</v>
       </c>
       <c r="D22" t="n">
         <v>4.30317e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-374.218</v>
+        <v>252.609</v>
       </c>
       <c r="D2" t="n">
         <v>4.35053e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-283.105</v>
+        <v>164.822</v>
       </c>
       <c r="D3" t="n">
         <v>4.51048e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-255.4689999999999</v>
+        <v>147.1370000000001</v>
       </c>
       <c r="D4" t="n">
         <v>4.48767e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-237.8200000000001</v>
+        <v>141.7979999999999</v>
       </c>
       <c r="D5" t="n">
         <v>4.4517e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-226.275</v>
+        <v>138.0910000000001</v>
       </c>
       <c r="D6" t="n">
         <v>4.4222e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-221.2859999999999</v>
+        <v>132.848</v>
       </c>
       <c r="D7" t="n">
         <v>4.39685e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-212.8420000000001</v>
+        <v>130.141</v>
       </c>
       <c r="D8" t="n">
         <v>4.38041e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-208.4019999999999</v>
+        <v>125.787</v>
       </c>
       <c r="D9" t="n">
         <v>4.36693e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-205.607</v>
+        <v>121.0740000000001</v>
       </c>
       <c r="D10" t="n">
         <v>4.35442e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-199.8399999999999</v>
+        <v>119.4400000000001</v>
       </c>
       <c r="D11" t="n">
         <v>4.34572e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-255.231</v>
+        <v>153.023</v>
       </c>
       <c r="D2" t="n">
         <v>4.51162e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-220.418</v>
+        <v>129.379</v>
       </c>
       <c r="D3" t="n">
         <v>4.46847e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-211.413</v>
+        <v>119.571</v>
       </c>
       <c r="D4" t="n">
         <v>4.43147e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-203.663</v>
+        <v>117.955</v>
       </c>
       <c r="D5" t="n">
         <v>4.40309e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-198.034</v>
+        <v>115.4640000000001</v>
       </c>
       <c r="D6" t="n">
         <v>4.38424e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-196.684</v>
+        <v>109.395</v>
       </c>
       <c r="D7" t="n">
         <v>4.36996e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-192.038</v>
+        <v>109.599</v>
       </c>
       <c r="D8" t="n">
         <v>4.35761e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-189.362</v>
+        <v>107.878</v>
       </c>
       <c r="D9" t="n">
         <v>4.34831e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-189.543</v>
+        <v>102.998</v>
       </c>
       <c r="D10" t="n">
         <v>4.34146e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-187.516</v>
+        <v>101.88</v>
       </c>
       <c r="D11" t="n">
         <v>4.33535e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-184.034</v>
+        <v>102.292</v>
       </c>
       <c r="D12" t="n">
         <v>4.32944e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-183.0409999999999</v>
+        <v>99.053</v>
       </c>
       <c r="D13" t="n">
         <v>4.32504e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-183.028</v>
+        <v>95.80500000000001</v>
       </c>
       <c r="D14" t="n">
         <v>4.3227e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-180.176</v>
+        <v>95.767</v>
       </c>
       <c r="D15" t="n">
         <v>4.31992e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-179.3140000000001</v>
+        <v>96.02799999999996</v>
       </c>
       <c r="D16" t="n">
         <v>4.31527e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-177.2739999999999</v>
+        <v>94.37</v>
       </c>
       <c r="D17" t="n">
         <v>4.31349e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-175.024</v>
+        <v>93.35500000000002</v>
       </c>
       <c r="D18" t="n">
         <v>4.31111e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-175.881</v>
+        <v>89.81599999999997</v>
       </c>
       <c r="D19" t="n">
         <v>4.31054e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-173.083</v>
+        <v>91.851</v>
       </c>
       <c r="D20" t="n">
         <v>4.30803e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-173.056</v>
+        <v>89.185</v>
       </c>
       <c r="D21" t="n">
         <v>4.308e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-171.023</v>
+        <v>88.81700000000001</v>
       </c>
       <c r="D22" t="n">
         <v>4.30646e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-371.366</v>
+        <v>222.272</v>
       </c>
       <c r="D2" t="n">
         <v>4.48386e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-287.437</v>
+        <v>146.141</v>
       </c>
       <c r="D3" t="n">
         <v>4.55766e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-254.654</v>
+        <v>134.244</v>
       </c>
       <c r="D4" t="n">
         <v>4.49985e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-235.508</v>
+        <v>128.718</v>
       </c>
       <c r="D5" t="n">
         <v>4.44787e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-224.22</v>
+        <v>124.217</v>
       </c>
       <c r="D6" t="n">
         <v>4.40734e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-220.336</v>
+        <v>118.112</v>
       </c>
       <c r="D7" t="n">
         <v>4.3773e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-212.02</v>
+        <v>114.285</v>
       </c>
       <c r="D8" t="n">
         <v>4.35741e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-205.276</v>
+        <v>112.262</v>
       </c>
       <c r="D9" t="n">
         <v>4.34237e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-201.3249999999999</v>
+        <v>108.089</v>
       </c>
       <c r="D10" t="n">
         <v>4.33108e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-198.921</v>
+        <v>104.666</v>
       </c>
       <c r="D11" t="n">
         <v>4.32166e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>169.7359999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>981.5706652040282</v>
+      </c>
       <c r="D2" t="n">
         <v>4.06231e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>156.4959999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>822.716150832833</v>
+      </c>
       <c r="D3" t="n">
         <v>4.01658e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>150.422</v>
       </c>
+      <c r="C4" t="n">
+        <v>819.4845709285679</v>
+      </c>
       <c r="D4" t="n">
         <v>4.01002e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>149.673</v>
       </c>
+      <c r="C5" t="n">
+        <v>945.0494002199925</v>
+      </c>
       <c r="D5" t="n">
         <v>4.00951e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>132.994</v>
       </c>
+      <c r="C6" t="n">
+        <v>883.3223279441712</v>
+      </c>
       <c r="D6" t="n">
         <v>4.03341e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>123.899</v>
       </c>
+      <c r="C7" t="n">
+        <v>870.7837497321913</v>
+      </c>
       <c r="D7" t="n">
         <v>4.04904e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>115.547</v>
       </c>
+      <c r="C8" t="n">
+        <v>834.47766586666</v>
+      </c>
       <c r="D8" t="n">
         <v>4.0578e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>110.194</v>
       </c>
+      <c r="C9" t="n">
+        <v>829.2698817281006</v>
+      </c>
       <c r="D9" t="n">
         <v>4.06198e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>106.366</v>
       </c>
+      <c r="C10" t="n">
+        <v>832.2576683994727</v>
+      </c>
       <c r="D10" t="n">
         <v>4.06765e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>103.319</v>
+      </c>
+      <c r="C11" t="n">
+        <v>833.9643613612189</v>
       </c>
       <c r="D11" t="n">
         <v>4.06819e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>146.6200000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1158.245178916465</v>
+      </c>
       <c r="D2" t="n">
         <v>4.38136e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>123.864</v>
       </c>
+      <c r="C3" t="n">
+        <v>811.5048114149108</v>
+      </c>
       <c r="D3" t="n">
         <v>4.33907e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>120.127</v>
       </c>
+      <c r="C4" t="n">
+        <v>821.0922197712887</v>
+      </c>
       <c r="D4" t="n">
         <v>4.31461e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>115.028</v>
       </c>
+      <c r="C5" t="n">
+        <v>797.0056871579822</v>
+      </c>
       <c r="D5" t="n">
         <v>4.29532e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>111.7569999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>775.8691131003998</v>
+      </c>
       <c r="D6" t="n">
         <v>4.28319e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>110.511</v>
       </c>
+      <c r="C7" t="n">
+        <v>830.5936162708834</v>
+      </c>
       <c r="D7" t="n">
         <v>4.27434e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>105.834</v>
       </c>
+      <c r="C8" t="n">
+        <v>786.7488257689147</v>
+      </c>
       <c r="D8" t="n">
         <v>4.26567e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>104.54</v>
       </c>
+      <c r="C9" t="n">
+        <v>830.9442347685457</v>
+      </c>
       <c r="D9" t="n">
         <v>4.25913e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>101.923</v>
       </c>
+      <c r="C10" t="n">
+        <v>821.234691593073</v>
+      </c>
       <c r="D10" t="n">
         <v>4.25449e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>101.522</v>
       </c>
+      <c r="C11" t="n">
+        <v>865.115266037779</v>
+      </c>
       <c r="D11" t="n">
         <v>4.25006e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>97.41800000000001</v>
       </c>
+      <c r="C12" t="n">
+        <v>826.9515630031428</v>
+      </c>
       <c r="D12" t="n">
         <v>4.24651e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>95.50299999999999</v>
       </c>
+      <c r="C13" t="n">
+        <v>801.4972287892305</v>
+      </c>
       <c r="D13" t="n">
         <v>4.24329e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>94.517</v>
       </c>
+      <c r="C14" t="n">
+        <v>828.6120530606524</v>
+      </c>
       <c r="D14" t="n">
         <v>4.24097e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>91.726</v>
       </c>
+      <c r="C15" t="n">
+        <v>788.6669762570326</v>
+      </c>
       <c r="D15" t="n">
         <v>4.24007e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>90.57299999999998</v>
       </c>
+      <c r="C16" t="n">
+        <v>789.3153687551186</v>
+      </c>
       <c r="D16" t="n">
         <v>4.23705e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>88.90000000000003</v>
       </c>
+      <c r="C17" t="n">
+        <v>793.9836823664394</v>
+      </c>
       <c r="D17" t="n">
         <v>4.23491e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>87.82900000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>829.3441563180164</v>
+      </c>
       <c r="D18" t="n">
         <v>4.23312e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>84.20699999999999</v>
       </c>
+      <c r="C19" t="n">
+        <v>779.1464909566723</v>
+      </c>
       <c r="D19" t="n">
         <v>4.23191e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>85.12200000000001</v>
       </c>
+      <c r="C20" t="n">
+        <v>829.5302802413765</v>
+      </c>
       <c r="D20" t="n">
         <v>4.23159e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>84.25</v>
       </c>
+      <c r="C21" t="n">
+        <v>850.7790718925049</v>
+      </c>
       <c r="D21" t="n">
         <v>4.2307e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>80.15899999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>782.6063177261946</v>
       </c>
       <c r="D22" t="n">
         <v>4.23035e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>159.521</v>
       </c>
+      <c r="C2" t="n">
+        <v>1337.339854305</v>
+      </c>
       <c r="D2" t="n">
         <v>4.04393e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>129.987</v>
       </c>
+      <c r="C3" t="n">
+        <v>854.7467510002933</v>
+      </c>
       <c r="D3" t="n">
         <v>4.07706e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>121.414</v>
       </c>
+      <c r="C4" t="n">
+        <v>798.2790782775323</v>
+      </c>
       <c r="D4" t="n">
         <v>4.07966e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>118.814</v>
       </c>
+      <c r="C5" t="n">
+        <v>800.1260177742972</v>
+      </c>
       <c r="D5" t="n">
         <v>4.07754e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>116.859</v>
       </c>
+      <c r="C6" t="n">
+        <v>817.0285687061125</v>
+      </c>
       <c r="D6" t="n">
         <v>4.07555e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>115.15</v>
       </c>
+      <c r="C7" t="n">
+        <v>847.4801478668043</v>
+      </c>
       <c r="D7" t="n">
         <v>4.07626e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>111.708</v>
       </c>
+      <c r="C8" t="n">
+        <v>828.6847737747993</v>
+      </c>
       <c r="D8" t="n">
         <v>4.07525e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>111.664</v>
       </c>
+      <c r="C9" t="n">
+        <v>903.5157236565656</v>
+      </c>
       <c r="D9" t="n">
         <v>4.07573e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>106.804</v>
       </c>
+      <c r="C10" t="n">
+        <v>853.0322863670558</v>
+      </c>
       <c r="D10" t="n">
         <v>4.07423e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>102.842</v>
       </c>
+      <c r="C11" t="n">
+        <v>810.1229125230125</v>
+      </c>
       <c r="D11" t="n">
         <v>4.07522e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>100.172</v>
       </c>
+      <c r="C12" t="n">
+        <v>793.8777669840641</v>
+      </c>
       <c r="D12" t="n">
         <v>4.07495e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>100.331</v>
       </c>
+      <c r="C13" t="n">
+        <v>827.2585291248532</v>
+      </c>
       <c r="D13" t="n">
         <v>4.07495e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>99.54599999999999</v>
       </c>
+      <c r="C14" t="n">
+        <v>886.4582365840547</v>
+      </c>
       <c r="D14" t="n">
         <v>4.07561e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>97.00899999999996</v>
       </c>
+      <c r="C15" t="n">
+        <v>834.8886958211322</v>
+      </c>
       <c r="D15" t="n">
         <v>4.07588e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>94.45400000000001</v>
       </c>
+      <c r="C16" t="n">
+        <v>815.5418746674343</v>
+      </c>
       <c r="D16" t="n">
         <v>4.0782e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>93.88200000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>848.4860392189031</v>
+      </c>
       <c r="D17" t="n">
         <v>4.0786e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>91.95400000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>835.8831773801375</v>
+      </c>
       <c r="D18" t="n">
         <v>4.07895e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>88.858</v>
       </c>
+      <c r="C19" t="n">
+        <v>792.808727316926</v>
+      </c>
       <c r="D19" t="n">
         <v>4.08034e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>87.77999999999997</v>
       </c>
+      <c r="C20" t="n">
+        <v>828.6739617257106</v>
+      </c>
       <c r="D20" t="n">
         <v>4.08109e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>86.488</v>
       </c>
+      <c r="C21" t="n">
+        <v>830.2629417737</v>
+      </c>
       <c r="D21" t="n">
         <v>4.08281e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>83.93599999999998</v>
+      </c>
+      <c r="C22" t="n">
+        <v>785.8788885979884</v>
       </c>
       <c r="D22" t="n">
         <v>4.0839e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>262.504</v>
       </c>
+      <c r="C2" t="n">
+        <v>2132.931072601401</v>
+      </c>
       <c r="D2" t="n">
         <v>4.10809e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>174.836</v>
       </c>
+      <c r="C3" t="n">
+        <v>962.0507560773692</v>
+      </c>
       <c r="D3" t="n">
         <v>4.27465e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>156.252</v>
       </c>
+      <c r="C4" t="n">
+        <v>844.7016828586424</v>
+      </c>
       <c r="D4" t="n">
         <v>4.26496e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>149.34</v>
       </c>
+      <c r="C5" t="n">
+        <v>826.1776097656403</v>
+      </c>
       <c r="D5" t="n">
         <v>4.24367e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>145.3699999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>835.6094439566376</v>
+      </c>
       <c r="D6" t="n">
         <v>4.22243e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>139.777</v>
       </c>
+      <c r="C7" t="n">
+        <v>808.9888000089759</v>
+      </c>
       <c r="D7" t="n">
         <v>4.20916e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>138.743</v>
       </c>
+      <c r="C8" t="n">
+        <v>848.1023659697598</v>
+      </c>
       <c r="D8" t="n">
         <v>4.19867e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>132.643</v>
       </c>
+      <c r="C9" t="n">
+        <v>818.8066573873742</v>
+      </c>
       <c r="D9" t="n">
         <v>4.18922e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>130.433</v>
       </c>
+      <c r="C10" t="n">
+        <v>836.571136778088</v>
+      </c>
       <c r="D10" t="n">
         <v>4.1818e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>125.848</v>
+      </c>
+      <c r="C11" t="n">
+        <v>826.2260452992264</v>
       </c>
       <c r="D11" t="n">
         <v>4.17697e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>154.8630000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1234.326845899763</v>
+      </c>
       <c r="D2" t="n">
         <v>4.34957e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>128.346</v>
       </c>
+      <c r="C3" t="n">
+        <v>830.1836086532726</v>
+      </c>
       <c r="D3" t="n">
         <v>4.32251e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>125.253</v>
       </c>
+      <c r="C4" t="n">
+        <v>855.0569320994252</v>
+      </c>
       <c r="D4" t="n">
         <v>4.29211e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>119.668</v>
       </c>
+      <c r="C5" t="n">
+        <v>800.4248962499717</v>
+      </c>
       <c r="D5" t="n">
         <v>4.26899e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>118.0219999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>842.4896489340592</v>
+      </c>
       <c r="D6" t="n">
         <v>4.25014e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>115.446</v>
       </c>
+      <c r="C7" t="n">
+        <v>840.2349759294596</v>
+      </c>
       <c r="D7" t="n">
         <v>4.23713e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>111.303</v>
       </c>
+      <c r="C8" t="n">
+        <v>837.7744288333091</v>
+      </c>
       <c r="D8" t="n">
         <v>4.22673e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>108.67</v>
       </c>
+      <c r="C9" t="n">
+        <v>810.3896600274452</v>
+      </c>
       <c r="D9" t="n">
         <v>4.21853e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>108.903</v>
       </c>
+      <c r="C10" t="n">
+        <v>862.3613416966576</v>
+      </c>
       <c r="D10" t="n">
         <v>4.21175e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>103.167</v>
       </c>
+      <c r="C11" t="n">
+        <v>804.8266974216032</v>
+      </c>
       <c r="D11" t="n">
         <v>4.20735e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>103.635</v>
       </c>
+      <c r="C12" t="n">
+        <v>855.7287605040963</v>
+      </c>
       <c r="D12" t="n">
         <v>4.20347e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>101.796</v>
       </c>
+      <c r="C13" t="n">
+        <v>847.4970056837491</v>
+      </c>
       <c r="D13" t="n">
         <v>4.20011e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>99.78700000000003</v>
       </c>
+      <c r="C14" t="n">
+        <v>842.8146477806347</v>
+      </c>
       <c r="D14" t="n">
         <v>4.19676e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>96.41400000000004</v>
       </c>
+      <c r="C15" t="n">
+        <v>801.2025420393586</v>
+      </c>
       <c r="D15" t="n">
         <v>4.19397e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>96.06</v>
       </c>
+      <c r="C16" t="n">
+        <v>825.6461295343061</v>
+      </c>
       <c r="D16" t="n">
         <v>4.19329e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>93.17400000000004</v>
       </c>
+      <c r="C17" t="n">
+        <v>785.4700475360258</v>
+      </c>
       <c r="D17" t="n">
         <v>4.18997e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>91.44099999999997</v>
       </c>
+      <c r="C18" t="n">
+        <v>765.6399789000141</v>
+      </c>
       <c r="D18" t="n">
         <v>4.18886e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>90.58600000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>769.5267211469886</v>
+      </c>
       <c r="D19" t="n">
         <v>4.18725e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>89.36499999999995</v>
       </c>
+      <c r="C20" t="n">
+        <v>802.6775075602387</v>
+      </c>
       <c r="D20" t="n">
         <v>4.18796e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>87.89699999999999</v>
       </c>
+      <c r="C21" t="n">
+        <v>801.9222450508177</v>
+      </c>
       <c r="D21" t="n">
         <v>4.18724e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>88.505</v>
+      </c>
+      <c r="C22" t="n">
+        <v>857.5028549134241</v>
       </c>
       <c r="D22" t="n">
         <v>4.18656e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>249.226</v>
       </c>
+      <c r="C2" t="n">
+        <v>1960.642146698272</v>
+      </c>
       <c r="D2" t="n">
         <v>4.30617e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>170.275</v>
       </c>
+      <c r="C3" t="n">
+        <v>924.4045478038105</v>
+      </c>
       <c r="D3" t="n">
         <v>4.45063e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>155.854</v>
       </c>
+      <c r="C4" t="n">
+        <v>849.885163958349</v>
+      </c>
       <c r="D4" t="n">
         <v>4.43561e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>149.561</v>
       </c>
+      <c r="C5" t="n">
+        <v>836.6921081328051</v>
+      </c>
       <c r="D5" t="n">
         <v>4.40693e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>144.996</v>
       </c>
+      <c r="C6" t="n">
+        <v>852.868629277738</v>
+      </c>
       <c r="D6" t="n">
         <v>4.38016e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>139.1750000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>837.7734302076218</v>
+      </c>
       <c r="D7" t="n">
         <v>4.36161e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>135.1300000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>831.5222623743668</v>
+      </c>
       <c r="D8" t="n">
         <v>4.34615e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>129.705</v>
       </c>
+      <c r="C9" t="n">
+        <v>818.6210053084528</v>
+      </c>
       <c r="D9" t="n">
         <v>4.33202e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>127.003</v>
       </c>
+      <c r="C10" t="n">
+        <v>834.3888419333576</v>
+      </c>
       <c r="D10" t="n">
         <v>4.31557e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>122.172</v>
+      </c>
+      <c r="C11" t="n">
+        <v>808.5438026539001</v>
       </c>
       <c r="D11" t="n">
         <v>4.30722e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>160.167</v>
       </c>
+      <c r="C2" t="n">
+        <v>1043.488223772058</v>
+      </c>
       <c r="D2" t="n">
         <v>4.58809e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>138.1</v>
       </c>
+      <c r="C3" t="n">
+        <v>884.9081570045441</v>
+      </c>
       <c r="D3" t="n">
         <v>4.53072e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>129.027</v>
       </c>
+      <c r="C4" t="n">
+        <v>808.5448063406125</v>
+      </c>
       <c r="D4" t="n">
         <v>4.48432e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>124.3340000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>813.539850958712</v>
+      </c>
       <c r="D5" t="n">
         <v>4.44464e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>120.244</v>
       </c>
+      <c r="C6" t="n">
+        <v>818.1181006768021</v>
+      </c>
       <c r="D6" t="n">
         <v>4.41536e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>118.028</v>
       </c>
+      <c r="C7" t="n">
+        <v>853.2044808485397</v>
+      </c>
       <c r="D7" t="n">
         <v>4.39399e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>113.074</v>
       </c>
+      <c r="C8" t="n">
+        <v>820.4497498212651</v>
+      </c>
       <c r="D8" t="n">
         <v>4.37618e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>109.406</v>
       </c>
+      <c r="C9" t="n">
+        <v>810.3757171685027</v>
+      </c>
       <c r="D9" t="n">
         <v>4.36257e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>106.69</v>
       </c>
+      <c r="C10" t="n">
+        <v>803.3956908552526</v>
+      </c>
       <c r="D10" t="n">
         <v>4.35313e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>103.692</v>
       </c>
+      <c r="C11" t="n">
+        <v>809.453438343553</v>
+      </c>
       <c r="D11" t="n">
         <v>4.34448e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>103.007</v>
       </c>
+      <c r="C12" t="n">
+        <v>828.6881346610938</v>
+      </c>
       <c r="D12" t="n">
         <v>4.33791e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>98.77200000000005</v>
       </c>
+      <c r="C13" t="n">
+        <v>776.9442698460623</v>
+      </c>
       <c r="D13" t="n">
         <v>4.33169e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>98.423</v>
       </c>
+      <c r="C14" t="n">
+        <v>822.5243209901458</v>
+      </c>
       <c r="D14" t="n">
         <v>4.32685e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>95.363</v>
       </c>
+      <c r="C15" t="n">
+        <v>797.6483694151879</v>
+      </c>
       <c r="D15" t="n">
         <v>4.32169e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>95.43600000000004</v>
       </c>
+      <c r="C16" t="n">
+        <v>830.8179406784708</v>
+      </c>
       <c r="D16" t="n">
         <v>4.3181e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>92.89800000000002</v>
       </c>
+      <c r="C17" t="n">
+        <v>801.233116758712</v>
+      </c>
       <c r="D17" t="n">
         <v>4.31649e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>92.55700000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>834.1956570558813</v>
+      </c>
       <c r="D18" t="n">
         <v>4.31129e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>89.63600000000002</v>
       </c>
+      <c r="C19" t="n">
+        <v>806.0227464239404</v>
+      </c>
       <c r="D19" t="n">
         <v>4.30989e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>88.459</v>
       </c>
+      <c r="C20" t="n">
+        <v>802.5224884028778</v>
+      </c>
       <c r="D20" t="n">
         <v>4.30699e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>86.61900000000003</v>
       </c>
+      <c r="C21" t="n">
+        <v>779.5675432615542</v>
+      </c>
       <c r="D21" t="n">
         <v>4.30495e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>85.46499999999997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>791.0505212679806</v>
       </c>
       <c r="D22" t="n">
         <v>4.30317e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>252.609</v>
       </c>
+      <c r="C2" t="n">
+        <v>2368.838046024616</v>
+      </c>
       <c r="D2" t="n">
         <v>4.35053e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>164.822</v>
       </c>
+      <c r="C3" t="n">
+        <v>935.9111320599898</v>
+      </c>
       <c r="D3" t="n">
         <v>4.51048e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>147.1370000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>826.5638912266113</v>
+      </c>
       <c r="D4" t="n">
         <v>4.48767e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>141.7979999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>799.3862411092333</v>
+      </c>
       <c r="D5" t="n">
         <v>4.4517e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>138.0910000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>811.0106204026055</v>
+      </c>
       <c r="D6" t="n">
         <v>4.4222e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>132.848</v>
       </c>
+      <c r="C7" t="n">
+        <v>802.0445561048178</v>
+      </c>
       <c r="D7" t="n">
         <v>4.39685e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>130.141</v>
       </c>
+      <c r="C8" t="n">
+        <v>816.625271683134</v>
+      </c>
       <c r="D8" t="n">
         <v>4.38041e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>125.787</v>
       </c>
+      <c r="C9" t="n">
+        <v>810.1837017576305</v>
+      </c>
       <c r="D9" t="n">
         <v>4.36693e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>121.0740000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>783.9633483053208</v>
+      </c>
       <c r="D10" t="n">
         <v>4.35442e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>119.4400000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>837.3760620435909</v>
       </c>
       <c r="D11" t="n">
         <v>4.34572e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>153.023</v>
       </c>
+      <c r="C2" t="n">
+        <v>1218.115784273938</v>
+      </c>
       <c r="D2" t="n">
         <v>4.51162e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>129.379</v>
       </c>
+      <c r="C3" t="n">
+        <v>849.4161967314963</v>
+      </c>
       <c r="D3" t="n">
         <v>4.46847e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>119.571</v>
       </c>
+      <c r="C4" t="n">
+        <v>786.2577100210832</v>
+      </c>
       <c r="D4" t="n">
         <v>4.43147e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>117.955</v>
       </c>
+      <c r="C5" t="n">
+        <v>806.8051627215439</v>
+      </c>
       <c r="D5" t="n">
         <v>4.40309e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>115.4640000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>798.854162741632</v>
+      </c>
       <c r="D6" t="n">
         <v>4.38424e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>109.395</v>
       </c>
+      <c r="C7" t="n">
+        <v>757.0462166453307</v>
+      </c>
       <c r="D7" t="n">
         <v>4.36996e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>109.599</v>
       </c>
+      <c r="C8" t="n">
+        <v>820.7290984517356</v>
+      </c>
       <c r="D8" t="n">
         <v>4.35761e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>107.878</v>
       </c>
+      <c r="C9" t="n">
+        <v>802.5648545550554</v>
+      </c>
       <c r="D9" t="n">
         <v>4.34831e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>102.998</v>
       </c>
+      <c r="C10" t="n">
+        <v>754.154687717345</v>
+      </c>
       <c r="D10" t="n">
         <v>4.34146e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>101.88</v>
       </c>
+      <c r="C11" t="n">
+        <v>765.997359315834</v>
+      </c>
       <c r="D11" t="n">
         <v>4.33535e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>102.292</v>
       </c>
+      <c r="C12" t="n">
+        <v>791.7857759088873</v>
+      </c>
       <c r="D12" t="n">
         <v>4.32944e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>99.053</v>
       </c>
+      <c r="C13" t="n">
+        <v>769.8171288125011</v>
+      </c>
       <c r="D13" t="n">
         <v>4.32504e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>95.80500000000001</v>
       </c>
+      <c r="C14" t="n">
+        <v>730.9405347501676</v>
+      </c>
       <c r="D14" t="n">
         <v>4.3227e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>95.767</v>
       </c>
+      <c r="C15" t="n">
+        <v>753.6890350173726</v>
+      </c>
       <c r="D15" t="n">
         <v>4.31992e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>96.02799999999996</v>
       </c>
+      <c r="C16" t="n">
+        <v>794.8234799865299</v>
+      </c>
       <c r="D16" t="n">
         <v>4.31527e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>94.37</v>
       </c>
+      <c r="C17" t="n">
+        <v>779.6009169260756</v>
+      </c>
       <c r="D17" t="n">
         <v>4.31349e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>93.35500000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>805.3870022442122</v>
+      </c>
       <c r="D18" t="n">
         <v>4.31111e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>89.81599999999997</v>
       </c>
+      <c r="C19" t="n">
+        <v>752.1526997067319</v>
+      </c>
       <c r="D19" t="n">
         <v>4.31054e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>91.851</v>
       </c>
+      <c r="C20" t="n">
+        <v>826.665778252878</v>
+      </c>
       <c r="D20" t="n">
         <v>4.30803e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>89.185</v>
       </c>
+      <c r="C21" t="n">
+        <v>791.8724801378852</v>
+      </c>
       <c r="D21" t="n">
         <v>4.308e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>88.81700000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>808.0437844623435</v>
       </c>
       <c r="D22" t="n">
         <v>4.30646e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>222.272</v>
       </c>
+      <c r="C2" t="n">
+        <v>2507.379003428469</v>
+      </c>
       <c r="D2" t="n">
         <v>4.48386e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>146.141</v>
       </c>
+      <c r="C3" t="n">
+        <v>885.2646513601907</v>
+      </c>
       <c r="D3" t="n">
         <v>4.55766e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>134.244</v>
       </c>
+      <c r="C4" t="n">
+        <v>813.0899474771742</v>
+      </c>
       <c r="D4" t="n">
         <v>4.49985e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>128.718</v>
       </c>
+      <c r="C5" t="n">
+        <v>804.2010713132283</v>
+      </c>
       <c r="D5" t="n">
         <v>4.44787e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>124.217</v>
       </c>
+      <c r="C6" t="n">
+        <v>828.7572684136031</v>
+      </c>
       <c r="D6" t="n">
         <v>4.40734e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>118.112</v>
       </c>
+      <c r="C7" t="n">
+        <v>787.2667825626219</v>
+      </c>
       <c r="D7" t="n">
         <v>4.3773e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>114.285</v>
       </c>
+      <c r="C8" t="n">
+        <v>807.9340787774646</v>
+      </c>
       <c r="D8" t="n">
         <v>4.35741e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>112.262</v>
       </c>
+      <c r="C9" t="n">
+        <v>827.4264766120192</v>
+      </c>
       <c r="D9" t="n">
         <v>4.34237e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>108.089</v>
       </c>
+      <c r="C10" t="n">
+        <v>827.0689323487677</v>
+      </c>
       <c r="D10" t="n">
         <v>4.33108e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>104.666</v>
+      </c>
+      <c r="C11" t="n">
+        <v>801.3653004231917</v>
       </c>
       <c r="D11" t="n">
         <v>4.32166e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -565,7 +565,7 @@
         <v>169.7359999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>981.5706652040282</v>
+        <v>364.2112549344725</v>
       </c>
       <c r="D2" t="n">
         <v>4.06231e-07</v>
@@ -598,16 +598,13 @@
         <v>-6186.824596413466</v>
       </c>
       <c r="Y2" t="n">
-        <v>519.5588140749594</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>413292553.9670471</v>
+        <v>229.3937072519961</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.846606468641e-06</v>
+        <v>9.031504096997553e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7726976832521258</v>
+        <v>0.8717949186827524</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>156.4959999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>822.716150832833</v>
+        <v>395.5816318211977</v>
       </c>
       <c r="D3" t="n">
         <v>4.01658e-07</v>
@@ -651,16 +648,13 @@
         <v>-7254.536331230087</v>
       </c>
       <c r="Y3" t="n">
-        <v>515.1447530719911</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>76340363.52911051</v>
+        <v>187.0791195007957</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.320704692016398e-06</v>
+        <v>8.371585621246313e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8206223692429329</v>
+        <v>0.864269905578789</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>150.422</v>
       </c>
       <c r="C4" t="n">
-        <v>819.4845709285679</v>
+        <v>351.1845691693365</v>
       </c>
       <c r="D4" t="n">
         <v>4.01002e-07</v>
@@ -704,16 +698,13 @@
         <v>-7341.728118451605</v>
       </c>
       <c r="Y4" t="n">
-        <v>509.7921866305265</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>36670084.60525571</v>
+        <v>224.6848893730291</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.208039586293898e-06</v>
+        <v>9.504994497915016e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8336700133681956</v>
+        <v>0.8709549973536931</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>149.673</v>
       </c>
       <c r="C5" t="n">
-        <v>945.0494002199925</v>
+        <v>329.0105373319811</v>
       </c>
       <c r="D5" t="n">
         <v>4.00951e-07</v>
@@ -757,16 +748,13 @@
         <v>-7705.298839750636</v>
       </c>
       <c r="Y5" t="n">
-        <v>500.2904901021955</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>382593169.5692241</v>
+        <v>230.0721543921444</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.124365288833633e-06</v>
+        <v>7.555984983706565e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8444167437723781</v>
+        <v>0.8919291419427892</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>132.994</v>
       </c>
       <c r="C6" t="n">
-        <v>883.3223279441712</v>
+        <v>132.994</v>
       </c>
       <c r="D6" t="n">
         <v>4.03341e-07</v>
@@ -809,11 +797,10 @@
       <c r="X6" t="n">
         <v>-7311.638077076997</v>
       </c>
-      <c r="Y6" t="n">
-        <v>486.6667719982777</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>125436262.6919927</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.024358980873656e-06</v>
@@ -830,7 +817,7 @@
         <v>123.899</v>
       </c>
       <c r="C7" t="n">
-        <v>870.7837497321913</v>
+        <v>297.1648673910337</v>
       </c>
       <c r="D7" t="n">
         <v>4.04904e-07</v>
@@ -863,16 +850,13 @@
         <v>-7322.592353732044</v>
       </c>
       <c r="Y7" t="n">
-        <v>476.2120706421102</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>89002016.8540733</v>
+        <v>232.6428394611358</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.652224676637845e-07</v>
+        <v>7.928241143695421e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8689490814493078</v>
+        <v>0.8981904103475515</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +867,7 @@
         <v>115.547</v>
       </c>
       <c r="C8" t="n">
-        <v>834.47766586666</v>
+        <v>289.137117022687</v>
       </c>
       <c r="D8" t="n">
         <v>4.0578e-07</v>
@@ -916,16 +900,13 @@
         <v>-7129.047920876661</v>
       </c>
       <c r="Y8" t="n">
-        <v>467.7221137386111</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>55643978.7912456</v>
+        <v>231.0015206261056</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.230098307439331e-07</v>
+        <v>8.045616226278231e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.875998154022779</v>
+        <v>0.9001906803416688</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +917,7 @@
         <v>110.194</v>
       </c>
       <c r="C9" t="n">
-        <v>829.2698817281006</v>
+        <v>282.5744634456573</v>
       </c>
       <c r="D9" t="n">
         <v>4.06198e-07</v>
@@ -969,16 +950,13 @@
         <v>-7228.637771056801</v>
       </c>
       <c r="Y9" t="n">
-        <v>460.9081317632145</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>27752247.97604188</v>
+        <v>229.0601806834662</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.916688351433397e-07</v>
+        <v>7.969698958458928e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8813696414110527</v>
+        <v>0.9024693461346858</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +967,7 @@
         <v>106.366</v>
       </c>
       <c r="C10" t="n">
-        <v>832.2576683994727</v>
+        <v>106.366</v>
       </c>
       <c r="D10" t="n">
         <v>4.06765e-07</v>
@@ -1021,11 +999,10 @@
       <c r="X10" t="n">
         <v>-7197.511933054325</v>
       </c>
-      <c r="Y10" t="n">
-        <v>455.3187362866913</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>130385447.7159736</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>8.686734850159351e-07</v>
@@ -1042,7 +1019,7 @@
         <v>103.319</v>
       </c>
       <c r="C11" t="n">
-        <v>833.9643613612189</v>
+        <v>272.3211415138931</v>
       </c>
       <c r="D11" t="n">
         <v>4.06819e-07</v>
@@ -1075,16 +1052,13 @@
         <v>-7299.499636574808</v>
       </c>
       <c r="Y11" t="n">
-        <v>450.4767903568224</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>57381590.60732438</v>
+        <v>226.7421637421469</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.491878219584032e-07</v>
+        <v>7.828221238721891e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8889358848696474</v>
+        <v>0.9069906276646911</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1215,7 @@
         <v>146.6200000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1158.245178916465</v>
+        <v>314.2568388365221</v>
       </c>
       <c r="D2" t="n">
         <v>4.38136e-07</v>
@@ -1274,16 +1248,13 @@
         <v>-6742.022109887177</v>
       </c>
       <c r="Y2" t="n">
-        <v>489.9742321541311</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>148118181.4788225</v>
+        <v>234.0325626680608</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.478231451742328e-06</v>
+        <v>8.323235930374676e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8172474898596364</v>
+        <v>0.8876035355395223</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1265,7 @@
         <v>123.864</v>
       </c>
       <c r="C3" t="n">
-        <v>811.5048114149108</v>
+        <v>533.8118161058592</v>
       </c>
       <c r="D3" t="n">
         <v>4.33907e-07</v>
@@ -1327,16 +1298,13 @@
         <v>-6812.802726634773</v>
       </c>
       <c r="Y3" t="n">
-        <v>480.2581810792708</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>38935196.01490787</v>
+        <v>0.01638926007336614</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.174355328937243e-06</v>
+        <v>4.801403823978965e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8501281648784971</v>
+        <v>0.850433925601586</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1315,7 @@
         <v>120.127</v>
       </c>
       <c r="C4" t="n">
-        <v>821.0922197712887</v>
+        <v>528.2278780864972</v>
       </c>
       <c r="D4" t="n">
         <v>4.31461e-07</v>
@@ -1380,16 +1348,13 @@
         <v>-7195.355208348639</v>
       </c>
       <c r="Y4" t="n">
-        <v>475.2972455033754</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>53640759.67525764</v>
+        <v>9.622616108570486e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.094773477069725e-06</v>
+        <v>4.982631094678598e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8597889939004243</v>
+        <v>0.8485983529373659</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1365,7 @@
         <v>115.028</v>
       </c>
       <c r="C5" t="n">
-        <v>797.0056871579822</v>
+        <v>520.8981410150786</v>
       </c>
       <c r="D5" t="n">
         <v>4.29532e-07</v>
@@ -1433,16 +1398,13 @@
         <v>-7129.177219382758</v>
       </c>
       <c r="Y5" t="n">
-        <v>470.9425137897255</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>44322862.68661626</v>
+        <v>0.2745440423345202</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.045463250749225e-06</v>
+        <v>4.628802977182604e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8660217394259915</v>
+        <v>0.8543474552232253</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1415,7 @@
         <v>111.7569999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>775.8691131003998</v>
+        <v>111.7569999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.28319e-07</v>
@@ -1485,11 +1447,10 @@
       <c r="X6" t="n">
         <v>-7093.682694217379</v>
       </c>
-      <c r="Y6" t="n">
-        <v>466.432824560886</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>82130829.68119729</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.008757036480951e-06</v>
@@ -1506,7 +1467,7 @@
         <v>110.511</v>
       </c>
       <c r="C7" t="n">
-        <v>830.5936162708834</v>
+        <v>289.1985396816502</v>
       </c>
       <c r="D7" t="n">
         <v>4.27434e-07</v>
@@ -1539,16 +1500,13 @@
         <v>-7453.784650128228</v>
       </c>
       <c r="Y7" t="n">
-        <v>461.8549488648044</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>56724908.32590564</v>
+        <v>225.5552303855345</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.76414534436509e-07</v>
+        <v>9.79694069501007e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8755254932747133</v>
+        <v>0.8849623840706675</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1517,7 @@
         <v>105.834</v>
       </c>
       <c r="C8" t="n">
-        <v>786.7488257689147</v>
+        <v>105.834</v>
       </c>
       <c r="D8" t="n">
         <v>4.26567e-07</v>
@@ -1591,11 +1549,10 @@
       <c r="X8" t="n">
         <v>-7223.820233961746</v>
       </c>
-      <c r="Y8" t="n">
-        <v>457.3615626041556</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>67801734.22047524</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>9.486780199241122e-07</v>
@@ -1612,7 +1569,7 @@
         <v>104.54</v>
       </c>
       <c r="C9" t="n">
-        <v>830.9442347685457</v>
+        <v>285.8635812609467</v>
       </c>
       <c r="D9" t="n">
         <v>4.25913e-07</v>
@@ -1645,16 +1602,13 @@
         <v>-7406.362743820021</v>
       </c>
       <c r="Y9" t="n">
-        <v>453.2546206910977</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>503463074.8002728</v>
+        <v>217.9728425607474</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.275650692967625e-07</v>
+        <v>8.970690356703056e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8827012141856697</v>
+        <v>0.8910703833751373</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1619,7 @@
         <v>101.923</v>
       </c>
       <c r="C10" t="n">
-        <v>821.234691593073</v>
+        <v>275.4054760796296</v>
       </c>
       <c r="D10" t="n">
         <v>4.25449e-07</v>
@@ -1698,16 +1652,13 @@
         <v>-7384.207958212489</v>
       </c>
       <c r="Y10" t="n">
-        <v>449.4920261038993</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>367980904.6520852</v>
+        <v>223.2820987312359</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.080503930994159e-07</v>
+        <v>8.904874048937905e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8857282762463824</v>
+        <v>0.895689753441502</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1669,7 @@
         <v>101.522</v>
       </c>
       <c r="C11" t="n">
-        <v>865.115266037779</v>
+        <v>271.400437223888</v>
       </c>
       <c r="D11" t="n">
         <v>4.25006e-07</v>
@@ -1751,16 +1702,13 @@
         <v>-7641.013345132657</v>
       </c>
       <c r="Y11" t="n">
-        <v>445.8780580103834</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>141980293.9109289</v>
+        <v>221.9531331793922</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.895668155853722e-07</v>
+        <v>8.608415054779085e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8886539260912504</v>
+        <v>0.8986785885903288</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1719,7 @@
         <v>97.41800000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>826.9515630031428</v>
+        <v>267.0949543201838</v>
       </c>
       <c r="D12" t="n">
         <v>4.24651e-07</v>
@@ -1804,16 +1752,13 @@
         <v>-7422.646926486967</v>
       </c>
       <c r="Y12" t="n">
-        <v>442.3503984287934</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>112240319.493892</v>
+        <v>222.5906539213925</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.764206311982184e-07</v>
+        <v>8.557156825838817e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8907696604704239</v>
+        <v>0.9011508663721418</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1769,7 @@
         <v>95.50299999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>801.4972287892305</v>
+        <v>259.3478641977206</v>
       </c>
       <c r="D13" t="n">
         <v>4.24329e-07</v>
@@ -1857,16 +1802,13 @@
         <v>-7320.492460151338</v>
       </c>
       <c r="Y13" t="n">
-        <v>438.9069988842543</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>26001814.29875525</v>
+        <v>225.4210627240493</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.634925066014833e-07</v>
+        <v>8.292807313863395e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8928959349140891</v>
+        <v>0.9052495061995293</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1819,7 @@
         <v>94.517</v>
       </c>
       <c r="C14" t="n">
-        <v>828.6120530606524</v>
+        <v>267.6247205735128</v>
       </c>
       <c r="D14" t="n">
         <v>4.24097e-07</v>
@@ -1910,16 +1852,13 @@
         <v>-7367.309836368556</v>
       </c>
       <c r="Y14" t="n">
-        <v>435.5607166733957</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>68972214.1317673</v>
+        <v>214.5384497505463</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.508675645135113e-07</v>
+        <v>8.477831193827511e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8950116281357834</v>
+        <v>0.9004007651282627</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1869,7 @@
         <v>91.726</v>
       </c>
       <c r="C15" t="n">
-        <v>788.6669762570326</v>
+        <v>255.4002337141713</v>
       </c>
       <c r="D15" t="n">
         <v>4.24007e-07</v>
@@ -1963,16 +1902,13 @@
         <v>-7193.465923212082</v>
       </c>
       <c r="Y15" t="n">
-        <v>432.1663647990239</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>355937089.6774742</v>
+        <v>222.5123319610902</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.401976279531202e-07</v>
+        <v>8.514621727993899e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8968687594459273</v>
+        <v>0.9058720215727988</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1919,7 @@
         <v>90.57299999999998</v>
       </c>
       <c r="C16" t="n">
-        <v>789.3153687551186</v>
+        <v>253.470619480466</v>
       </c>
       <c r="D16" t="n">
         <v>4.23705e-07</v>
@@ -2016,16 +1952,13 @@
         <v>-7289.452757198575</v>
       </c>
       <c r="Y16" t="n">
-        <v>428.8040168914721</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>352665882.4857401</v>
+        <v>221.1311204448838</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.296606311151344e-07</v>
+        <v>8.883878026666471e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8986614520891326</v>
+        <v>0.9033988720260029</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1969,7 @@
         <v>88.90000000000003</v>
       </c>
       <c r="C17" t="n">
-        <v>793.9836823664394</v>
+        <v>88.90000000000003</v>
       </c>
       <c r="D17" t="n">
         <v>4.23491e-07</v>
@@ -2068,11 +2001,10 @@
       <c r="X17" t="n">
         <v>-7233.477705375245</v>
       </c>
-      <c r="Y17" t="n">
-        <v>425.5181398561159</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>233348024.7402682</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>8.20844195289727e-07</v>
@@ -2089,7 +2021,7 @@
         <v>87.82900000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>829.3441563180164</v>
+        <v>247.5388610405294</v>
       </c>
       <c r="D18" t="n">
         <v>4.23312e-07</v>
@@ -2122,16 +2054,13 @@
         <v>-7399.724136359128</v>
       </c>
       <c r="Y18" t="n">
-        <v>422.2054309710713</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>173599336.1105402</v>
+        <v>218.1513898727368</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.111308803992081e-07</v>
+        <v>8.070466848166446e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9019044205140203</v>
+        <v>0.9116378652486057</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2071,7 @@
         <v>84.20699999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>779.1464909566723</v>
+        <v>84.20699999999999</v>
       </c>
       <c r="D19" t="n">
         <v>4.23191e-07</v>
@@ -2174,11 +2103,10 @@
       <c r="X19" t="n">
         <v>-7065.125182309032</v>
       </c>
-      <c r="Y19" t="n">
-        <v>418.8913705290404</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>343891492.0842941</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>8.030844396002918e-07</v>
@@ -2195,7 +2123,7 @@
         <v>85.12200000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>829.5302802413765</v>
+        <v>258.6404169473366</v>
       </c>
       <c r="D20" t="n">
         <v>4.23159e-07</v>
@@ -2228,16 +2156,13 @@
         <v>-7358.892142885788</v>
       </c>
       <c r="Y20" t="n">
-        <v>415.6398467546637</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>170711867.1082714</v>
+        <v>197.1904335799699</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.949215883028286e-07</v>
+        <v>6.453627447572227e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9048873269211634</v>
+        <v>0.9183915326276507</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2173,7 @@
         <v>84.25</v>
       </c>
       <c r="C21" t="n">
-        <v>850.7790718925049</v>
+        <v>84.25</v>
       </c>
       <c r="D21" t="n">
         <v>4.2307e-07</v>
@@ -2280,11 +2205,10 @@
       <c r="X21" t="n">
         <v>-7330.866382177048</v>
       </c>
-      <c r="Y21" t="n">
-        <v>412.3606945871971</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>225638062.5626982</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>7.856700057113214e-07</v>
@@ -2301,7 +2225,7 @@
         <v>80.15899999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>782.6063177261946</v>
+        <v>246.7918239421191</v>
       </c>
       <c r="D22" t="n">
         <v>4.23035e-07</v>
@@ -2334,16 +2258,13 @@
         <v>-6898.664298580803</v>
       </c>
       <c r="Y22" t="n">
-        <v>409.0709526386851</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>223706718.6679012</v>
+        <v>201.7655946533369</v>
       </c>
       <c r="AA22" t="n">
-        <v>7.80187494533801e-07</v>
+        <v>6.545770384207148e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9076586219078739</v>
+        <v>0.9232031941307086</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2421,7 @@
         <v>159.521</v>
       </c>
       <c r="C2" t="n">
-        <v>1337.339854305</v>
+        <v>325.6009098334775</v>
       </c>
       <c r="D2" t="n">
         <v>4.04393e-07</v>
@@ -2533,16 +2454,13 @@
         <v>-7280.475695272173</v>
       </c>
       <c r="Y2" t="n">
-        <v>499.1176390781113</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>243775353.7656611</v>
+        <v>231.6062229443673</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.249454044055751e-06</v>
+        <v>6.578177819430088e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8299942220424288</v>
+        <v>0.9021870045127223</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2471,7 @@
         <v>129.987</v>
       </c>
       <c r="C3" t="n">
-        <v>854.7467510002933</v>
+        <v>129.987</v>
       </c>
       <c r="D3" t="n">
         <v>4.07706e-07</v>
@@ -2585,11 +2503,10 @@
       <c r="X3" t="n">
         <v>-7375.903936424929</v>
       </c>
-      <c r="Y3" t="n">
-        <v>486.2898482420558</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>200647960.2769898</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.035668630598142e-06</v>
@@ -2606,7 +2523,7 @@
         <v>121.414</v>
       </c>
       <c r="C4" t="n">
-        <v>798.2790782775323</v>
+        <v>534.9936278491897</v>
       </c>
       <c r="D4" t="n">
         <v>4.07966e-07</v>
@@ -2639,16 +2556,13 @@
         <v>-7260.903349333928</v>
       </c>
       <c r="Y4" t="n">
-        <v>481.4264374623174</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>70490596.89608534</v>
+        <v>0.4720572073604776</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.807443637112244e-07</v>
+        <v>4.729085915958695e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8676408994231256</v>
+        <v>0.8529921870937395</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2573,7 @@
         <v>118.814</v>
       </c>
       <c r="C5" t="n">
-        <v>800.1260177742972</v>
+        <v>312.5414057182386</v>
       </c>
       <c r="D5" t="n">
         <v>4.07754e-07</v>
@@ -2692,16 +2606,13 @@
         <v>-7415.660134759206</v>
       </c>
       <c r="Y5" t="n">
-        <v>477.3102502881576</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>49194235.607234</v>
+        <v>220.2587520809274</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.503341995736951e-07</v>
+        <v>8.962210372799445e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8723129801885814</v>
+        <v>0.8837895416313755</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2623,7 @@
         <v>116.859</v>
       </c>
       <c r="C6" t="n">
-        <v>817.0285687061125</v>
+        <v>306.4382752681356</v>
       </c>
       <c r="D6" t="n">
         <v>4.07555e-07</v>
@@ -2745,16 +2656,13 @@
         <v>-7589.47571592912</v>
       </c>
       <c r="Y6" t="n">
-        <v>472.9588709053863</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>66754175.71743279</v>
+        <v>220.6091950208913</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.261465598722945e-07</v>
+        <v>8.733939115778584e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8761298590883635</v>
+        <v>0.8872839315914437</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2673,7 @@
         <v>115.15</v>
       </c>
       <c r="C7" t="n">
-        <v>847.4801478668043</v>
+        <v>296.2089882461019</v>
       </c>
       <c r="D7" t="n">
         <v>4.07626e-07</v>
@@ -2798,16 +2706,13 @@
         <v>-7732.434431159663</v>
       </c>
       <c r="Y7" t="n">
-        <v>468.4717608769296</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>40467841.915176</v>
+        <v>227.2296580417415</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.03637099704054e-07</v>
+        <v>9.86083509440035e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8798555448635064</v>
+        <v>0.8834791968393523</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2723,7 @@
         <v>111.708</v>
       </c>
       <c r="C8" t="n">
-        <v>828.6847737747993</v>
+        <v>292.4083784043376</v>
       </c>
       <c r="D8" t="n">
         <v>4.07525e-07</v>
@@ -2851,16 +2756,13 @@
         <v>-7633.516383021247</v>
       </c>
       <c r="Y8" t="n">
-        <v>464.1141487701912</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>47936162.10497496</v>
+        <v>223.9927255231791</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.850825373548373e-07</v>
+        <v>8.623779891050405e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8829553946364356</v>
+        <v>0.8933474480039763</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2773,7 @@
         <v>111.664</v>
       </c>
       <c r="C9" t="n">
-        <v>903.5157236565656</v>
+        <v>111.664</v>
       </c>
       <c r="D9" t="n">
         <v>4.07573e-07</v>
@@ -2903,11 +2805,10 @@
       <c r="X9" t="n">
         <v>-8116.589163396268</v>
       </c>
-      <c r="Y9" t="n">
-        <v>460.0229431340741</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>89417581.47126876</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>8.662062897082133e-07</v>
@@ -2924,7 +2825,7 @@
         <v>106.804</v>
       </c>
       <c r="C10" t="n">
-        <v>853.0322863670558</v>
+        <v>279.2182448396852</v>
       </c>
       <c r="D10" t="n">
         <v>4.07423e-07</v>
@@ -2957,16 +2858,13 @@
         <v>-7777.134174220517</v>
       </c>
       <c r="Y10" t="n">
-        <v>456.2402362992059</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>486361881.5455183</v>
+        <v>227.6460155697613</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.539360900901032e-07</v>
+        <v>8.619929141998738e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8883164337014405</v>
+        <v>0.8982629816877998</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2875,7 @@
         <v>102.842</v>
       </c>
       <c r="C11" t="n">
-        <v>810.1229125230125</v>
+        <v>274.756074170621</v>
       </c>
       <c r="D11" t="n">
         <v>4.07522e-07</v>
@@ -3010,16 +2908,13 @@
         <v>-7507.112775363232</v>
       </c>
       <c r="Y11" t="n">
-        <v>452.6263035733331</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>47796829.53332189</v>
+        <v>226.9385201267122</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.42081609816923e-07</v>
+        <v>8.320489474818235e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8904541333673119</v>
+        <v>0.9011136110729741</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2925,7 @@
         <v>100.172</v>
       </c>
       <c r="C12" t="n">
-        <v>793.8777669840641</v>
+        <v>100.172</v>
       </c>
       <c r="D12" t="n">
         <v>4.07495e-07</v>
@@ -3062,11 +2957,10 @@
       <c r="X12" t="n">
         <v>-7342.240245234433</v>
       </c>
-      <c r="Y12" t="n">
-        <v>449.0300279010361</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>86506340.2766064</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>8.325347789270932e-07</v>
@@ -3083,7 +2977,7 @@
         <v>100.331</v>
       </c>
       <c r="C13" t="n">
-        <v>827.2585291248532</v>
+        <v>267.2192470483694</v>
       </c>
       <c r="D13" t="n">
         <v>4.07495e-07</v>
@@ -3116,16 +3010,13 @@
         <v>-7606.439003292698</v>
       </c>
       <c r="Y13" t="n">
-        <v>445.5425135130176</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>495200450.8970287</v>
+        <v>225.7508001803847</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.20693032661026e-07</v>
+        <v>7.859900496764586e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8943121180026801</v>
+        <v>0.9079681505116317</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3027,7 @@
         <v>99.54599999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>886.4582365840547</v>
+        <v>265.4799761118043</v>
       </c>
       <c r="D14" t="n">
         <v>4.07561e-07</v>
@@ -3169,16 +3060,13 @@
         <v>-7787.121506335484</v>
       </c>
       <c r="Y14" t="n">
-        <v>442.1132882423688</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>41647265.46886921</v>
+        <v>224.9690262276742</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.127781237429013e-07</v>
+        <v>8.821372827317297e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8958032447841887</v>
+        <v>0.9007000714159904</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3077,7 @@
         <v>97.00899999999996</v>
       </c>
       <c r="C15" t="n">
-        <v>834.8886958211322</v>
+        <v>97.00899999999996</v>
       </c>
       <c r="D15" t="n">
         <v>4.07588e-07</v>
@@ -3221,11 +3109,10 @@
       <c r="X15" t="n">
         <v>-7659.417691555616</v>
       </c>
-      <c r="Y15" t="n">
-        <v>438.7846401522244</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>241283099.4159756</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>8.022724761816673e-07</v>
@@ -3242,7 +3129,7 @@
         <v>94.45400000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>815.5418746674343</v>
+        <v>94.45400000000001</v>
       </c>
       <c r="D16" t="n">
         <v>4.0782e-07</v>
@@ -3274,11 +3161,10 @@
       <c r="X16" t="n">
         <v>-7450.193141842873</v>
       </c>
-      <c r="Y16" t="n">
-        <v>435.334903354623</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>478121641.4895244</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>7.947759096426171e-07</v>
@@ -3295,7 +3181,7 @@
         <v>93.88200000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>848.4860392189031</v>
+        <v>93.88200000000001</v>
       </c>
       <c r="D17" t="n">
         <v>4.0786e-07</v>
@@ -3327,11 +3213,10 @@
       <c r="X17" t="n">
         <v>-7618.619376268224</v>
       </c>
-      <c r="Y17" t="n">
-        <v>431.8980721291372</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>355786911.2603794</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>7.885532963749957e-07</v>
@@ -3348,7 +3233,7 @@
         <v>91.95400000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>835.8831773801375</v>
+        <v>263.1183681036536</v>
       </c>
       <c r="D18" t="n">
         <v>4.07895e-07</v>
@@ -3381,16 +3266,13 @@
         <v>-7518.765585391766</v>
       </c>
       <c r="Y18" t="n">
-        <v>428.4997763259188</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>176168883.5768803</v>
+        <v>208.4739769470261</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.795747484222539e-07</v>
+        <v>6.723417004400459e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9021921772586892</v>
+        <v>0.9168827609828701</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3283,7 @@
         <v>88.858</v>
       </c>
       <c r="C19" t="n">
-        <v>792.808727316926</v>
+        <v>270.0196701454669</v>
       </c>
       <c r="D19" t="n">
         <v>4.08034e-07</v>
@@ -3434,16 +3316,13 @@
         <v>-7255.863403884056</v>
       </c>
       <c r="Y19" t="n">
-        <v>425.087672523999</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>349205414.8950536</v>
+        <v>197.661798330679</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.735203486760573e-07</v>
+        <v>6.380215866766665e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9034251029183138</v>
+        <v>0.9171931632547942</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3333,7 @@
         <v>87.77999999999997</v>
       </c>
       <c r="C20" t="n">
-        <v>828.6739617257106</v>
+        <v>265.4084430936342</v>
       </c>
       <c r="D20" t="n">
         <v>4.08109e-07</v>
@@ -3487,16 +3366,13 @@
         <v>-7405.167210656181</v>
       </c>
       <c r="Y20" t="n">
-        <v>421.7213660033631</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>173240697.9551121</v>
+        <v>198.2163788862036</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.651207285496407e-07</v>
+        <v>6.31373561593111e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9050834176348366</v>
+        <v>0.9196027555673992</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3383,7 @@
         <v>86.488</v>
       </c>
       <c r="C21" t="n">
-        <v>830.2629417737</v>
+        <v>86.488</v>
       </c>
       <c r="D21" t="n">
         <v>4.08281e-07</v>
@@ -3539,11 +3415,10 @@
       <c r="X21" t="n">
         <v>-7349.342759269707</v>
       </c>
-      <c r="Y21" t="n">
-        <v>418.3605202623948</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>114614647.8682878</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>7.594625391339403e-07</v>
@@ -3560,7 +3435,7 @@
         <v>83.93599999999998</v>
       </c>
       <c r="C22" t="n">
-        <v>785.8788885979884</v>
+        <v>254.4446013393094</v>
       </c>
       <c r="D22" t="n">
         <v>4.0839e-07</v>
@@ -3593,16 +3468,13 @@
         <v>-7104.662817970229</v>
       </c>
       <c r="Y22" t="n">
-        <v>415.0494363389573</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>140184727.2398659</v>
+        <v>200.7223586094783</v>
       </c>
       <c r="AA22" t="n">
-        <v>7.530284246436029e-07</v>
+        <v>6.217059593453861e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9075943564179231</v>
+        <v>0.9245249990532178</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3631,7 @@
         <v>262.504</v>
       </c>
       <c r="C2" t="n">
-        <v>2132.931072601401</v>
+        <v>386.9688380059437</v>
       </c>
       <c r="D2" t="n">
         <v>4.10809e-07</v>
@@ -3792,16 +3664,13 @@
         <v>-5664.475697975076</v>
       </c>
       <c r="Y2" t="n">
-        <v>484.9861151643555</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>332736872.0083891</v>
+        <v>248.4034555975236</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.29287172787754e-05</v>
+        <v>4.152985457942313e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.9175395601635062</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3681,7 @@
         <v>174.836</v>
       </c>
       <c r="C3" t="n">
-        <v>962.0507560773692</v>
+        <v>372.5860701230871</v>
       </c>
       <c r="D3" t="n">
         <v>4.27465e-07</v>
@@ -3845,16 +3714,13 @@
         <v>-6235.016696184286</v>
       </c>
       <c r="Y3" t="n">
-        <v>521.3350682481924</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>400990891.9343027</v>
+        <v>230.2433579451874</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.677452522839929e-06</v>
+        <v>9.910100455766197e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7256973211863861</v>
+        <v>0.8626683297482547</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3731,7 @@
         <v>156.252</v>
       </c>
       <c r="C4" t="n">
-        <v>844.7016828586424</v>
+        <v>584.9956989095737</v>
       </c>
       <c r="D4" t="n">
         <v>4.26496e-07</v>
@@ -3898,16 +3764,13 @@
         <v>-6457.222985885509</v>
       </c>
       <c r="Y4" t="n">
-        <v>517.3713649115799</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>338453846.786369</v>
+        <v>0.0437515989737394</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.817158349230833e-06</v>
+        <v>5.080840049843393e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7823188836726278</v>
+        <v>0.8416957197618008</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3781,7 @@
         <v>149.34</v>
       </c>
       <c r="C5" t="n">
-        <v>826.1776097656403</v>
+        <v>579.75375036546</v>
       </c>
       <c r="D5" t="n">
         <v>4.24367e-07</v>
@@ -3951,16 +3814,13 @@
         <v>-6711.919872729918</v>
       </c>
       <c r="Y5" t="n">
-        <v>513.1693295433734</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>71587039.11022817</v>
+        <v>0.2617102378333245</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.551584797607573e-06</v>
+        <v>5.630324872672207e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8050175307555576</v>
+        <v>0.8359862383246385</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3831,7 @@
         <v>145.3699999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>835.6094439566376</v>
+        <v>368.0117228045702</v>
       </c>
       <c r="D6" t="n">
         <v>4.22243e-07</v>
@@ -4004,16 +3864,13 @@
         <v>-6971.727991215119</v>
       </c>
       <c r="Y6" t="n">
-        <v>508.7904941824024</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>53603483.59283476</v>
+        <v>208.6151632905602</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.403257078285212e-06</v>
+        <v>1.043657091761073e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.819241634951197</v>
+        <v>0.8575425553072402</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3881,7 @@
         <v>139.777</v>
       </c>
       <c r="C7" t="n">
-        <v>808.9888000089759</v>
+        <v>565.1003094788185</v>
       </c>
       <c r="D7" t="n">
         <v>4.20916e-07</v>
@@ -4057,16 +3914,13 @@
         <v>-6978.950978077645</v>
       </c>
       <c r="Y7" t="n">
-        <v>504.1404758598058</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>127015839.6190417</v>
+        <v>0.8114549233465586</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.2989293958207e-06</v>
+        <v>5.316816493977956e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8303017056326936</v>
+        <v>0.8413367542271358</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3931,7 @@
         <v>138.743</v>
       </c>
       <c r="C8" t="n">
-        <v>848.1023659697598</v>
+        <v>558.0674052708374</v>
       </c>
       <c r="D8" t="n">
         <v>4.19867e-07</v>
@@ -4110,16 +3964,13 @@
         <v>-7388.882746748612</v>
       </c>
       <c r="Y8" t="n">
-        <v>499.4335336193562</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>24540362.74458681</v>
+        <v>1.100126105891328</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.223309426751137e-06</v>
+        <v>5.163952980466266e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8389065445825524</v>
+        <v>0.8440743182746762</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3981,7 @@
         <v>132.643</v>
       </c>
       <c r="C9" t="n">
-        <v>818.8066573873742</v>
+        <v>553.1205607003441</v>
       </c>
       <c r="D9" t="n">
         <v>4.18922e-07</v>
@@ -4163,16 +4014,13 @@
         <v>-7186.108315126336</v>
       </c>
       <c r="Y9" t="n">
-        <v>494.6814522457348</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>240916987.3990885</v>
+        <v>0.1989601124261439</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.162745934544996e-06</v>
+        <v>5.173947592612121e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.846174600581583</v>
+        <v>0.8443019662706216</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4031,7 @@
         <v>130.433</v>
       </c>
       <c r="C10" t="n">
-        <v>836.571136778088</v>
+        <v>545.4639979495945</v>
       </c>
       <c r="D10" t="n">
         <v>4.1818e-07</v>
@@ -4216,16 +4064,13 @@
         <v>-7332.145161253643</v>
       </c>
       <c r="Y10" t="n">
-        <v>489.836180994921</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>410904260.3103519</v>
+        <v>0.9365509847107479</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.116260850621299e-06</v>
+        <v>4.948620976432002e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8520377104751431</v>
+        <v>0.8482625710397395</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4081,7 @@
         <v>125.848</v>
       </c>
       <c r="C11" t="n">
-        <v>826.2260452992264</v>
+        <v>539.402080789784</v>
       </c>
       <c r="D11" t="n">
         <v>4.17697e-07</v>
@@ -4269,16 +4114,13 @@
         <v>-7347.820697820334</v>
       </c>
       <c r="Y11" t="n">
-        <v>485.1460599920371</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>60299381.14163633</v>
+        <v>0.8934497099086123</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.073682635026227e-06</v>
+        <v>4.878486683882288e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8576846166664608</v>
+        <v>0.8499009787466187</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4277,7 @@
         <v>154.8630000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1234.326845899763</v>
+        <v>317.4583765608153</v>
       </c>
       <c r="D2" t="n">
         <v>4.34957e-07</v>
@@ -4468,16 +4310,13 @@
         <v>-5851.072698290834</v>
       </c>
       <c r="Y2" t="n">
-        <v>490.6367201800968</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>444957475.7575544</v>
+        <v>234.1254134774562</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.789976648279128e-06</v>
+        <v>7.737237370337372e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7876958551000325</v>
+        <v>0.8912045397336189</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4327,7 @@
         <v>128.346</v>
       </c>
       <c r="C3" t="n">
-        <v>830.1836086532726</v>
+        <v>319.3992680277374</v>
       </c>
       <c r="D3" t="n">
         <v>4.32251e-07</v>
@@ -4521,16 +4360,13 @@
         <v>-6273.527778223771</v>
       </c>
       <c r="Y3" t="n">
-        <v>480.9967073330358</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>98211573.19599701</v>
+        <v>222.0966202434813</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.292418458022157e-06</v>
+        <v>1.036184181070506e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8352058649312752</v>
+        <v>0.8721675982328289</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4377,7 @@
         <v>125.253</v>
       </c>
       <c r="C4" t="n">
-        <v>855.0569320994252</v>
+        <v>309.4398771924821</v>
       </c>
       <c r="D4" t="n">
         <v>4.29211e-07</v>
@@ -4574,16 +4410,13 @@
         <v>-6896.834561365011</v>
       </c>
       <c r="Y4" t="n">
-        <v>476.5104644538858</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>174464456.9436574</v>
+        <v>225.71365692985</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.167616733782872e-06</v>
+        <v>1.034338286156373e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8493114793289552</v>
+        <v>0.8760555329039844</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4427,7 @@
         <v>119.668</v>
       </c>
       <c r="C5" t="n">
-        <v>800.4248962499717</v>
+        <v>119.668</v>
       </c>
       <c r="D5" t="n">
         <v>4.26899e-07</v>
@@ -4626,11 +4459,10 @@
       <c r="X5" t="n">
         <v>-6797.38766962644</v>
       </c>
-      <c r="Y5" t="n">
-        <v>472.7525593398541</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>118491567.6754503</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.097665810904654e-06</v>
@@ -4647,7 +4479,7 @@
         <v>118.0219999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>842.4896489340592</v>
+        <v>118.0219999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.25014e-07</v>
@@ -4679,11 +4511,10 @@
       <c r="X6" t="n">
         <v>-7126.489023836115</v>
       </c>
-      <c r="Y6" t="n">
-        <v>468.9819122443698</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>112812922.6847093</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.051812760341511e-06</v>
@@ -4700,7 +4531,7 @@
         <v>115.446</v>
       </c>
       <c r="C7" t="n">
-        <v>840.2349759294596</v>
+        <v>293.3082551300243</v>
       </c>
       <c r="D7" t="n">
         <v>4.23713e-07</v>
@@ -4733,16 +4564,13 @@
         <v>-7171.224210644265</v>
       </c>
       <c r="Y7" t="n">
-        <v>465.0790243736301</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>111156231.6956024</v>
+        <v>226.6384995919103</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.013681429750216e-06</v>
+        <v>9.977861528278126e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8685320003717431</v>
+        <v>0.883375170577083</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4581,7 @@
         <v>111.303</v>
       </c>
       <c r="C8" t="n">
-        <v>837.7744288333091</v>
+        <v>288.8545359745053</v>
       </c>
       <c r="D8" t="n">
         <v>4.22673e-07</v>
@@ -4786,16 +4614,13 @@
         <v>-7055.838377605582</v>
       </c>
       <c r="Y8" t="n">
-        <v>461.1516122042609</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>66260437.21048671</v>
+        <v>225.9589540910015</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.79331295351269e-07</v>
+        <v>9.85668279198644e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8733319569118753</v>
+        <v>0.8853771951470979</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4631,7 @@
         <v>108.67</v>
       </c>
       <c r="C9" t="n">
-        <v>810.3896600274452</v>
+        <v>108.67</v>
       </c>
       <c r="D9" t="n">
         <v>4.21853e-07</v>
@@ -4838,11 +4663,10 @@
       <c r="X9" t="n">
         <v>-7112.722165157036</v>
       </c>
-      <c r="Y9" t="n">
-        <v>457.3864809506157</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>55553887.17777497</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>9.541075920291812e-07</v>
@@ -4859,7 +4683,7 @@
         <v>108.903</v>
       </c>
       <c r="C10" t="n">
-        <v>862.3613416966576</v>
+        <v>278.4303502973506</v>
       </c>
       <c r="D10" t="n">
         <v>4.21175e-07</v>
@@ -4892,16 +4716,13 @@
         <v>-7403.041572670372</v>
       </c>
       <c r="Y10" t="n">
-        <v>453.7330725039115</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>27254715.81268415</v>
+        <v>226.0705584057281</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.329199084660932e-07</v>
+        <v>9.110087050379693e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8800895374504167</v>
+        <v>0.8937811389052788</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4733,7 @@
         <v>103.167</v>
       </c>
       <c r="C11" t="n">
-        <v>804.8266974216032</v>
+        <v>103.167</v>
       </c>
       <c r="D11" t="n">
         <v>4.20735e-07</v>
@@ -4944,11 +4765,10 @@
       <c r="X11" t="n">
         <v>-7029.460609951821</v>
       </c>
-      <c r="Y11" t="n">
-        <v>450.2221643621617</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>63839364.51118754</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>9.158146631407134e-07</v>
@@ -4965,7 +4785,7 @@
         <v>103.635</v>
       </c>
       <c r="C12" t="n">
-        <v>855.7287605040963</v>
+        <v>271.6801795045053</v>
       </c>
       <c r="D12" t="n">
         <v>4.20347e-07</v>
@@ -4998,16 +4818,13 @@
         <v>-7356.21618013666</v>
       </c>
       <c r="Y12" t="n">
-        <v>446.8388964258468</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>236340210.8547626</v>
+        <v>224.0767048259526</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.996273767565365e-07</v>
+        <v>8.784091944489551e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8852391797187512</v>
+        <v>0.8979126039812361</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4835,7 @@
         <v>101.796</v>
       </c>
       <c r="C13" t="n">
-        <v>847.4970056837491</v>
+        <v>101.796</v>
       </c>
       <c r="D13" t="n">
         <v>4.20011e-07</v>
@@ -5050,11 +4867,10 @@
       <c r="X13" t="n">
         <v>-7329.036117939046</v>
       </c>
-      <c r="Y13" t="n">
-        <v>443.5286139056063</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>104506479.3569433</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>8.846161540240556e-07</v>
@@ -5071,7 +4887,7 @@
         <v>99.78700000000003</v>
       </c>
       <c r="C14" t="n">
-        <v>842.8146477806347</v>
+        <v>99.78700000000003</v>
       </c>
       <c r="D14" t="n">
         <v>4.19676e-07</v>
@@ -5103,11 +4919,10 @@
       <c r="X14" t="n">
         <v>-7328.840189038013</v>
       </c>
-      <c r="Y14" t="n">
-        <v>440.2728386421616</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>48907273.27580757</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>8.702026283103438e-07</v>
@@ -5124,7 +4939,7 @@
         <v>96.41400000000004</v>
       </c>
       <c r="C15" t="n">
-        <v>801.2025420393586</v>
+        <v>261.8299441351565</v>
       </c>
       <c r="D15" t="n">
         <v>4.19397e-07</v>
@@ -5157,16 +4972,13 @@
         <v>-7005.441102406066</v>
       </c>
       <c r="Y15" t="n">
-        <v>436.9733621935648</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>37707447.05188376</v>
+        <v>222.177406553192</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.626656148130543e-07</v>
+        <v>8.18497827046614e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8912124570067083</v>
+        <v>0.9070416755312508</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4989,7 @@
         <v>96.06</v>
       </c>
       <c r="C16" t="n">
-        <v>825.6461295343061</v>
+        <v>258.8468213748537</v>
       </c>
       <c r="D16" t="n">
         <v>4.19329e-07</v>
@@ -5210,16 +5022,13 @@
         <v>-7291.197489787197</v>
       </c>
       <c r="Y16" t="n">
-        <v>433.802254192731</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>48255195.06780083</v>
+        <v>221.3022495325653</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.488422569119952e-07</v>
+        <v>8.021700132743762e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8935906829007343</v>
+        <v>0.9094638675352485</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5039,7 @@
         <v>93.17400000000004</v>
       </c>
       <c r="C17" t="n">
-        <v>785.4700475360258</v>
+        <v>93.17400000000004</v>
       </c>
       <c r="D17" t="n">
         <v>4.18997e-07</v>
@@ -5262,11 +5071,10 @@
       <c r="X17" t="n">
         <v>-7010.913950724082</v>
       </c>
-      <c r="Y17" t="n">
-        <v>430.589869034477</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>16593249.91813339</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>8.396386542920469e-07</v>
@@ -5283,7 +5091,7 @@
         <v>91.44099999999997</v>
       </c>
       <c r="C18" t="n">
-        <v>765.6399789000141</v>
+        <v>253.5612474868946</v>
       </c>
       <c r="D18" t="n">
         <v>4.18886e-07</v>
@@ -5316,16 +5124,13 @@
         <v>-6876.684018773698</v>
       </c>
       <c r="Y18" t="n">
-        <v>427.3854692308652</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>703133306.1587847</v>
+        <v>218.2646566896803</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.297869985299549e-07</v>
+        <v>7.670122560903506e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8968476481013549</v>
+        <v>0.9134384393870905</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5141,7 @@
         <v>90.58600000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>769.5267211469886</v>
+        <v>90.58600000000001</v>
       </c>
       <c r="D19" t="n">
         <v>4.18725e-07</v>
@@ -5368,11 +5173,10 @@
       <c r="X19" t="n">
         <v>-7012.96178817961</v>
       </c>
-      <c r="Y19" t="n">
-        <v>424.2195163582124</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>174618713.9645715</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>8.189301531234026e-07</v>
@@ -5389,7 +5193,7 @@
         <v>89.36499999999995</v>
       </c>
       <c r="C20" t="n">
-        <v>802.6775075602387</v>
+        <v>266.9691223087277</v>
       </c>
       <c r="D20" t="n">
         <v>4.18796e-07</v>
@@ -5422,16 +5226,13 @@
         <v>-7049.52408508412</v>
       </c>
       <c r="Y20" t="n">
-        <v>421.0071287354223</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>173122596.5523554</v>
+        <v>196.3718844314327</v>
       </c>
       <c r="AA20" t="n">
-        <v>8.120594659232375e-07</v>
+        <v>6.570874570739643e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9000478760096424</v>
+        <v>0.9158642223403541</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5243,7 @@
         <v>87.89699999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>801.9222450508177</v>
+        <v>260.7573679228944</v>
       </c>
       <c r="D21" t="n">
         <v>4.18724e-07</v>
@@ -5475,16 +5276,13 @@
         <v>-7043.293606001984</v>
       </c>
       <c r="Y21" t="n">
-        <v>417.8126408326631</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>343337304.2052764</v>
+        <v>199.288884347962</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.040902748043091e-07</v>
+        <v>6.919558796340987e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9015033507399853</v>
+        <v>0.9147467510310986</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5293,7 @@
         <v>88.505</v>
       </c>
       <c r="C22" t="n">
-        <v>857.5028549134241</v>
+        <v>255.6697198233371</v>
       </c>
       <c r="D22" t="n">
         <v>4.18656e-07</v>
@@ -5528,16 +5326,13 @@
         <v>-7317.219125309516</v>
       </c>
       <c r="Y22" t="n">
-        <v>414.5699333941683</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>170322252.8409989</v>
+        <v>199.7567329144671</v>
       </c>
       <c r="AA22" t="n">
-        <v>7.943590377711847e-07</v>
+        <v>6.507090418743232e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9033020411966273</v>
+        <v>0.9202557369779359</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5489,7 @@
         <v>249.226</v>
       </c>
       <c r="C2" t="n">
-        <v>1960.642146698272</v>
+        <v>380.4700614118278</v>
       </c>
       <c r="D2" t="n">
         <v>4.30617e-07</v>
@@ -5727,16 +5522,13 @@
         <v>-5573.693806484659</v>
       </c>
       <c r="Y2" t="n">
-        <v>479.2253385644894</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>472354131.9910227</v>
+        <v>244.6467974605519</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.352861052745718e-05</v>
+        <v>4.881209197017351e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.904635313788705</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5539,7 @@
         <v>170.275</v>
       </c>
       <c r="C3" t="n">
-        <v>924.4045478038105</v>
+        <v>591.439993695518</v>
       </c>
       <c r="D3" t="n">
         <v>4.45063e-07</v>
@@ -5780,16 +5572,13 @@
         <v>-5894.239021872533</v>
       </c>
       <c r="Y3" t="n">
-        <v>511.49299941495</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>902520402.7178111</v>
+        <v>0.04468848580871975</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.526782239979953e-06</v>
+        <v>4.828369282908809e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6919302999864283</v>
+        <v>0.8447708636212935</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5589,7 @@
         <v>155.854</v>
       </c>
       <c r="C4" t="n">
-        <v>849.885163958349</v>
+        <v>546.4698760691716</v>
       </c>
       <c r="D4" t="n">
         <v>4.43561e-07</v>
@@ -5833,16 +5622,13 @@
         <v>-6293.619681130627</v>
       </c>
       <c r="Y4" t="n">
-        <v>511.259118049216</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>367048545.7249072</v>
+        <v>32.44403396711391</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.181476508861705e-06</v>
+        <v>5.349500196421602e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7613140111214566</v>
+        <v>0.8469629565385348</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5639,7 @@
         <v>149.561</v>
       </c>
       <c r="C5" t="n">
-        <v>836.6921081328051</v>
+        <v>501.8708839871644</v>
       </c>
       <c r="D5" t="n">
         <v>4.40693e-07</v>
@@ -5886,16 +5672,13 @@
         <v>-6581.25142678913</v>
       </c>
       <c r="Y5" t="n">
-        <v>507.8293741020886</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>304339646.6292965</v>
+        <v>69.35087103516179</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.78223714246108e-06</v>
+        <v>5.790275856934541e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.79020552261438</v>
+        <v>0.852097135907128</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5689,7 @@
         <v>144.996</v>
       </c>
       <c r="C6" t="n">
-        <v>852.868629277738</v>
+        <v>566.6798151849074</v>
       </c>
       <c r="D6" t="n">
         <v>4.38016e-07</v>
@@ -5939,16 +5722,13 @@
         <v>-6871.507724383208</v>
       </c>
       <c r="Y6" t="n">
-        <v>503.5583085184324</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>31448815.66216073</v>
+        <v>0.4178695065384621</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.565254805349706e-06</v>
+        <v>5.463631814367484e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8085861289201479</v>
+        <v>0.8388579158868048</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5739,7 @@
         <v>139.1750000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>837.7734302076218</v>
+        <v>498.0815102594668</v>
       </c>
       <c r="D7" t="n">
         <v>4.36161e-07</v>
@@ -5992,16 +5772,13 @@
         <v>-6990.026653880045</v>
       </c>
       <c r="Y7" t="n">
-        <v>498.6612136504206</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>271746175.66655</v>
+        <v>58.67030859233385</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.421163704164713e-06</v>
+        <v>5.515408494016607e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8223049159105247</v>
+        <v>0.8541747790184252</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5789,7 @@
         <v>135.1300000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>831.5222623743668</v>
+        <v>552.1368600230833</v>
       </c>
       <c r="D8" t="n">
         <v>4.34615e-07</v>
@@ -6045,16 +5822,13 @@
         <v>-7046.55101699981</v>
       </c>
       <c r="Y8" t="n">
-        <v>493.5944305799873</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>207468445.7795521</v>
+        <v>0.3203036331136381</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.317363148607506e-06</v>
+        <v>5.275134793447312e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8331295148860398</v>
+        <v>0.8424409011646704</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5839,7 @@
         <v>129.705</v>
       </c>
       <c r="C9" t="n">
-        <v>818.6210053084528</v>
+        <v>543.603220030384</v>
       </c>
       <c r="D9" t="n">
         <v>4.33202e-07</v>
@@ -6098,16 +5872,13 @@
         <v>-7016.856535205619</v>
       </c>
       <c r="Y9" t="n">
-        <v>488.5616172285689</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>273495237.9056231</v>
+        <v>1.431320850966262</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.234759630935135e-06</v>
+        <v>5.078914120501508e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8423148227569807</v>
+        <v>0.8460589231489493</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5889,7 @@
         <v>127.003</v>
       </c>
       <c r="C10" t="n">
-        <v>834.3888419333576</v>
+        <v>315.0855186868077</v>
       </c>
       <c r="D10" t="n">
         <v>4.31557e-07</v>
@@ -6151,16 +5922,13 @@
         <v>-7168.370743560709</v>
       </c>
       <c r="Y10" t="n">
-        <v>483.6703421743699</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>38899764.29307637</v>
+        <v>228.441578714414</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.171538292361146e-06</v>
+        <v>1.094328748892432e-08</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8496277698707549</v>
+        <v>0.8704685082258777</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5939,7 @@
         <v>122.172</v>
       </c>
       <c r="C11" t="n">
-        <v>808.5438026539001</v>
+        <v>533.4046925234528</v>
       </c>
       <c r="D11" t="n">
         <v>4.30722e-07</v>
@@ -6204,16 +5972,13 @@
         <v>-7046.44320841293</v>
       </c>
       <c r="Y11" t="n">
-        <v>479.1177921100242</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>134952739.5320344</v>
+        <v>0.1674354169738678</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.121123047400696e-06</v>
+        <v>5.055285459165512e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8559192472240215</v>
+        <v>0.8474215419057752</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6135,7 @@
         <v>160.167</v>
       </c>
       <c r="C2" t="n">
-        <v>1043.488223772058</v>
+        <v>334.1164969201689</v>
       </c>
       <c r="D2" t="n">
         <v>4.58809e-07</v>
@@ -6403,16 +6168,13 @@
         <v>-5459.126046942333</v>
       </c>
       <c r="Y2" t="n">
-        <v>495.8142821417966</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>156362982.2244543</v>
+        <v>233.9764274278086</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.939460051597208e-06</v>
+        <v>8.964671957241233e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7230908482518855</v>
+        <v>0.8773984199962824</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6185,7 @@
         <v>138.1</v>
       </c>
       <c r="C3" t="n">
-        <v>884.9081570045441</v>
+        <v>138.1</v>
       </c>
       <c r="D3" t="n">
         <v>4.53072e-07</v>
@@ -6455,11 +6217,10 @@
       <c r="X3" t="n">
         <v>-6046.519547476223</v>
       </c>
-      <c r="Y3" t="n">
-        <v>489.3332543864511</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>22716617.17866769</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.723593905626079e-06</v>
@@ -6476,7 +6237,7 @@
         <v>129.027</v>
       </c>
       <c r="C4" t="n">
-        <v>808.5448063406125</v>
+        <v>129.027</v>
       </c>
       <c r="D4" t="n">
         <v>4.48432e-07</v>
@@ -6508,11 +6269,10 @@
       <c r="X4" t="n">
         <v>-6307.153016777313</v>
       </c>
-      <c r="Y4" t="n">
-        <v>484.174340005828</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>78898726.29831912</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.445534303458247e-06</v>
@@ -6529,7 +6289,7 @@
         <v>124.3340000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>813.539850958712</v>
+        <v>124.3340000000001</v>
       </c>
       <c r="D5" t="n">
         <v>4.44464e-07</v>
@@ -6561,11 +6321,10 @@
       <c r="X5" t="n">
         <v>-6567.897026605417</v>
       </c>
-      <c r="Y5" t="n">
-        <v>479.4093085140572</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>171103766.1913403</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.299772470422183e-06</v>
@@ -6582,7 +6341,7 @@
         <v>120.244</v>
       </c>
       <c r="C6" t="n">
-        <v>818.1181006768021</v>
+        <v>304.5602772333994</v>
       </c>
       <c r="D6" t="n">
         <v>4.41536e-07</v>
@@ -6615,16 +6374,13 @@
         <v>-6629.071089220419</v>
       </c>
       <c r="Y6" t="n">
-        <v>474.5617476358946</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>65175634.19993156</v>
+        <v>229.5371511089537</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.206148627871701e-06</v>
+        <v>1.255786432560667e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8488725973355692</v>
+        <v>0.8637443553173987</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6391,7 @@
         <v>118.028</v>
       </c>
       <c r="C7" t="n">
-        <v>853.2044808485397</v>
+        <v>118.028</v>
       </c>
       <c r="D7" t="n">
         <v>4.39399e-07</v>
@@ -6667,11 +6423,10 @@
       <c r="X7" t="n">
         <v>-7007.293960867753</v>
       </c>
-      <c r="Y7" t="n">
-        <v>469.7630187700368</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>104170035.1149336</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>1.135032723436958e-06</v>
@@ -6688,7 +6443,7 @@
         <v>113.074</v>
       </c>
       <c r="C8" t="n">
-        <v>820.4497498212651</v>
+        <v>407.0084909503017</v>
       </c>
       <c r="D8" t="n">
         <v>4.37618e-07</v>
@@ -6721,16 +6476,13 @@
         <v>-6852.533653382613</v>
       </c>
       <c r="Y8" t="n">
-        <v>465.0424294029989</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>108463446.6572052</v>
+        <v>112.6253883585625</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.083236618129556e-06</v>
+        <v>8.898413762927624e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8636058093250398</v>
+        <v>0.8424894444735603</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6493,7 @@
         <v>109.406</v>
       </c>
       <c r="C9" t="n">
-        <v>810.3757171685027</v>
+        <v>109.406</v>
       </c>
       <c r="D9" t="n">
         <v>4.36257e-07</v>
@@ -6773,11 +6525,10 @@
       <c r="X9" t="n">
         <v>-6896.546207187512</v>
       </c>
-      <c r="Y9" t="n">
-        <v>460.5687854783792</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>106565178.2821618</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.040844649526188e-06</v>
@@ -6794,7 +6545,7 @@
         <v>106.69</v>
       </c>
       <c r="C10" t="n">
-        <v>803.3956908552526</v>
+        <v>283.0177213957264</v>
       </c>
       <c r="D10" t="n">
         <v>4.35313e-07</v>
@@ -6827,16 +6578,13 @@
         <v>-6967.256924568538</v>
       </c>
       <c r="Y10" t="n">
-        <v>456.3086191296907</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40386859.37707627</v>
+        <v>225.1587883726307</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.006394073931005e-06</v>
+        <v>9.678698599853923e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8738246336810223</v>
+        <v>0.8877503672403353</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6595,7 @@
         <v>103.692</v>
       </c>
       <c r="C11" t="n">
-        <v>809.453438343553</v>
+        <v>103.692</v>
       </c>
       <c r="D11" t="n">
         <v>4.34448e-07</v>
@@ -6879,11 +6627,10 @@
       <c r="X11" t="n">
         <v>-6904.239530447566</v>
       </c>
-      <c r="Y11" t="n">
-        <v>452.2078351562517</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>62697817.95367827</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>9.803227553144902e-07</v>
@@ -6900,7 +6647,7 @@
         <v>103.007</v>
       </c>
       <c r="C12" t="n">
-        <v>828.6881346610938</v>
+        <v>273.7173824493697</v>
       </c>
       <c r="D12" t="n">
         <v>4.33791e-07</v>
@@ -6933,16 +6680,13 @@
         <v>-7139.873421238864</v>
       </c>
       <c r="Y12" t="n">
-        <v>448.3115515227257</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>96016442.48212782</v>
+        <v>224.5632628593702</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.569377701865932e-07</v>
+        <v>9.317784042985342e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8808555663346426</v>
+        <v>0.8935434217384292</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6697,7 @@
         <v>98.77200000000005</v>
       </c>
       <c r="C13" t="n">
-        <v>776.9442698460623</v>
+        <v>268.5064614968211</v>
       </c>
       <c r="D13" t="n">
         <v>4.33169e-07</v>
@@ -6986,16 +6730,13 @@
         <v>-6889.204435189553</v>
       </c>
       <c r="Y13" t="n">
-        <v>444.6650435858865</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>180879024.3102809</v>
+        <v>225.5041473890273</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.361365042195794e-07</v>
+        <v>9.552012560205847e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8839315605615186</v>
+        <v>0.8936472632074388</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6747,7 @@
         <v>98.423</v>
       </c>
       <c r="C14" t="n">
-        <v>822.5243209901458</v>
+        <v>263.0339150579779</v>
       </c>
       <c r="D14" t="n">
         <v>4.32685e-07</v>
@@ -7039,16 +6780,13 @@
         <v>-7245.118436099759</v>
       </c>
       <c r="Y14" t="n">
-        <v>441.1438797420638</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>26692653.95806248</v>
+        <v>225.8151480451947</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.169170173836528e-07</v>
+        <v>9.137200282402247e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8868648255645546</v>
+        <v>0.8981775171635348</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6797,7 @@
         <v>95.363</v>
       </c>
       <c r="C15" t="n">
-        <v>797.6483694151879</v>
+        <v>95.363</v>
       </c>
       <c r="D15" t="n">
         <v>4.32169e-07</v>
@@ -7091,11 +6829,10 @@
       <c r="X15" t="n">
         <v>-7071.456782491423</v>
       </c>
-      <c r="Y15" t="n">
-        <v>437.784385584846</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>53063169.06322414</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>9.019821697617403e-07</v>
@@ -7112,7 +6849,7 @@
         <v>95.43600000000004</v>
       </c>
       <c r="C16" t="n">
-        <v>830.8179406784708</v>
+        <v>257.9728825513806</v>
       </c>
       <c r="D16" t="n">
         <v>4.3181e-07</v>
@@ -7145,16 +6882,13 @@
         <v>-7240.648976410118</v>
       </c>
       <c r="Y16" t="n">
-        <v>434.5817543191504</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>482158631.2871308</v>
+        <v>223.1497669117101</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.881227119662631e-07</v>
+        <v>8.813216970690735e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8913408360591843</v>
+        <v>0.9026102574503376</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6899,7 @@
         <v>92.89800000000002</v>
       </c>
       <c r="C17" t="n">
-        <v>801.233116758712</v>
+        <v>254.2766419065472</v>
       </c>
       <c r="D17" t="n">
         <v>4.31649e-07</v>
@@ -7198,16 +6932,13 @@
         <v>-7098.044478056531</v>
       </c>
       <c r="Y17" t="n">
-        <v>431.4658987977885</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>66454227.7795037</v>
+        <v>222.5908433526382</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.778198949022282e-07</v>
+        <v>8.677304191536069e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8930375616049108</v>
+        <v>0.9041558733344822</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6949,7 @@
         <v>92.55700000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>834.1956570558813</v>
+        <v>252.9985975797835</v>
       </c>
       <c r="D18" t="n">
         <v>4.31129e-07</v>
@@ -7251,16 +6982,13 @@
         <v>-7292.476624573471</v>
       </c>
       <c r="Y18" t="n">
-        <v>428.3829152722445</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>353225684.149655</v>
+        <v>220.5782957544154</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.644316165480016e-07</v>
+        <v>8.630892086397648e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8951668052222892</v>
+        <v>0.9053247698842103</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6999,7 @@
         <v>89.63600000000002</v>
       </c>
       <c r="C19" t="n">
-        <v>806.0227464239404</v>
+        <v>89.63600000000002</v>
       </c>
       <c r="D19" t="n">
         <v>4.30989e-07</v>
@@ -7303,11 +7031,10 @@
       <c r="X19" t="n">
         <v>-7092.611485683071</v>
       </c>
-      <c r="Y19" t="n">
-        <v>425.3353741601115</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>116867376.7142304</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>8.536167775033069e-07</v>
@@ -7324,7 +7051,7 @@
         <v>88.459</v>
       </c>
       <c r="C20" t="n">
-        <v>802.5224884028778</v>
+        <v>88.459</v>
       </c>
       <c r="D20" t="n">
         <v>4.30699e-07</v>
@@ -7356,11 +7083,10 @@
       <c r="X20" t="n">
         <v>-7095.151652313633</v>
       </c>
-      <c r="Y20" t="n">
-        <v>422.2906207194653</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>231628942.6914996</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>8.443795545922185e-07</v>
@@ -7377,7 +7103,7 @@
         <v>86.61900000000003</v>
       </c>
       <c r="C21" t="n">
-        <v>779.5675432615542</v>
+        <v>251.0088762303748</v>
       </c>
       <c r="D21" t="n">
         <v>4.30495e-07</v>
@@ -7410,16 +7136,13 @@
         <v>-6975.334469223051</v>
       </c>
       <c r="Y21" t="n">
-        <v>419.3044655653769</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>229870125.7516502</v>
+        <v>209.9150038260544</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.342861206783969e-07</v>
+        <v>7.256691602076838e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9002518912254268</v>
+        <v>0.9149628709237932</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7153,7 @@
         <v>85.46499999999997</v>
       </c>
       <c r="C22" t="n">
-        <v>791.0505212679806</v>
+        <v>243.0121241848016</v>
       </c>
       <c r="D22" t="n">
         <v>4.30317e-07</v>
@@ -7463,16 +7186,13 @@
         <v>-7100.616029708968</v>
       </c>
       <c r="Y22" t="n">
-        <v>416.3153368583119</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>369199774.5804985</v>
+        <v>215.2431753859917</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.240718858778662e-07</v>
+        <v>7.825916516477219e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9020368808862339</v>
+        <v>0.914317278246609</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7349,7 @@
         <v>252.609</v>
       </c>
       <c r="C2" t="n">
-        <v>2368.838046024616</v>
+        <v>377.4397619545867</v>
       </c>
       <c r="D2" t="n">
         <v>4.35053e-07</v>
@@ -7662,16 +7382,13 @@
         <v>-5422.829001986913</v>
       </c>
       <c r="Y2" t="n">
-        <v>473.7338192961772</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3662580913.677582</v>
+        <v>236.5820145616161</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.362371856452821e-05</v>
+        <v>3.921569755919438e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000002</v>
+        <v>0.9202110267367234</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7399,7 @@
         <v>164.822</v>
       </c>
       <c r="C3" t="n">
-        <v>935.9111320599898</v>
+        <v>415.9483039897123</v>
       </c>
       <c r="D3" t="n">
         <v>4.51048e-07</v>
@@ -7715,16 +7432,13 @@
         <v>-5935.181640114986</v>
       </c>
       <c r="Y3" t="n">
-        <v>505.2416117076925</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1013067522.250978</v>
+        <v>162.7118168876084</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.907913506570322e-06</v>
+        <v>7.213899344885438e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7218054592484467</v>
+        <v>0.8635338508208802</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7449,7 @@
         <v>147.1370000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>826.5638912266113</v>
+        <v>530.6638339282691</v>
       </c>
       <c r="D4" t="n">
         <v>4.48767e-07</v>
@@ -7768,16 +7482,13 @@
         <v>-6306.031847322581</v>
       </c>
       <c r="Y4" t="n">
-        <v>501.9309252934821</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>462625513.1415778</v>
+        <v>33.58819674369533</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.896365003181546e-06</v>
+        <v>5.236126528890592e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7837861139106181</v>
+        <v>0.8502248498490675</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7499,7 @@
         <v>141.7979999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>799.3862411092333</v>
+        <v>560.4140204916351</v>
       </c>
       <c r="D5" t="n">
         <v>4.4517e-07</v>
@@ -7821,16 +7532,13 @@
         <v>-6693.238552575581</v>
       </c>
       <c r="Y5" t="n">
-        <v>498.1829296978888</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>290644206.8760032</v>
+        <v>0.5467358702557993</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.591777310518496e-06</v>
+        <v>5.632429798621797e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8085333773744523</v>
+        <v>0.8373143519807432</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7549,7 @@
         <v>138.0910000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>811.0106204026055</v>
+        <v>554.0804433343902</v>
       </c>
       <c r="D6" t="n">
         <v>4.4222e-07</v>
@@ -7874,16 +7582,13 @@
         <v>-7021.644868862996</v>
       </c>
       <c r="Y6" t="n">
-        <v>494.0539812384313</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>92908426.54140775</v>
+        <v>0.01079943288819366</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.426486985183265e-06</v>
+        <v>5.500397832912439e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8238595213477984</v>
+        <v>0.8392904455664761</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7599,7 @@
         <v>132.848</v>
       </c>
       <c r="C7" t="n">
-        <v>802.0445561048178</v>
+        <v>483.5527475669858</v>
       </c>
       <c r="D7" t="n">
         <v>4.39685e-07</v>
@@ -7927,16 +7632,13 @@
         <v>-7046.79146399494</v>
       </c>
       <c r="Y7" t="n">
-        <v>489.4233714150621</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>227679531.9324244</v>
+        <v>61.27820192442701</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.316241109357098e-06</v>
+        <v>5.498115757507937e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8350115586261411</v>
+        <v>0.8568130994864849</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7649,7 @@
         <v>130.141</v>
       </c>
       <c r="C8" t="n">
-        <v>816.625271683134</v>
+        <v>130.141</v>
       </c>
       <c r="D8" t="n">
         <v>4.38041e-07</v>
@@ -7979,11 +7681,10 @@
       <c r="X8" t="n">
         <v>-7248.825986570318</v>
       </c>
-      <c r="Y8" t="n">
-        <v>484.6246491553262</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>160794777.1034012</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.231416102251103e-06</v>
@@ -8000,7 +7701,7 @@
         <v>125.787</v>
       </c>
       <c r="C9" t="n">
-        <v>810.1837017576305</v>
+        <v>125.787</v>
       </c>
       <c r="D9" t="n">
         <v>4.36693e-07</v>
@@ -8032,11 +7733,10 @@
       <c r="X9" t="n">
         <v>-7355.659449026061</v>
       </c>
-      <c r="Y9" t="n">
-        <v>479.7650701934186</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>134412634.0496769</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.16560288558556e-06</v>
@@ -8053,7 +7753,7 @@
         <v>121.0740000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>783.9633483053208</v>
+        <v>121.0740000000001</v>
       </c>
       <c r="D10" t="n">
         <v>4.35442e-07</v>
@@ -8085,11 +7785,10 @@
       <c r="X10" t="n">
         <v>-7170.807106811348</v>
       </c>
-      <c r="Y10" t="n">
-        <v>475.0659821543966</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>75374975.55866922</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.114184749502611e-06</v>
@@ -8106,7 +7805,7 @@
         <v>119.4400000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>837.3760620435909</v>
+        <v>119.4400000000001</v>
       </c>
       <c r="D11" t="n">
         <v>4.34572e-07</v>
@@ -8138,11 +7837,10 @@
       <c r="X11" t="n">
         <v>-7612.879650833882</v>
       </c>
-      <c r="Y11" t="n">
-        <v>470.5584005846731</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>162780846.5726622</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.072257515075533e-06</v>
@@ -8305,7 +8003,7 @@
         <v>153.023</v>
       </c>
       <c r="C2" t="n">
-        <v>1218.115784273938</v>
+        <v>313.2897016304861</v>
       </c>
       <c r="D2" t="n">
         <v>4.51162e-07</v>
@@ -8338,16 +8036,13 @@
         <v>-6274.935947885607</v>
       </c>
       <c r="Y2" t="n">
-        <v>484.884699817303</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>355113031.7250056</v>
+        <v>231.1732521385077</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.808766172188195e-06</v>
+        <v>7.956098708234876e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7916546012767963</v>
+        <v>0.8908302935498644</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8053,7 @@
         <v>129.379</v>
       </c>
       <c r="C3" t="n">
-        <v>849.4161967314963</v>
+        <v>129.379</v>
       </c>
       <c r="D3" t="n">
         <v>4.46847e-07</v>
@@ -8390,11 +8085,10 @@
       <c r="X3" t="n">
         <v>-6945.694822136638</v>
       </c>
-      <c r="Y3" t="n">
-        <v>474.7035148491834</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>206070272.7912714</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.298060893215393e-06</v>
@@ -8411,7 +8105,7 @@
         <v>119.571</v>
       </c>
       <c r="C4" t="n">
-        <v>786.2577100210832</v>
+        <v>523.2220748138061</v>
       </c>
       <c r="D4" t="n">
         <v>4.43147e-07</v>
@@ -8444,16 +8138,13 @@
         <v>-6902.711823665977</v>
       </c>
       <c r="Y4" t="n">
-        <v>470.0777566933614</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>113522863.573035</v>
+        <v>0.0001933815270209351</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.173991412747739e-06</v>
+        <v>5.0991633834588e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8533364120133866</v>
+        <v>0.8479513196795739</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8155,7 @@
         <v>117.955</v>
       </c>
       <c r="C5" t="n">
-        <v>806.8051627215439</v>
+        <v>518.2150800571458</v>
       </c>
       <c r="D5" t="n">
         <v>4.40309e-07</v>
@@ -8497,16 +8188,13 @@
         <v>-7214.44922391076</v>
       </c>
       <c r="Y5" t="n">
-        <v>466.3156443603283</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>62791011.76172917</v>
+        <v>0.0001231129370903861</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.106332742237177e-06</v>
+        <v>5.027801322130716e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8612522102451547</v>
+        <v>0.8494882779680456</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8205,7 @@
         <v>115.4640000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>798.854162741632</v>
+        <v>511.730035774104</v>
       </c>
       <c r="D6" t="n">
         <v>4.38424e-07</v>
@@ -8550,16 +8238,13 @@
         <v>-7358.138420855429</v>
       </c>
       <c r="Y6" t="n">
-        <v>462.6292425085679</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>101367344.4809037</v>
+        <v>0.2329993735128586</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.057235159675903e-06</v>
+        <v>4.720539321122799e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8674125484443523</v>
+        <v>0.8543111532345116</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8255,7 @@
         <v>109.395</v>
       </c>
       <c r="C7" t="n">
-        <v>757.0462166453307</v>
+        <v>508.1335931525707</v>
       </c>
       <c r="D7" t="n">
         <v>4.36996e-07</v>
@@ -8603,16 +8288,13 @@
         <v>-7022.075921221984</v>
       </c>
       <c r="Y7" t="n">
-        <v>458.8581701532798</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>42430884.49731868</v>
+        <v>0.003117061186989331</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02005034564565e-06</v>
+        <v>4.748147717970063e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8722783261207379</v>
+        <v>0.8545876777279866</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8305,7 @@
         <v>109.599</v>
       </c>
       <c r="C8" t="n">
-        <v>820.7290984517356</v>
+        <v>412.6560463597323</v>
       </c>
       <c r="D8" t="n">
         <v>4.35761e-07</v>
@@ -8656,16 +8338,13 @@
         <v>-7434.344010347481</v>
       </c>
       <c r="Y8" t="n">
-        <v>455.0869893102939</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>74210787.16324848</v>
+        <v>88.58710662521277</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.922564139804294e-07</v>
+        <v>5.148387467296643e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8759964846137275</v>
+        <v>0.8767034840531128</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8355,7 @@
         <v>107.878</v>
       </c>
       <c r="C9" t="n">
-        <v>802.5648545550554</v>
+        <v>107.878</v>
       </c>
       <c r="D9" t="n">
         <v>4.34831e-07</v>
@@ -8708,11 +8387,10 @@
       <c r="X9" t="n">
         <v>-7428.082345821925</v>
       </c>
-      <c r="Y9" t="n">
-        <v>451.5493399788623</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>145881031.8591446</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>9.670763581717393e-07</v>
@@ -8729,7 +8407,7 @@
         <v>102.998</v>
       </c>
       <c r="C10" t="n">
-        <v>754.154687717345</v>
+        <v>401.807862650037</v>
       </c>
       <c r="D10" t="n">
         <v>4.34146e-07</v>
@@ -8762,16 +8440,13 @@
         <v>-7170.580770642491</v>
       </c>
       <c r="Y10" t="n">
-        <v>448.3053541255115</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>27559080.97169546</v>
+        <v>91.50799367691586</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.463653600061264e-07</v>
+        <v>5.104254664694757e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.882536788197224</v>
+        <v>0.8803014727068694</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8457,7 @@
         <v>101.88</v>
       </c>
       <c r="C11" t="n">
-        <v>765.997359315834</v>
+        <v>491.1440979420111</v>
       </c>
       <c r="D11" t="n">
         <v>4.33535e-07</v>
@@ -8815,16 +8490,13 @@
         <v>-7209.415035910584</v>
       </c>
       <c r="Y11" t="n">
-        <v>445.1064134618819</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>143682236.2221341</v>
+        <v>0.06689358918225871</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.30002885933358e-07</v>
+        <v>4.425012599587308e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.884943565494608</v>
+        <v>0.86195778556679</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8507,7 @@
         <v>102.292</v>
       </c>
       <c r="C12" t="n">
-        <v>791.7857759088873</v>
+        <v>487.5179649450142</v>
       </c>
       <c r="D12" t="n">
         <v>4.32944e-07</v>
@@ -8868,16 +8540,13 @@
         <v>-7605.863129560093</v>
       </c>
       <c r="Y12" t="n">
-        <v>442.0399033444564</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>355382726.0797141</v>
+        <v>0.04410234101551238</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.144436966195757e-07</v>
+        <v>4.359573661322397e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8872742840777263</v>
+        <v>0.8635683528310324</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8557,7 @@
         <v>99.053</v>
       </c>
       <c r="C13" t="n">
-        <v>769.8171288125011</v>
+        <v>99.053</v>
       </c>
       <c r="D13" t="n">
         <v>4.32504e-07</v>
@@ -8920,11 +8589,10 @@
       <c r="X13" t="n">
         <v>-7405.061580935761</v>
       </c>
-      <c r="Y13" t="n">
-        <v>439.0231331823721</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>253139142.7484311</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>8.990603939861496e-07</v>
@@ -8941,7 +8609,7 @@
         <v>95.80500000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>730.9405347501676</v>
+        <v>476.4583179211646</v>
       </c>
       <c r="D14" t="n">
         <v>4.3227e-07</v>
@@ -8974,16 +8642,13 @@
         <v>-7101.120272662076</v>
       </c>
       <c r="Y14" t="n">
-        <v>436.0900456156388</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>110425024.3092927</v>
+        <v>1.704095497509032</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.868767868096841e-07</v>
+        <v>3.912352948975336e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8916151497611586</v>
+        <v>0.8725150452502605</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8659,7 @@
         <v>95.767</v>
       </c>
       <c r="C15" t="n">
-        <v>753.6890350173726</v>
+        <v>262.8910508807895</v>
       </c>
       <c r="D15" t="n">
         <v>4.31992e-07</v>
@@ -9027,16 +8692,13 @@
         <v>-7290.849198095433</v>
       </c>
       <c r="Y15" t="n">
-        <v>433.187297301179</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>44756321.40970081</v>
+        <v>217.15724175619</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.754502068073215e-07</v>
+        <v>8.800484726504791e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8934618427485918</v>
+        <v>0.9006545739675987</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8709,7 @@
         <v>96.02799999999996</v>
       </c>
       <c r="C16" t="n">
-        <v>794.8234799865299</v>
+        <v>262.5722163674482</v>
       </c>
       <c r="D16" t="n">
         <v>4.31527e-07</v>
@@ -9080,16 +8742,13 @@
         <v>-7541.798441316817</v>
       </c>
       <c r="Y16" t="n">
-        <v>430.328627180213</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>204915776.1680939</v>
+        <v>213.7035219855187</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.664470345149445e-07</v>
+        <v>8.495622274722188e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8948725901518495</v>
+        <v>0.9025131260735079</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8759,7 @@
         <v>94.37</v>
       </c>
       <c r="C17" t="n">
-        <v>779.6009169260756</v>
+        <v>259.7704060435931</v>
       </c>
       <c r="D17" t="n">
         <v>4.31349e-07</v>
@@ -9133,16 +8792,13 @@
         <v>-7529.773770926233</v>
       </c>
       <c r="Y17" t="n">
-        <v>427.5118109095331</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>236039388.4358574</v>
+        <v>213.1090910607948</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.555866333473535e-07</v>
+        <v>8.336396855207659e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8966884849992028</v>
+        <v>0.9048192750092632</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8809,7 @@
         <v>93.35500000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>805.3870022442122</v>
+        <v>251.1923533359191</v>
       </c>
       <c r="D18" t="n">
         <v>4.31111e-07</v>
@@ -9186,16 +8842,13 @@
         <v>-7617.267294575604</v>
       </c>
       <c r="Y18" t="n">
-        <v>424.6600818163836</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>467146461.0758933</v>
+        <v>218.0671771020388</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.453533080133084e-07</v>
+        <v>8.383182298544991e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.898406185788005</v>
+        <v>0.9082196401617074</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8859,7 @@
         <v>89.81599999999997</v>
       </c>
       <c r="C19" t="n">
-        <v>752.1526997067319</v>
+        <v>250.9709343648124</v>
       </c>
       <c r="D19" t="n">
         <v>4.31054e-07</v>
@@ -9239,16 +8892,13 @@
         <v>-7309.895856728192</v>
       </c>
       <c r="Y19" t="n">
-        <v>421.7794216213097</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>177374146.0547042</v>
+        <v>214.5838698732216</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.36700635626022e-07</v>
+        <v>8.079893261906339e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8999286810833996</v>
+        <v>0.9101214374061797</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8909,7 @@
         <v>91.851</v>
       </c>
       <c r="C20" t="n">
-        <v>826.665778252878</v>
+        <v>252.8425253186774</v>
       </c>
       <c r="D20" t="n">
         <v>4.30803e-07</v>
@@ -9292,16 +8942,13 @@
         <v>-7777.014113823913</v>
       </c>
       <c r="Y20" t="n">
-        <v>418.8648413205626</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>229731178.3723945</v>
+        <v>209.060667570288</v>
       </c>
       <c r="AA20" t="n">
-        <v>8.29334772169683e-07</v>
+        <v>7.746456551264658e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.901180577618217</v>
+        <v>0.911525795442002</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8959,7 @@
         <v>89.185</v>
       </c>
       <c r="C21" t="n">
-        <v>791.8724801378852</v>
+        <v>89.185</v>
       </c>
       <c r="D21" t="n">
         <v>4.308e-07</v>
@@ -9344,11 +8991,10 @@
       <c r="X21" t="n">
         <v>-7507.868026603772</v>
       </c>
-      <c r="Y21" t="n">
-        <v>416.0055626305751</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>120526718.694884</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>8.212145709939803e-07</v>
@@ -9365,7 +9011,7 @@
         <v>88.81700000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>808.0437844623435</v>
+        <v>241.6725942525742</v>
       </c>
       <c r="D22" t="n">
         <v>4.30646e-07</v>
@@ -9398,16 +9044,13 @@
         <v>-7676.419263588273</v>
       </c>
       <c r="Y22" t="n">
-        <v>413.0712188009529</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>121548027.0439025</v>
+        <v>212.7578631133867</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.129018748708925e-07</v>
+        <v>7.448945008599114e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.904123777226483</v>
+        <v>0.918199076133883</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9207,7 @@
         <v>222.272</v>
       </c>
       <c r="C2" t="n">
-        <v>2507.379003428469</v>
+        <v>353.3575561525302</v>
       </c>
       <c r="D2" t="n">
         <v>4.48386e-07</v>
@@ -9597,16 +9240,13 @@
         <v>-5178.691403244354</v>
       </c>
       <c r="Y2" t="n">
-        <v>454.7140628599946</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>296787138.5262638</v>
+        <v>235.0370460086797</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.442896959231097e-05</v>
+        <v>4.649237520811054e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.913086834691063</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9257,7 @@
         <v>146.141</v>
       </c>
       <c r="C3" t="n">
-        <v>885.2646513601907</v>
+        <v>556.170447240961</v>
       </c>
       <c r="D3" t="n">
         <v>4.55766e-07</v>
@@ -9650,16 +9290,13 @@
         <v>-5595.680165755084</v>
       </c>
       <c r="Y3" t="n">
-        <v>493.7219846016717</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>684393800.2032897</v>
+        <v>0.258635050847444</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.145430711220483e-06</v>
+        <v>4.751005632617188e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7682074996702765</v>
+        <v>0.8477972560227365</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9307,7 @@
         <v>134.244</v>
       </c>
       <c r="C4" t="n">
-        <v>813.0899474771742</v>
+        <v>544.5013319015781</v>
       </c>
       <c r="D4" t="n">
         <v>4.49985e-07</v>
@@ -9703,16 +9340,13 @@
         <v>-6219.262191740373</v>
       </c>
       <c r="Y4" t="n">
-        <v>487.0570230297017</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>83416286.49601777</v>
+        <v>0.03030348206688691</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.559200790171495e-06</v>
+        <v>4.774008285414497e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8135065963305714</v>
+        <v>0.8498666677041483</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9357,7 @@
         <v>128.718</v>
       </c>
       <c r="C5" t="n">
-        <v>804.2010713132283</v>
+        <v>536.800104841796</v>
       </c>
       <c r="D5" t="n">
         <v>4.44787e-07</v>
@@ -9756,16 +9390,13 @@
         <v>-6630.67046464207</v>
       </c>
       <c r="Y5" t="n">
-        <v>481.4987956014188</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>97234133.54792821</v>
+        <v>0.1531012684170474</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.341308952563464e-06</v>
+        <v>4.971192323250702e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8341125685920484</v>
+        <v>0.8477538189558278</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9407,7 @@
         <v>124.217</v>
       </c>
       <c r="C6" t="n">
-        <v>828.7572684136031</v>
+        <v>305.3409246034814</v>
       </c>
       <c r="D6" t="n">
         <v>4.40734e-07</v>
@@ -9809,16 +9440,13 @@
         <v>-6913.117957816235</v>
       </c>
       <c r="Y6" t="n">
-        <v>475.6589047444313</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>40392632.62186754</v>
+        <v>229.1155811284453</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.215800879654981e-06</v>
+        <v>1.135109647061333e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8473687714558438</v>
+        <v>0.8705621653772283</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9457,7 @@
         <v>118.112</v>
       </c>
       <c r="C7" t="n">
-        <v>787.2667825626219</v>
+        <v>520.0444126110438</v>
       </c>
       <c r="D7" t="n">
         <v>4.3773e-07</v>
@@ -9862,16 +9490,13 @@
         <v>-6779.458745065738</v>
       </c>
       <c r="Y7" t="n">
-        <v>469.5170387710796</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>237065273.760372</v>
+        <v>0.1527565954224059</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13258003917621e-06</v>
+        <v>4.566063374446851e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8569422978983555</v>
+        <v>0.8553134969635551</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9507,7 @@
         <v>114.285</v>
       </c>
       <c r="C8" t="n">
-        <v>807.9340787774646</v>
+        <v>290.3060177403862</v>
       </c>
       <c r="D8" t="n">
         <v>4.35741e-07</v>
@@ -9915,16 +9540,13 @@
         <v>-6985.424340662788</v>
       </c>
       <c r="Y8" t="n">
-        <v>463.5401903201668</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>194730491.0327183</v>
+        <v>227.0685318645292</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.067916225075361e-06</v>
+        <v>1.00071103126385e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8650359142213063</v>
+        <v>0.8833710219899705</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9557,7 @@
         <v>112.262</v>
       </c>
       <c r="C9" t="n">
-        <v>827.4264766120192</v>
+        <v>285.6419406409255</v>
       </c>
       <c r="D9" t="n">
         <v>4.34237e-07</v>
@@ -9968,16 +9590,13 @@
         <v>-7262.25964341097</v>
       </c>
       <c r="Y9" t="n">
-        <v>457.9519030044322</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>48138607.27177531</v>
+        <v>225.6740811319628</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.019854564218235e-06</v>
+        <v>1.036942287176548e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8714067212329445</v>
+        <v>0.8823746107270162</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9607,7 @@
         <v>108.089</v>
       </c>
       <c r="C10" t="n">
-        <v>827.0689323487677</v>
+        <v>108.089</v>
       </c>
       <c r="D10" t="n">
         <v>4.33108e-07</v>
@@ -10020,11 +9639,10 @@
       <c r="X10" t="n">
         <v>-7258.901441500197</v>
       </c>
-      <c r="Y10" t="n">
-        <v>452.7277353084801</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>51712806.20927975</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>9.815714045508991e-07</v>
@@ -10041,7 +9659,7 @@
         <v>104.666</v>
       </c>
       <c r="C11" t="n">
-        <v>801.3653004231917</v>
+        <v>274.6576556691974</v>
       </c>
       <c r="D11" t="n">
         <v>4.32166e-07</v>
@@ -10074,16 +9692,13 @@
         <v>-7197.159314864291</v>
       </c>
       <c r="Y11" t="n">
-        <v>447.9635293046174</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>68623519.53066643</v>
+        <v>222.4276230014928</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.532182013866964e-07</v>
+        <v>9.015651857710094e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8808114597849536</v>
+        <v>0.8944816661828154</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 54.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>8.491878219584032e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8889358848696474</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>169.7359999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>981.5871035159663</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.06231e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-75.92700000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3845479297057577</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5853427330038721</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.368009598585035</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.999910024957944</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.00214520235519</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.31904019323876</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.05250869740089</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6186.824596413466</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-326.7316989407959</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.846606468641e-06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.7726976832521258</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>156.4959999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9219965122307583</v>
+      </c>
+      <c r="D13" t="n">
+        <v>816.4935903427236</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.831809614672105</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.01658e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-77.262</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8037512408050527</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.033109438989221</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.772339886195368</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.470926973875821</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.57290596688247</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.28703657916409</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.12962880506918</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7254.536331230087</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-200.7335108686739</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.320704692016398e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8206223692429329</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>150.422</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8862115284913044</v>
+      </c>
+      <c r="D14" t="n">
+        <v>807.9161982255528</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8230713253379773</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.01002e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-77.672</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1038561340040198</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7978692452520235</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.533344702110725</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.306458710094026</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.52437313992124</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.42140891304169</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.48719656247537</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7341.728118451605</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-200.5890023785698</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.208039586293898e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8336700133681956</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>149.673</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8817987934203708</v>
+      </c>
+      <c r="D15" t="n">
+        <v>936.9647059616592</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.954540562529323</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.00951e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-77.985</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2701663118939374</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9648191692705834</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.824760286292498</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.421282501401598</v>
+      </c>
+      <c r="L15" t="n">
+        <v>18.42995625072856</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.69160508820447</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.27356221133092</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-7705.298839750636</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-315.0968017263104</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.124365288833633e-06</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8444167437723781</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>132.994</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7835344299382572</v>
+      </c>
+      <c r="D16" t="n">
+        <v>868.1132768488613</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8843975982766574</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.03341e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-78.367</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1296755385574064</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8195420234838361</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.592554015208401</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.244106770824501</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18.27020855510006</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.6495160290913</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13.1446584816687</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-7311.638077076997</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-280.7450435367661</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.024358980873656e-06</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8594018771637804</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>123.899</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.729951218362634</v>
+      </c>
+      <c r="D17" t="n">
+        <v>862.775037423124</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8789592226025923</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.04904e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-78.67</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3866251402718449</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7593663139502894</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.337668774811911</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.238099725959418</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.87034911768952</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.77472239040441</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.53564966542519</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-7322.592353732044</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-291.9039089966907</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.652224676637845e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8689490814493078</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>115.547</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.68074539284536</v>
+      </c>
+      <c r="D18" t="n">
+        <v>827.5444130552688</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8430677319323686</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.0578e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-78.93000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1777446246158907</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7228030124591078</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.428752240155295</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.23411350238359</v>
+      </c>
+      <c r="L18" t="n">
+        <v>19.06487527526921</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.77259387230671</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.52880962644852</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-7129.047920876661</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-273.8458100087879</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.230098307439331e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.875998154022779</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110.194</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6492081821181132</v>
+      </c>
+      <c r="D19" t="n">
+        <v>822.3940920007037</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8378207996569577</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.06198e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-79.127</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2310114130021612</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9108384694331664</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.476907687196027</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.408816668596422</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.22242904412619</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.89937489564757</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.94858544649129</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-7228.637771056801</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-279.2287752588014</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.916688351433397e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8813696414110527</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106.366</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6266555120893624</v>
+      </c>
+      <c r="D20" t="n">
+        <v>801.471314997186</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8165055471148511</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.06765e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-79.301</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.05317208811171149</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6035895388635084</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.381494455177385</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.138656845442183</v>
+      </c>
+      <c r="L20" t="n">
+        <v>19.86553738430784</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.94808366500585</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.11683428752971</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7197.511933054325</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-268.5582362076385</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.686734850159351e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.885505297278968</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103.319</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6087041051986618</v>
+      </c>
+      <c r="D21" t="n">
+        <v>826.2169462986078</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8417153641680549</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.06819e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-79.45099999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.373491704239077</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9432675202739751</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.430791968920269</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.518442436930063</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21.06314399125852</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.04956526492397</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.48067438528013</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-7299.499636574808</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-297.1659947607396</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.491878219584032e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8889358848696474</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>7.80187494533801e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9076586219078739</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>146.6200000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1126.058770359317</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.38136e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-76.828</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3924209983879824</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8910132017726454</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.614097729271899</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.306355301069031</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.65069156023822</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.14651427036735</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.7768284397507</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6742.022109887177</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-493.3882292778032</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.478231451742328e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8172474898596364</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>123.864</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8447960714772877</v>
+      </c>
+      <c r="D24" t="n">
+        <v>800.1982379694881</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7106185387767554</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.33907e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-77.80800000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5544682007665085</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.371329812182093</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.200639383766575</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18.15825014107626</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.43425584999352</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.52248243356156</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-6812.802726634773</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-234.7542155305896</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.174355328937243e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8501281648784971</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>120.127</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8193084163142815</v>
+      </c>
+      <c r="D25" t="n">
+        <v>813.997859670964</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7228733358306184</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.31461e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-78.137</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3419299628915256</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7032330073002038</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.560724885946134</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.488244405021416</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.41374222147842</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.72503267955744</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.3777439907933</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-7195.355208348639</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-255.5761345108543</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.094773477069725e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8597889939004243</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>115.028</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7845314418223974</v>
+      </c>
+      <c r="D26" t="n">
+        <v>791.1425752835594</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7025766293095976</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.29532e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-78.36499999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2689838213703519</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5947670443258029</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.358287551024505</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.172710327564091</v>
+      </c>
+      <c r="L26" t="n">
+        <v>18.65114934197274</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.74488277369484</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.44038275558935</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-7129.177219382758</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-241.2176592430294</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.045463250749225e-06</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8660217394259915</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111.7569999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7622220706588453</v>
+      </c>
+      <c r="D27" t="n">
+        <v>769.6856214708598</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6835217146128693</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.28319e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-78.559</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1959637013551754</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6451804356809925</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.561364031254846</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.427714661989078</v>
+      </c>
+      <c r="L27" t="n">
+        <v>19.9277282170277</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.77791914159805</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.5459354280871</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7093.682694217379</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-227.7917393789655</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.008757036480951e-06</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8709474405750814</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>110.511</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.753723912153867</v>
+      </c>
+      <c r="D28" t="n">
+        <v>822.7137056363293</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7306134700001558</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.27434e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-78.73999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5853508196965488</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.148258223508681</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.704540254966236</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.677197328111044</v>
+      </c>
+      <c r="L28" t="n">
+        <v>21.37355494812692</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.00770599639398</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.32835946341241</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7453.784650128228</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-280.8434009823754</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.76414534436509e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8755254932747133</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>105.834</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7218251261765104</v>
+      </c>
+      <c r="D29" t="n">
+        <v>791.9101754708012</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7032582990478448</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.26567e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.90300000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1620191109249551</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7927896207236551</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.582693475529581</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.512423912947165</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.18832148142454</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.94466451637027</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.10489225944609</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7223.820233961746</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-259.7764735658163</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.486780199241122e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8795528532825296</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7129995907788836</v>
+      </c>
+      <c r="D30" t="n">
+        <v>830.5448252614452</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7375679201862833</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.25913e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-79.035</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1934440461196696</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9217267792799397</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.548172736611009</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.540775212139333</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.9344835537499</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.07607965060043</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.57883173067389</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7406.362743820021</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-299.6787227796926</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.275650692967625e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8827012141856697</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101.923</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6951507297776562</v>
+      </c>
+      <c r="D31" t="n">
+        <v>813.4289211796463</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7223680882304988</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.25449e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-79.17</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5898868227231487</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9754121063680682</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.645764916656965</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.538981844753542</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.83726287810773</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.10565377072155</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14.68989071328384</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7384.207958212489</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-288.9428153901226</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.080503930994159e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8857282762463824</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101.522</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6924157686536622</v>
+      </c>
+      <c r="D32" t="n">
+        <v>854.4597118607617</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7588056097534853</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.25006e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-79.30800000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.916902483679086</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.211021110451384</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.836011087939798</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.514841850400109</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21.25621549355462</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.25781826491523</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>15.28901824021155</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-7641.013345132657</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-330.5647678024887</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.895668155853722e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8886539260912504</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97.41800000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6644250443322873</v>
+      </c>
+      <c r="D33" t="n">
+        <v>827.1719876458434</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7345726612314371</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.24651e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-79.402</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5515187304837327</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.11457692261262</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.891092280276125</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.42082606058055</v>
+      </c>
+      <c r="L33" t="n">
+        <v>21.42518727881927</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.19457242780233</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15.03418603426702</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-7422.646926486967</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-310.2125243118734</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.764206311982184e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8907696604704239</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95.50299999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6513640703860315</v>
+      </c>
+      <c r="D34" t="n">
+        <v>801.5089056901531</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7117824813303459</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.24329e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-79.49299999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3421948417589228</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9068870139793079</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.595254980404627</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.642209985595446</v>
+      </c>
+      <c r="L34" t="n">
+        <v>22.52980404655059</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.18119739029416</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>14.98137460725235</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-7320.492460151338</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-291.2585898899756</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.634925066014833e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8928959349140891</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>94.517</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6446392033828943</v>
+      </c>
+      <c r="D35" t="n">
+        <v>801.5553509857897</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7118237272198671</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.24097e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-79.61</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4658419382573964</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.883764495243796</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.60875843712789</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.594318049850169</v>
+      </c>
+      <c r="L35" t="n">
+        <v>22.87069040942833</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.23643882630302</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>15.20191862512941</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7367.309836368556</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-295.3073007345214</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.508675645135113e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8950116281357834</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91.726</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6256036011458188</v>
+      </c>
+      <c r="D36" t="n">
+        <v>781.2120135397187</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6937577630077332</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.24007e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.70699999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6564991690311296</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.565212807252517</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.310630091720536</v>
+      </c>
+      <c r="L36" t="n">
+        <v>21.28672910471354</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.18873829179076</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>15.01110439671592</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-7193.465923212082</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-280.8982089467157</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.401976279531202e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8968687594459273</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90.57299999999998</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6177397353703447</v>
+      </c>
+      <c r="D37" t="n">
+        <v>797.4804102113902</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7082049633669829</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.23705e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.794</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2367392183175776</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9360960970092798</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.537793554309302</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.42255822182277</v>
+      </c>
+      <c r="L37" t="n">
+        <v>22.30368955893963</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.2659016490831</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>15.32220933072214</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-7289.452757198575</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-299.5246003023614</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.296606311151344e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8986614520891326</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>88.90000000000003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6063292865911881</v>
+      </c>
+      <c r="D38" t="n">
+        <v>778.0864930635075</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6909821348092033</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.23491e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.873</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1407556048805033</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7678014904433822</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.509005065534174</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.401990178739131</v>
+      </c>
+      <c r="L38" t="n">
+        <v>21.97836461856139</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.27059090147748</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>15.34152966587589</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7233.477705375245</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-285.5876731439228</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.20844195289727e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9001907248450632</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>87.82900000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.599024689673987</v>
+      </c>
+      <c r="D39" t="n">
+        <v>820.311084855051</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7284798151283841</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.23312e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.964</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4960474678057184</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.002676634913937</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.844652241094084</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.773682377630725</v>
+      </c>
+      <c r="L39" t="n">
+        <v>23.58888379740582</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.37729202165276</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15.79465059968024</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7399.724136359128</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-327.5194980332438</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.111308803992081e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9019044205140203</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>84.20699999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5743213749829489</v>
+      </c>
+      <c r="D40" t="n">
+        <v>766.7198928745187</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6808879900911955</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.23191e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-80.042</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1480482520921864</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.589249828434978</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.525893564501388</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.378652054244133</v>
+      </c>
+      <c r="L40" t="n">
+        <v>22.34097047071391</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.25518816750865</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15.27824967962557</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7065.125182309032</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-282.9517107423186</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.030844396002918e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9033714295641402</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>85.12200000000001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.580561996999045</v>
+      </c>
+      <c r="D41" t="n">
+        <v>820.084493206843</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7282785897090965</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.23159e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-80.127</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.379394562511104</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.081908449901843</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.694891183887842</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.665309263989076</v>
+      </c>
+      <c r="L41" t="n">
+        <v>23.44104404501469</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.41945351399555</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15.98112878927881</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7358.892142885788</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-334.7580100738921</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.949215883028286e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9048873269211634</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5746146501159457</v>
+      </c>
+      <c r="D42" t="n">
+        <v>787.4608267514425</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6993070410527235</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.2307e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-80.227</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3409916298120794</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.12801311177894</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.663242745868579</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.790401580927847</v>
+      </c>
+      <c r="L42" t="n">
+        <v>23.28617940161484</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.43873896347283</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>16.06789720132253</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7330.866382177048</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-308.8989855671634</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.856700057113214e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9066104531347747</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80.15899999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5467125903696628</v>
+      </c>
+      <c r="D43" t="n">
+        <v>752.3080118390474</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6680894742278782</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.23035e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-80.279</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.459496532458217</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.371256892159129</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.371632645822643</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22.79776784187481</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.27015346145507</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15.33972530396093</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-6898.664298580803</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-280.9176626563031</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.80187494533801e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9076586219078739</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>7.530284246436029e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9075943564179231</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>159.521</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1360.929892269295</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.04393e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-77.526</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5128678408020836</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.010198460901405</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.753057614057082</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.654851914870114</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.11356296709194</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.37045796082725</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.34917721138359</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7280.475695272173</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-674.8942507865065</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.249454044055751e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8299942220424288</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>129.987</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.814858231831546</v>
+      </c>
+      <c r="D24" t="n">
+        <v>847.714643775886</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6228936909912062</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.07706e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-78.378</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1955306492728645</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8346090242609679</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.620687598744095</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.362669443611765</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19.03413791091354</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.70198419608978</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.30573701345608</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7375.903936424929</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-268.7502629801289</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.035668630598142e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.859359573301552</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>121.414</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7611160912983245</v>
+      </c>
+      <c r="D25" t="n">
+        <v>905.801278995981</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6655752688961767</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.07966e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-78.658</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4334773202270193</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.216060465862294</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.19418921396628</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.10699697142644</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.7228042362088</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.37074816836922</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-7260.903349333928</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-329.0307742571213</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.807443637112244e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8676408994231256</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>118.814</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7448172967822418</v>
+      </c>
+      <c r="D26" t="n">
+        <v>794.3372802677687</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5836724468908855</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.07754e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-78.816</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1128098140560156</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5480933134465793</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.45632799062722</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.392103392535487</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.34346435217874</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.85060828652833</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.78408724670077</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-7415.660134759206</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-236.3047862035027</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.503341995736951e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8723129801885814</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>116.859</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7325618570595722</v>
+      </c>
+      <c r="D27" t="n">
+        <v>810.2111402299309</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5953364275649327</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.07555e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-78.95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3814648350988993</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7400469682968751</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.518196759781987</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.239976347338744</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20.1793928003085</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.97968856055924</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.22818046103546</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7589.47571592912</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-255.9031128604807</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.261465598722945e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8761298590883635</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>115.15</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7218485340488087</v>
+      </c>
+      <c r="D28" t="n">
+        <v>839.0894694644131</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6165559844271372</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.07626e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-79.09699999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7797265859284079</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9417643708241996</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.708120726229179</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.716087528872767</v>
+      </c>
+      <c r="L28" t="n">
+        <v>21.57531470783789</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.09102856914589</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.63475933658059</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7732.434431159663</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-287.6120788293192</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.03637099704054e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8798555448635064</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>111.708</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.700271437616364</v>
+      </c>
+      <c r="D29" t="n">
+        <v>820.8041031615124</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6031200488901415</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.07525e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-79.20999999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6056782124111291</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9975941515531509</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.648743558066118</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.460048320521651</v>
+      </c>
+      <c r="L29" t="n">
+        <v>20.77266558213071</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.08941493964015</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.62870179468062</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7633.516383021247</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-276.9673507855659</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.850825373548373e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8829553946364356</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>111.664</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.699995611863015</v>
+      </c>
+      <c r="D30" t="n">
+        <v>879.9971411455131</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.646614602371731</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.07573e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-79.35899999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.197156707757679</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.343889384146011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.891830945225419</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.820965382163825</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.7919021481966</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.3369970745009</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>15.62043466018733</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8116.589163396268</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-335.342589638515</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.662062897082133e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.886201533607208</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106.804</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6695294036521837</v>
+      </c>
+      <c r="D31" t="n">
+        <v>843.4907930182416</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6197900404786869</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.07423e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-79.43600000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4801313799470114</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.067847330544208</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.824302581011899</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.69832084277739</v>
+      </c>
+      <c r="L31" t="n">
+        <v>22.20842076285486</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.23085091490984</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15.17931617679168</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7777.134174220517</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-307.561731482034</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.539360900901032e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8883164337014405</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>102.842</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6446925483165227</v>
+      </c>
+      <c r="D32" t="n">
+        <v>802.7854632143084</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5898801016676151</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.07522e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-79.52800000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3219884691250597</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7404669856994633</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.458527584781532</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.508352093893085</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21.9141269915061</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.1455908825501</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14.84256607047867</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-7507.112775363232</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-275.5576416399167</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.42081609816923e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8904541333673119</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>100.172</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6279549401019304</v>
+      </c>
+      <c r="D33" t="n">
+        <v>767.7902631280917</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5641659188246888</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.07495e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-79.599</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4060713520669976</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6227153238548443</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.420712858373282</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.302039866775125</v>
+      </c>
+      <c r="L33" t="n">
+        <v>20.69425925304807</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.10219382292112</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14.67681073983312</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-7342.240245234433</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-248.4839505202588</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.325347789270932e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8921685425401087</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100.331</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6289516740742601</v>
+      </c>
+      <c r="D34" t="n">
+        <v>818.4429520648192</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6013850946429715</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.07495e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-79.709</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5441537152874398</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9344389408116007</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.536038053596743</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.197714762943662</v>
+      </c>
+      <c r="L34" t="n">
+        <v>21.39979381547813</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.25619071657593</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>15.2823526925668</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-7606.439003292698</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-297.9389973355042</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.20693032661026e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8943121180026801</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99.54599999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6240306918838273</v>
+      </c>
+      <c r="D35" t="n">
+        <v>875.6918373585926</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6434511008487087</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.07561e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-79.77200000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.7747359672404535</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.17189043131714</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.94071100384978</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.912152116826619</v>
+      </c>
+      <c r="L35" t="n">
+        <v>23.35274763797629</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.36223952402705</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>15.72911987119276</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7787.121506335484</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-353.5603787841515</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.127781237429013e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8958032447841887</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97.00899999999996</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6081268296964035</v>
+      </c>
+      <c r="D36" t="n">
+        <v>825.6312413119931</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.606666989976454</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.07588e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.873</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6376461958148864</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8843719676971835</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.686785722127975</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.642680109420358</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22.15900321291861</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.34080378605297</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>15.63672915093479</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-7659.417691555616</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-312.4086919709623</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.022724761816673e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8977678598770742</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>94.45400000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5921101297007919</v>
+      </c>
+      <c r="D37" t="n">
+        <v>790.6197028129441</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5809408018032566</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.0782e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.95399999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2481860798644547</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7926315870408949</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.591118715946928</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.545663664073011</v>
+      </c>
+      <c r="L37" t="n">
+        <v>22.39426097276289</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.28041387999662</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>15.38215930717319</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-7450.193141842873</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-284.7835158811475</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.947759096426171e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8992533863527454</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93.88200000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5885243949072537</v>
+      </c>
+      <c r="D38" t="n">
+        <v>828.5847902731853</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6088372332622908</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.0786e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-80.00700000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5489499351611101</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.151220398004392</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.760872953896504</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.499386584803543</v>
+      </c>
+      <c r="L38" t="n">
+        <v>22.29640701652342</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.3823934739746</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>15.81698322664535</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7618.619376268224</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-322.9149395343706</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.885532963749957e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.900456080681713</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91.95400000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5764382118968664</v>
+      </c>
+      <c r="D39" t="n">
+        <v>826.393385979111</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6072270075581436</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.07895e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-80.09999999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5426439490807828</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.897906125717846</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.621922968896409</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.834042995825286</v>
+      </c>
+      <c r="L39" t="n">
+        <v>23.49761019033234</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.3717566834879</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15.77048949639992</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7518.765585391766</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-324.7614140488583</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.795747484222539e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9021921772586892</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>88.858</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.557030108888485</v>
+      </c>
+      <c r="D40" t="n">
+        <v>785.3170805093731</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5770444789039711</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.08034e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-80.15900000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1456429891133929</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.7387318409051296</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.644947817427679</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.510226943894417</v>
+      </c>
+      <c r="L40" t="n">
+        <v>23.01736148891735</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.28548445354127</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15.40321610280369</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7255.863403884056</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-291.7836314071607</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>7.735203486760573e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9034251029183138</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87.77999999999997</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5502723779314322</v>
+      </c>
+      <c r="D41" t="n">
+        <v>820.5341349251809</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6029216784686634</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.08109e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-80.256</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3010772146332337</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8982335349571927</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.759301655848004</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.572200670504321</v>
+      </c>
+      <c r="L41" t="n">
+        <v>22.88572999399127</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.3838129704954</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15.82320854714007</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7405.167210656181</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-327.4272242862827</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.651207285496407e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9050834176348366</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86.488</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5421731308103637</v>
+      </c>
+      <c r="D42" t="n">
+        <v>802.3124583457379</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5895325416123489</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.08281e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-80.313</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1157751344692449</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8083735790233221</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.570541387662018</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.35406224614756</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22.44159439168356</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.38921301969647</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>15.84693558220773</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7349.342759269707</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-314.8376837052657</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.594625391339403e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9062712972722259</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83.93599999999998</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5261752371161164</v>
+      </c>
+      <c r="D43" t="n">
+        <v>769.820257707435</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.565657542008862</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.0839e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-80.384</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.04192480855325642</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6313475509712926</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.347895192247431</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.255286379449523</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22.14836969215325</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.30979593016248</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15.50497817787444</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7104.662817970229</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-289.2507392472922</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.530284246436029e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9075943564179231</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.073682635026227e-06</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8576846166664608</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>262.504</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>386.9688380059437</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.10809e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-72.67100000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3760607688977225</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5960263478065286</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.219805852761114</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.739733406768973</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.33663405942446</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.70459489039814</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.811191425346159</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5664.475697975076</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>248.4034555975236</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.152985457942313e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9175395601635062</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>174.836</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6660317557065797</v>
+      </c>
+      <c r="D13" t="n">
+        <v>954.8240920702758</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.467444399374634</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.27465e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-75.34099999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3825606324296922</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.708897980451684</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.326946508238823</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.011795601829562</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13.26082319176915</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.27422222106367</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.973303530021342</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6235.016696184286</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-293.0690120800874</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.677452522839929e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.7256973211863861</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>156.252</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5952366440130438</v>
+      </c>
+      <c r="D14" t="n">
+        <v>834.7079968384423</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.157041898101422</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.26496e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.214</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.06422594773600597</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5193973706787749</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.506615492334164</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.166445366476919</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.82290636303078</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.67273293376704</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.72418122338732</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-6457.222985885509</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-211.3050863911247</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.817158349230833e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.7823188836726278</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>149.34</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5689056166763176</v>
+      </c>
+      <c r="D15" t="n">
+        <v>821.3489547827545</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.122519629785122</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.24367e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.712</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.119776886174554</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6565780103354363</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.432384821598352</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.277327044843894</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15.9592478865652</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.95536822507026</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.32840873787003</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-6711.919872729918</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-209.2693139093729</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.551584797607573e-06</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8050175307555576</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>145.3699999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5537820376070459</v>
+      </c>
+      <c r="D16" t="n">
+        <v>829.9734554708946</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.144806955897949</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.22243e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.059</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2260882118717157</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7393817500528544</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.57151861350703</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.163097749616126</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15.98088238782829</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.19587264337859</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11.89840326745445</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-6971.727991215119</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-224.3776810569355</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.403257078285212e-06</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.819241634951197</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>139.777</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5324756956084479</v>
+      </c>
+      <c r="D17" t="n">
+        <v>808.7090923972022</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.089855856519332</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.20916e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.36499999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4169296705717941</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5676502412179942</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.424936145993078</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.184301441729694</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17.05153095504486</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.27155152418317</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.08972580048006</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-6978.950978077645</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-212.7117955427347</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.2989293958207e-06</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8303017056326936</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>138.743</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5285367080120684</v>
+      </c>
+      <c r="D18" t="n">
+        <v>847.6643052746051</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.190523427267767</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.19867e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-77.604</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5279483020288382</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.209691643272182</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.973219766587984</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.487239703336152</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18.43937855717516</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.56297724600542</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.88728986709451</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-7388.882746748612</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-253.6938221717188</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.223309426751137e-06</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8389065445825524</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>132.643</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5052989668728857</v>
+      </c>
+      <c r="D19" t="n">
+        <v>813.0034185985854</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.100953200231844</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.18922e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-77.831</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2923016671155175</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9120185383793875</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.628110465360352</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.380228442089888</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18.57181762477026</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.51228589144141</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12.74113342932064</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-7186.108315126336</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-229.9217965803894</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.162745934544996e-06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.846174600581583</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>130.433</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4968800475421327</v>
+      </c>
+      <c r="D20" t="n">
+        <v>836.4196808550358</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.161465210390375</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.1818e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.01000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.384175237538015</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9602037977760616</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.673158636056737</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.084246318302073</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18.0246516925667</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.64535672007067</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.1320550372761</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7332.145161253643</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-256.6975065679478</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.116260850621299e-06</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8520377104751431</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>125.848</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4794136470301406</v>
+      </c>
+      <c r="D21" t="n">
+        <v>820.1188246125876</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.119340742884291</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.17697e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.20699999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4070840462417472</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.01608500206003</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.765796502429194</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.586652876146154</v>
+      </c>
+      <c r="L21" t="n">
+        <v>19.88638200211895</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.7085873613081</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13.3262874016879</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-7347.820697820334</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-248.7557723198426</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.073682635026227e-06</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8576846166664608</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>7.943590377711847e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9033020411966273</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>154.8630000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1197.655489330734</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.34957e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-76.021</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.13108792360626</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7004788898026604</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.236659109750848</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.998474552184525</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13.35847398918895</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.34137867276681</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.09245365316553</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-5851.072698290834</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-543.3894491106084</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.789976648279128e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.7876958551000325</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>128.346</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8287712365122719</v>
+      </c>
+      <c r="D24" t="n">
+        <v>824.2540701212449</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6882230135995528</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.32251e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-77.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1334385730557313</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6846546224824683</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.329431169532908</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.058497222916822</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15.28721553629523</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.00298876246667</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.43692355308581</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-6273.527778223771</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-251.6589650193323</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.292418458022157e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8352058649312752</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>125.253</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8087987446969253</v>
+      </c>
+      <c r="D25" t="n">
+        <v>846.592129650389</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7068745037218307</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.29211e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-77.78</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7045473468512315</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.145112988204874</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.772769972013858</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.370752173596686</v>
+      </c>
+      <c r="L25" t="n">
+        <v>17.4291762377234</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.49559100147437</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.69371635068393</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-6896.834561365011</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-280.6216910710075</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.167616733782872e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8493114793289552</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>119.668</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7727346105912966</v>
+      </c>
+      <c r="D26" t="n">
+        <v>786.8624992377825</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6570023735936715</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.26899e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-78.095</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3799081480786351</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8078241662232671</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.377606246016697</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.117706638016172</v>
+      </c>
+      <c r="L26" t="n">
+        <v>17.62211819010094</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.5016101024145</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.71077140345731</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-6797.38766962644</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-233.5210631100159</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.097665810904654e-06</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8577348042543627</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>118.0219999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7621058613096731</v>
+      </c>
+      <c r="D27" t="n">
+        <v>841.9381808486517</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7029886209757515</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.25014e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-78.306</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8850650598072066</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.141731747056997</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.826287521292426</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.343698509802317</v>
+      </c>
+      <c r="L27" t="n">
+        <v>18.45108375475308</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.73307133933369</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.40304061897154</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7126.489023836115</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-287.5327462543942</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.051812760341511e-06</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8634700582968291</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>115.446</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.74547180411073</v>
+      </c>
+      <c r="D28" t="n">
+        <v>840.0661355309213</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7014255293067303</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.23713e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-78.51300000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7153038373974264</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.086511902130768</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.45265967152724</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.352426362564199</v>
+      </c>
+      <c r="L28" t="n">
+        <v>18.58237865560925</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.80503641341028</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.63381644306993</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7171.224210644265</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-291.1301578325765</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.013681429750216e-06</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8685320003717431</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>111.303</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7187191259371183</v>
+      </c>
+      <c r="D29" t="n">
+        <v>813.7575557867229</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6794587951510677</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.22673e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.712</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3100730686201351</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6699868548954904</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.450439832010598</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.259604964412067</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.18796585542277</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.79298279271276</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13.59461373565817</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7055.838377605582</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-273.0046768204991</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.79331295351269e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8733319569118753</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>108.67</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7017170014787262</v>
+      </c>
+      <c r="D30" t="n">
+        <v>802.461637230826</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6700271024343172</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.21853e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.857</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3943259313555657</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8740324571671987</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.483373369666582</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.341574975554589</v>
+      </c>
+      <c r="L30" t="n">
+        <v>19.49934147399136</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.86617075478213</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.83616121563415</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7112.722165157036</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-267.8247282760826</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.541075920291812e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.876963732069677</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>108.903</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.703221557118227</v>
+      </c>
+      <c r="D31" t="n">
+        <v>851.4123571737554</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7108992233230075</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.21175e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.991</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.66467338441554</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.205555272375719</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.866087991863654</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.435619051090081</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.21415709950004</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.04721851291664</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14.47204994659154</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7403.041572670372</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-316.1917066627358</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.329199084660932e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8800895374504167</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103.167</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6661823676410759</v>
+      </c>
+      <c r="D32" t="n">
+        <v>791.3335264847823</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6607355233072827</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.20735e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-79.10899999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1425720595855672</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8095302163976215</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.502399980038932</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.514397898327171</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.47793135831148</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.90117617036917</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13.95473628862328</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-7029.460609951821</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-266.8754219595904</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.158146631407134e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8827075870709763</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103.635</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6692043935607599</v>
+      </c>
+      <c r="D33" t="n">
+        <v>845.8496657969624</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7062545726481282</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.20347e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-79.223</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6876712420412286</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.336113454959132</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.096723645604279</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.740901971391303</v>
+      </c>
+      <c r="L33" t="n">
+        <v>21.78819654744828</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.09682199415462</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14.65654897842345</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-7356.21618013666</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-319.8189832393668</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.996273767565365e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8852391797187512</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101.796</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6573293814532842</v>
+      </c>
+      <c r="D34" t="n">
+        <v>827.9342006419425</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6912957925025696</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.20011e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-79.34099999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5456993096448471</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.13902987790713</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.702008353412342</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.48828933990042</v>
+      </c>
+      <c r="L34" t="n">
+        <v>21.63682406280757</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.11823548043371</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>14.73765081843047</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-7329.036117939046</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-307.709388255737</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.846161540240556e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8876430945055536</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99.78700000000003</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6443566248878041</v>
+      </c>
+      <c r="D35" t="n">
+        <v>824.0312693383981</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6880369828212267</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.19676e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-79.458</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5761079211704008</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.186960581649092</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.765980417693056</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.466087752953278</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.48228935430566</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.15113165755315</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>14.86399776831588</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7328.840189038013</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-308.0800623467797</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.702026283103438e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8899835589731141</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>96.41400000000004</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6225760833769203</v>
+      </c>
+      <c r="D36" t="n">
+        <v>785.2912526161463</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6556904382035418</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.19397e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.497</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.03930176500610308</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9362346332199328</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.470991863678789</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.362434346840123</v>
+      </c>
+      <c r="L36" t="n">
+        <v>20.85213752420258</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.02377315489622</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>14.38644502270059</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-7005.441102406066</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-277.1650752430896</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.626656148130543e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8912124570067083</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>96.06</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6202901919761336</v>
+      </c>
+      <c r="D37" t="n">
+        <v>825.7922696742288</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6895073558554744</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.19329e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.631</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6272792231972879</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9542797956554196</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.617131045771197</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.578248841991928</v>
+      </c>
+      <c r="L37" t="n">
+        <v>21.37610644363616</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.19642498284472</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>15.04153010215688</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-7291.197489787197</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-317.1512808614162</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.488422569119952e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8935906829007343</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93.17400000000004</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6016543654714167</v>
+      </c>
+      <c r="D38" t="n">
+        <v>771.6703928872246</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6443175017871328</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.18997e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.693</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2475995699591194</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7046117909454926</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.366942869660273</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.269372345747574</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20.92689408291118</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.09150478381427</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>14.63654799396766</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7010.913950724082</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-272.0146691338257</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.396386542920469e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8951239476083211</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91.44099999999997</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5904638293201083</v>
+      </c>
+      <c r="D39" t="n">
+        <v>751.0127732574939</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6270691195822681</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.18886e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.794</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4199580397912129</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.330593823012697</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.216074211779245</v>
+      </c>
+      <c r="L39" t="n">
+        <v>21.18607599866911</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.05765811255874</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>14.51049466468189</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-6876.684018773698</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-257.3446194007236</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.297869985299549e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8968476481013549</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90.58600000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5849428204283785</v>
+      </c>
+      <c r="D40" t="n">
+        <v>754.6919225287181</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6301410791766587</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.18725e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.902</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.05856886699174287</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6852906709247946</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.324654474920868</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.161327634690301</v>
+      </c>
+      <c r="L40" t="n">
+        <v>21.15584780840677</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.15734959276618</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14.88812220568255</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7012.96178817961</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-263.9880967737304</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.189301531234026e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.898756777894239</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>89.36499999999995</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.577058432291767</v>
+      </c>
+      <c r="D41" t="n">
+        <v>794.1679621443626</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6631021768940869</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.18796e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.967</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1827045578692102</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6405631131214343</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.576576035289089</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.42376620260316</v>
+      </c>
+      <c r="L41" t="n">
+        <v>21.64132518953993</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.20525123828185</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15.07661827029655</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7049.52408508412</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-303.1807319517184</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.120594659232375e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9000478760096424</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87.89699999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5675790860308787</v>
+      </c>
+      <c r="D42" t="n">
+        <v>793.7782720251658</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6627767994189546</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.18724e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-80.048</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2796324987421598</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8168759075816147</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.505320676618938</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.406129102809667</v>
+      </c>
+      <c r="L42" t="n">
+        <v>21.80420633611146</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.2322946739904</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>15.18514959942751</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7043.293606001984</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-306.2601005904593</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.040902748043091e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9015033507399853</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>88.505</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5715051367983311</v>
+      </c>
+      <c r="D43" t="n">
+        <v>845.3451185958534</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7058332935694583</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.18656e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-80.14700000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4757256036866235</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.096372378941198</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.511833305970431</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.505537954186257</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22.59009422143666</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.38932829967922</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15.84744287846921</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7317.219125309516</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-356.4190046523106</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.943590377711847e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9033020411966273</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.121123047400696e-06</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8559192472240215</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>249.226</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>380.4700614118278</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.30617e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-72.37</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.305229528160217</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8253259981307368</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.384169276939502</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.1734979514652</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.67308331595372</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.77194845816865</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.884767934930937</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5573.693806484659</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>244.6467974605519</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.881209197017351e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.904635313788705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>170.275</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6832152343655958</v>
+      </c>
+      <c r="D13" t="n">
+        <v>918.2838535879727</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.413550885398064</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.45063e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-74.81399999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1071602219277513</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.401740825963118</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.238570543361571</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.88900320002873</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.40087124205822</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.02418309048512</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.553149794099227</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-5894.239021872533</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-268.6337998642754</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.526782239979953e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.6919302999864283</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>155.854</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6253520900708593</v>
+      </c>
+      <c r="D14" t="n">
+        <v>838.7848042955202</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.204601332317719</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.43561e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-75.70399999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2351618820208391</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9154875863525624</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.238688259116721</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.112405078300682</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13.84794507091336</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.57038930128259</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.52085836601968</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-6293.619681130627</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-219.449375765021</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.181476508861705e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.7613140111214566</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>149.561</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6001019155304825</v>
+      </c>
+      <c r="D15" t="n">
+        <v>824.187464497679</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.166234739835583</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.40693e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.26600000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.08108969542901653</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7533157998888476</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.666809488322929</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.286957500059363</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.98979468907687</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.88794457234106</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.17821653123506</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-6581.25142678913</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-216.2690770594127</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.78223714246108e-06</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.79020552261438</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>144.996</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5817852070008749</v>
+      </c>
+      <c r="D16" t="n">
+        <v>838.9211336832203</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.204959650623223</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.38016e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-76.676</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4691174207770005</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9113640926323461</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.706397667624951</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.355141898100458</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16.55808468769415</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.16016319501142</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11.8101997073542</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-6871.507724383208</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-236.8472215433483</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.565254805349706e-06</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8085861289201479</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>139.1750000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5584288958615877</v>
+      </c>
+      <c r="D17" t="n">
+        <v>831.6168035960286</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.185761477552556</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.36161e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.036</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3256704509302275</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9945306649274145</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.515106000077675</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.186167042026732</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17.03955666462918</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.30933337209662</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.18754652869191</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-6990.026653880045</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-238.0944253891106</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.421163704164713e-06</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8223049159105247</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>135.1300000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5421986470111467</v>
+      </c>
+      <c r="D18" t="n">
+        <v>830.8849007201812</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.183837796953007</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.34615e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-77.334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.586105722921163</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8259174716164517</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.433450832553683</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.22960281966186</v>
+      </c>
+      <c r="L18" t="n">
+        <v>17.30733813309292</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.41296251207909</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.46410482946496</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-7046.55101699981</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-244.961063299749</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.317363148607506e-06</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8331295148860398</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>129.705</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5204312551659941</v>
+      </c>
+      <c r="D19" t="n">
+        <v>812.5668295768697</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.135691903225291</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.33202e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-77.616</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3528677494585213</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7460709670908044</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.558113684113225</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.269430226166837</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18.41359769329891</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.4649106739612</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12.60748603523212</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-7016.856535205619</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-236.1165078906858</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.234759630935135e-06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8423148227569807</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>127.003</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5095896896792471</v>
+      </c>
+      <c r="D20" t="n">
+        <v>827.4840040491838</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.174899126040563</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.31557e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-77.833</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.344359586258705</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9018746507369042</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.543571437864111</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.042470154786654</v>
+      </c>
+      <c r="L20" t="n">
+        <v>17.9100196265023</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.60893138353242</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.02269798875889</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7168.370743560709</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-256.1145298197704</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.171538292361146e-06</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8496277698707549</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>122.172</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4902056767752964</v>
+      </c>
+      <c r="D21" t="n">
+        <v>802.710183019031</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.109785406085244</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.30722e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.05500000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2066984345779428</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7280502579867337</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.55056713981142</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.211320619324486</v>
+      </c>
+      <c r="L21" t="n">
+        <v>18.46445037567896</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.59917131842867</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>12.9937029969154</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-7046.44320841293</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-240.4494236195044</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.121123047400696e-06</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8559192472240215</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>8.240718858778662e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9020368808862339</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>160.167</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1034.506910599089</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.58809e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-74.592</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3301024091499679</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8367008061126036</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.430308606711741</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.103371869625002</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11.75328740451347</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.81631011434521</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.229626298103566</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-5459.126046942333</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-386.9052362141252</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.939460051597208e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.7230908482518855</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8622250526013473</v>
+      </c>
+      <c r="D24" t="n">
+        <v>854.8005856005074</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8262879414749265</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.53072e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.09</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3806347025851536</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.856073063515977</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.44672589866453</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.060983420269634</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13.93987495509508</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.66449696472088</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10.70753133669543</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-6046.519547476223</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-264.9461390807161</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.723593905626079e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.7996433236301838</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>129.027</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8055779280376109</v>
+      </c>
+      <c r="D25" t="n">
+        <v>808.3584406137708</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7813949161012809</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.48432e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.806</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.09832894851399479</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8096666569219945</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.422649477070008</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.185257300687062</v>
+      </c>
+      <c r="L25" t="n">
+        <v>15.74395477127287</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.9938808202409</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.41600966374292</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-6307.153016777313</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-235.0941334244989</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.445534303458247e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8242070913563007</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>124.3340000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7762772606092393</v>
+      </c>
+      <c r="D26" t="n">
+        <v>795.2842894481685</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7687568650340039</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.44464e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.283</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3643596888248495</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7706186277139501</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.61628120304449</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.309543787157372</v>
+      </c>
+      <c r="L26" t="n">
+        <v>16.89281130760495</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.2567288732417</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.05177323224869</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-6567.897026605417</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-231.3233031929148</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.299772470422183e-06</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8386997720779665</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>120.244</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7507414136495034</v>
+      </c>
+      <c r="D27" t="n">
+        <v>804.5637803083612</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7777268301112007</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.41536e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.63</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.09160527067149264</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.499590684864099</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.237115638558158</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.080913409329291</v>
+      </c>
+      <c r="L27" t="n">
+        <v>16.97244244015152</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.36876273292559</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.34463715394038</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-6629.071089220419</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-246.5674317314974</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.206148627871701e-06</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8488725973355692</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>118.028</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7369058545143503</v>
+      </c>
+      <c r="D28" t="n">
+        <v>829.1371278037582</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8014805114482992</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.39399e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.94799999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5685054548624868</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.021299630864505</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.542907336311795</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.323747345589888</v>
+      </c>
+      <c r="L28" t="n">
+        <v>18.18577346056051</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.65429685905549</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.15917499015366</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7007.293960867753</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-275.0314039919269</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.135032723436958e-06</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8572078173344774</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>113.074</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7059756379279123</v>
+      </c>
+      <c r="D29" t="n">
+        <v>805.2226389620038</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7783637119404976</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.37618e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.17700000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.148797826965246</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.000193715681134</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.438205525959162</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.199232034490155</v>
+      </c>
+      <c r="L29" t="n">
+        <v>18.25034403102211</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.62865855973675</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13.08169760955599</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-6852.533653382613</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-260.5202864720491</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.083236618129556e-06</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8636058093250398</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>109.406</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6830745409478856</v>
+      </c>
+      <c r="D30" t="n">
+        <v>797.0873140987593</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7704997481719682</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.36257e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.402</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1397488358035178</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.755138197938148</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.494686820779296</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.150051514413872</v>
+      </c>
+      <c r="L30" t="n">
+        <v>18.49056759013806</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.70910225532666</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.32789250950225</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-6896.546207187512</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-259.1542638574145</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.040844649526188e-06</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.869109418292883</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106.69</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6661172401306136</v>
+      </c>
+      <c r="D31" t="n">
+        <v>796.5596083224327</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7699896444975317</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.35313e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.59699999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2602718641736783</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7047072204277379</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.522673123184286</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.102489221188576</v>
+      </c>
+      <c r="L31" t="n">
+        <v>18.93168678249232</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.79834206250902</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13.61201628628344</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-6967.256924568538</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-264.1806209131174</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.006394073931005e-06</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8738246336810223</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103.692</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6473992770046263</v>
+      </c>
+      <c r="D32" t="n">
+        <v>788.5308800615279</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7622287217055754</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.34448e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-78.744</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2014230840990293</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8403745690595604</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.389985924028697</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.356618685942855</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.05736392964297</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.81055176757511</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13.65182944744899</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-6904.239530447566</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-262.483927089498</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.803227553144902e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8774668121334069</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103.007</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6431224909001229</v>
+      </c>
+      <c r="D33" t="n">
+        <v>820.2229790450344</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7928637021574251</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.33791e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-78.896</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5543197696236071</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.020110270664494</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.504087092508719</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.374108811120671</v>
+      </c>
+      <c r="L33" t="n">
+        <v>20.4364350603683</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.9756923366898</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14.21400506685705</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-7139.873421238864</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-295.5780508095725</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.569377701865932e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8808555663346426</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98.77200000000005</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6166813388525728</v>
+      </c>
+      <c r="D34" t="n">
+        <v>771.1667886353216</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7454438252024185</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.33169e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-79.036</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.07056558954419857</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7946050012761117</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.348902652833653</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.208742077573862</v>
+      </c>
+      <c r="L34" t="n">
+        <v>19.96063557613817</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.88751051667424</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>13.90820635337586</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-6889.204435189553</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-256.138942725115</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.361365042195794e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8839315605615186</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98.423</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6145023631584533</v>
+      </c>
+      <c r="D35" t="n">
+        <v>822.616872771044</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.795177745400136</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.32685e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-79.175</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6033970467645074</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9826136528965708</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.794629844238146</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.43300026544915</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.22966461485848</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.10551997027011</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>14.68938446323112</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7245.118436099759</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-306.7717953356089</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.169170173836528e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8868648255645546</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95.363</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5953973040638832</v>
+      </c>
+      <c r="D36" t="n">
+        <v>782.5736068113524</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7564701586750727</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.32169e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.285</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2945994155730148</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8271544871707466</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.499336488060087</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.446928111911252</v>
+      </c>
+      <c r="L36" t="n">
+        <v>21.4677964091038</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.05576800368037</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>14.50351911353975</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-7071.456782491423</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-274.90561820716</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.019821697617403e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8891495212336263</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>95.43600000000004</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5958530783494729</v>
+      </c>
+      <c r="D37" t="n">
+        <v>820.8362714596561</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.793456537650681</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.3181e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.396</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4770217624174433</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.120168369559101</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.455633954601606</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.274729245990715</v>
+      </c>
+      <c r="L37" t="n">
+        <v>21.30710425442786</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.17066780525838</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>14.94005762490695</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-7240.648976410118</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-313.1258237874088</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.881227119662631e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8913408360591843</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92.89800000000002</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5800071175710353</v>
+      </c>
+      <c r="D38" t="n">
+        <v>792.880295377221</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7664330583524658</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.31649e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.471</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1559035676611303</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8480736603321325</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.494076041095436</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.596383081130563</v>
+      </c>
+      <c r="L38" t="n">
+        <v>21.84588691238783</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.13380830266429</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>14.79719499513266</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7098.044478056531</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-291.6175450592303</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.778198949022282e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8930375616049108</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92.55700000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5778780897438299</v>
+      </c>
+      <c r="D39" t="n">
+        <v>823.4285607294327</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7959623587749453</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.31129e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.586</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4257928777744838</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9171493087409457</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.689249606026482</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.466755017837257</v>
+      </c>
+      <c r="L39" t="n">
+        <v>21.7914060903328</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.25571142886017</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15.28039089519118</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7292.476624573471</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-322.791095881857</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.644316165480016e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8951668052222892</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>89.63600000000002</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5596408748368891</v>
+      </c>
+      <c r="D40" t="n">
+        <v>781.7034635250845</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7556290398025424</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.30989e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.684</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2111668079154354</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8126515938433891</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.490046600137014</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.325984382326963</v>
+      </c>
+      <c r="L40" t="n">
+        <v>22.04711285548316</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.1929289729532</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15.02767687447183</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7092.611485683071</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-288.6210012615235</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.536167775033069e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8969892537466958</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>88.459</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5522922949171801</v>
+      </c>
+      <c r="D41" t="n">
+        <v>784.8753230656495</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.758695099108737</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.30699e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.76300000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5005092969562875</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8139377058121606</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.626681106828833</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.289998404132656</v>
+      </c>
+      <c r="L41" t="n">
+        <v>22.20521660699501</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.22281452282172</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15.14692699141047</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7095.151652313633</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-295.0398429295978</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.443795545922185e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8985259004989633</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86.61900000000003</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5408042855269813</v>
+      </c>
+      <c r="D42" t="n">
+        <v>771.8248347182374</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7460799215650177</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.30495e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.858</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.00811650823342331</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7718418572958412</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.485597179166969</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.54199421033908</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22.93427862070832</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.19572113363522</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>15.03873899755497</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-6975.334469223051</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-286.4908803352249</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.342861206783969e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9002518912254268</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>85.46499999999997</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5335993057246496</v>
+      </c>
+      <c r="D43" t="n">
+        <v>783.1462540642377</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7570237047626031</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.30317e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.95699999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3884003365453135</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7801152234514965</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.421376201130203</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.324018478173127</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22.31528397773949</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.28564577899618</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15.40388698850746</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7100.616029708968</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-300.1768393053282</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>8.240718858778662e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9020368808862339</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.072257515075533e-06</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8639418305740996</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>252.609</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>377.4397619545867</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.35053e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-72.215</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07494999410207356</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5224796477982206</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.007061474031461</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.845286531739781</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.24152671045876</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.58538992846334</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.684231716737626</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5422.829001986913</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>236.5820145616161</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.921569755919438e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9202110267367234</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>164.822</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6524787319533349</v>
+      </c>
+      <c r="D13" t="n">
+        <v>922.1856707647372</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.443265823370496</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.51048e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-75.105</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1294939604485836</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5591128041388731</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.106089032672827</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.854707082003852</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.73065200533692</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.20194311112579</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.848138519560406</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-5935.181640114986</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-284.4494306501484</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.907913506570322e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.7218054592484467</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>147.1370000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.582469349864811</v>
+      </c>
+      <c r="D14" t="n">
+        <v>812.2038051098812</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.15187663563545</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.48767e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.081</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2707300567918456</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3484621423115785</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.550362900643524</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.043126197502781</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.9781018147828</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.73115555062793</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.84377867017155</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-6306.031847322581</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-210.4330106671858</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.896365003181546e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.7837861139106181</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>141.7979999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5613339192190299</v>
+      </c>
+      <c r="D15" t="n">
+        <v>794.0578780253443</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.103800283026049</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.4517e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.666</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4278865188866369</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6777494026762336</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.511280251332855</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.421054742695428</v>
+      </c>
+      <c r="L15" t="n">
+        <v>16.8020621508026</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.10512346645012</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.67676420210202</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-6693.238552575581</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-203.3924165922456</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.591777310518496e-06</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8085333773744523</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>138.0910000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5466590659873561</v>
+      </c>
+      <c r="D16" t="n">
+        <v>804.7664490955115</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.132171885993136</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.4222e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.078</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4222523958070771</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9227632086996448</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.471330521776808</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.277703540529941</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17.01931446852708</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.38209844644207</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12.38044189166691</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-7021.644868862996</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-219.7710447834822</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.426486985183265e-06</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8238595213477984</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>132.848</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.525903669307111</v>
+      </c>
+      <c r="D17" t="n">
+        <v>801.7430166393438</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.124161515171284</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.39685e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.392</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3875755868357272</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9457263721267988</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.945491464372651</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.363142947218843</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.60235871732878</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.46358061360702</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.60377408319593</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-7046.79146399494</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-223.9486400817617</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.316241109357098e-06</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8350115586261411</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>130.141</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.515187503216433</v>
+      </c>
+      <c r="D18" t="n">
+        <v>795.6748993942017</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.108084466972339</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.38041e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-77.69199999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6671738680270394</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8918938203421688</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.354037446110056</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.203811387639494</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18.09449420288878</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.6395974237423</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.11464296838327</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-7248.825986570318</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-225.151614238026</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.231416102251103e-06</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.844397028578406</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>125.787</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4979513794045343</v>
+      </c>
+      <c r="D19" t="n">
+        <v>797.3766130886877</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.112593037255644</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.36693e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-77.94</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3499211619454445</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6923854450650276</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.563167399719332</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.074825788515141</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18.67577918250349</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.75641327648039</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.47703686619924</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-7355.659449026061</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-233.621619556554</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.16560288558556e-06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.852158727711832</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>121.0740000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4792940869090177</v>
+      </c>
+      <c r="D20" t="n">
+        <v>771.9530394364732</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.045235073906585</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.35442e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.15600000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1576471462609564</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7758500399060214</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.221779496156935</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.210061607507137</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18.78908597422313</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.71535107482742</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.34740299585458</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7170.807106811348</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-217.345291008688</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.114184749502611e-06</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8584902098275503</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>119.4400000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4728255921206292</v>
+      </c>
+      <c r="D21" t="n">
+        <v>814.5258828030711</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.158028816532251</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.34572e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.352</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6174313884504437</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.196623538959351</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.871864379854434</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.395632901970171</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.66021138085898</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.98735396082425</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.25545003970677</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-7612.879650833882</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-261.1367041328247</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.072257515075533e-06</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8639418305740996</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>8.129018748708925e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.904123777226483</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>153.023</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1181.876455626282</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.51162e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-76.18899999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3954790235673624</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8986636399182683</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.457795934763493</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.225899420923451</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15.2969759082039</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.78155887837785</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.94910537441375</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6274.935947885607</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-536.8872818468551</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.808766172188195e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.7916546012767963</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>129.379</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8454872796899815</v>
+      </c>
+      <c r="D24" t="n">
+        <v>841.0650342724834</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7116353238687705</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.46847e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-77.459</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5426517475235575</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8023568618923603</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.654951819723135</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.532757409658499</v>
+      </c>
+      <c r="L24" t="n">
+        <v>17.80190002952353</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.52275984351037</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.77106185435287</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-6945.694822136638</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-273.8563841467249</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.298060893215393e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8395822544043737</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>119.571</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7813923397136378</v>
+      </c>
+      <c r="D25" t="n">
+        <v>781.1488161158635</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6609394851697331</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.43147e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-77.929</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.09626587662243742</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5809360837645944</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.461483184914488</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.110971794860276</v>
+      </c>
+      <c r="L25" t="n">
+        <v>18.29143690963812</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.59049512193246</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.96803549334798</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-6902.711823665977</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-230.0053238721327</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.173991412747739e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8533364120133866</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>117.955</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7708318357371114</v>
+      </c>
+      <c r="D26" t="n">
+        <v>793.1797981420477</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6711190449442859</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.40309e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-78.21899999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5463298529664354</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9966130032339197</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.71676896098834</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.553522552966333</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.51388126886687</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.81503565292</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.66650862869756</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-7214.44922391076</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-246.2738734027003</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.106332742237177e-06</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8612522102451547</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>115.4640000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7545532370950777</v>
+      </c>
+      <c r="D27" t="n">
+        <v>798.4206080819542</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6755533577821107</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.38424e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-78.45399999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.320733105169013</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.065937749813664</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.69329677443694</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.64859952839368</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21.28982981625905</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.93631231606432</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.07580496942494</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7358.138420855429</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-256.1483868712037</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.057235159675903e-06</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8674125484443523</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>109.395</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7148925324951152</v>
+      </c>
+      <c r="D28" t="n">
+        <v>752.0671844803366</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6363331640123188</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.36996e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-78.65300000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.02308955365584387</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2962273406165908</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.230955514514277</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.133223712173573</v>
+      </c>
+      <c r="L28" t="n">
+        <v>19.95224243670808</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.80957651988884</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.64864086890501</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7022.075921221984</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-219.9434642529057</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.02005034564565e-06</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8722783261207379</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>109.599</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.716225665422845</v>
+      </c>
+      <c r="D29" t="n">
+        <v>813.1223052209655</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6879926419974991</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.35761e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.806</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.271176099736725</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8632295493782897</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.578816308790989</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.568733443599278</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.74756553282938</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.05776625480708</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.51089397159833</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7434.344010347481</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-279.2127904714413</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.922564139804294e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8759964846137275</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107.878</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7049789900864577</v>
+      </c>
+      <c r="D30" t="n">
+        <v>780.2464420779412</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6601759755544713</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.34831e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.958</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7375631544367928</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.166167421999446</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.650315027091714</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.305217470755197</v>
+      </c>
+      <c r="L30" t="n">
+        <v>21.61770891371232</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.09417664486328</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.64659155253502</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7428.082345821925</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-254.4143689330494</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.670763581717393e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8795255559379543</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>102.998</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6730883592662542</v>
+      </c>
+      <c r="D31" t="n">
+        <v>748.9373344703192</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.63368495996771</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.34146e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-79.08499999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4843801294289575</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.32994268557688</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.118634061249154</v>
+      </c>
+      <c r="L31" t="n">
+        <v>21.00617605249601</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.00484263254724</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14.3180568778303</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7170.580770642491</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-230.6667518130781</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.463653600061264e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.882536788197224</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6657822680250682</v>
+      </c>
+      <c r="D32" t="n">
+        <v>745.1335571202053</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6304665378289102</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.33535e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-79.193</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.06022446530299828</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4887503189985041</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.536441576178775</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.267467342364317</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21.25096327109982</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.05829791752852</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14.5128574133625</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-7209.415035910584</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-231.0512230387461</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.30002885933358e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.884943565494608</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>102.292</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6684746737418561</v>
+      </c>
+      <c r="D33" t="n">
+        <v>790.3855590403791</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6687548053586957</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.32944e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-79.298</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2970016313356598</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.005326027823049</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.706930591003404</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.499816020920369</v>
+      </c>
+      <c r="L33" t="n">
+        <v>23.02256270212751</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.27178652094392</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15.34646353967342</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-7605.863129560093</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-275.2983378033858</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.144436966195757e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8872742840777263</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99.053</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.647307921031479</v>
+      </c>
+      <c r="D34" t="n">
+        <v>763.2893104586067</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.645828340876912</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.32504e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-79.416</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2532910934620763</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.112229087297223</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.528161032653196</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.597229840480135</v>
+      </c>
+      <c r="L34" t="n">
+        <v>23.45194191815173</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.21263108231373</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>15.10608168303221</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-7405.061580935761</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-254.505209256925</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.990603939861496e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8896628045424204</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95.80500000000001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6260823536331142</v>
+      </c>
+      <c r="D35" t="n">
+        <v>726.2975194109523</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6145291379259129</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.3227e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-79.515</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6378677810240075</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.302365557335614</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.231168559049447</v>
+      </c>
+      <c r="L35" t="n">
+        <v>22.2081721504607</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.09831015066743</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>14.66215651106469</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7101.120272662076</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-224.8379717536995</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.868767868096841e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8916151497611586</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95.767</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6258340249504978</v>
+      </c>
+      <c r="D36" t="n">
+        <v>740.879680330946</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.626867281096949</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.31992e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.607</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.004435171210107106</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8094648509357272</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.452646407803397</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.212484525711077</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22.4289478380131</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.21686815057282</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>15.12304969400374</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-7290.849198095433</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-241.232535426591</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.754502068073215e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8934618427485918</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>96.02799999999996</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6275396509021518</v>
+      </c>
+      <c r="D37" t="n">
+        <v>777.9526918347831</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6582352056607664</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.31527e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.66500000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5390021242613001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.070161164165414</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.668888662435726</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.409355673089174</v>
+      </c>
+      <c r="L37" t="n">
+        <v>22.91855394854259</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.35533008557465</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>15.69922079080311</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-7541.798441316817</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-277.8114827885216</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8.664470345149445e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8948725901518495</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>94.37</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6167046783816813</v>
+      </c>
+      <c r="D38" t="n">
+        <v>779.172142192576</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6592669973949935</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.31349e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.765</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3643890896918707</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8453801948027435</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.698536922345339</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.343762223860124</v>
+      </c>
+      <c r="L38" t="n">
+        <v>22.80854492461772</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.37799283449269</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>15.79771482541936</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7529.773770926233</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-282.1377379210435</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.555866333473535e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8966884849992028</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93.35500000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6100716885696924</v>
+      </c>
+      <c r="D39" t="n">
+        <v>796.3438553295545</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.673796192096549</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.31111e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.85599999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5775117228490287</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.022711579728271</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.628840384171398</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.517901021395853</v>
+      </c>
+      <c r="L39" t="n">
+        <v>23.58118865610425</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.44201250614353</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>16.08271867019238</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7617.267294575604</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-300.8676773763902</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.453533080133084e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.898406185788005</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>89.81599999999997</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5869444462597125</v>
+      </c>
+      <c r="D40" t="n">
+        <v>745.9580253055415</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6311641303576481</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.31054e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.937</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.09685203989231268</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5685338284950219</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.442970807435745</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.192420290822016</v>
+      </c>
+      <c r="L40" t="n">
+        <v>22.781903876149</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.33631493433467</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15.6175183565893</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7309.895856728192</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-258.620955811155</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.36700635626022e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8999286810833996</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91.851</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6002431007103508</v>
+      </c>
+      <c r="D41" t="n">
+        <v>827.0144744820439</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.699746974859403</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.30803e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.996</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.7348494887905714</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.156915979215683</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.95047100214665</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.887146786916396</v>
+      </c>
+      <c r="L41" t="n">
+        <v>25.58043844447385</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.55759977950409</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>16.62410470942704</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7777.014113823913</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-334.8800256357637</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.29334772169683e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.901180577618217</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>89.185</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5828208831352151</v>
+      </c>
+      <c r="D42" t="n">
+        <v>774.5740508871169</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6553764965870876</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.308e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-80.07599999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3982373443570966</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.088019030154891</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.685246054501414</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.625350942684013</v>
+      </c>
+      <c r="L42" t="n">
+        <v>25.20038396350387</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.47434297442163</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>16.23057618194329</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7507.868026603772</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-290.9318428411493</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.212145709939803e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9026517839142629</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>88.81700000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5804160158930358</v>
+      </c>
+      <c r="D43" t="n">
+        <v>797.9696768396847</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.67517181939024</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.30646e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-80.157</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5415108053123554</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.153963007970476</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.690934445762615</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.597024038870879</v>
+      </c>
+      <c r="L43" t="n">
+        <v>24.83299458204647</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.56979034950589</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>16.68332702673313</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7676.419263588273</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-315.1090767005458</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>8.129018748708925e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.904123777226483</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8808114597849536</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>222.272</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>353.3575561525302</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.48386e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-72.426</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.464407036805686</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6227947881769539</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.412425566988911</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.087748790372248</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.989746360768549</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.7018265444289</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.808196206338663</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5178.691403244354</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>235.0370460086797</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.649237520811054e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.913086834691063</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>146.141</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6574872228620788</v>
+      </c>
+      <c r="D13" t="n">
+        <v>874.4097339653556</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.474574885241475</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.55766e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-75.372</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.36825653796398</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9830782953847407</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.738876564115999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.34347434991799</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.1345972705217</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.734283207498484</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-5595.680165755084</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-267.0781438947058</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.145430711220483e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.7682074996702765</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>134.244</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6039627123524328</v>
+      </c>
+      <c r="D14" t="n">
+        <v>807.468721097435</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.285132175718589</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.49985e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.474</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2174740823336929</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.665381204577432</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.531696644955461</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.174559556798013</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.96356773191735</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.8710411289631</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11.14118006192885</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-6219.262191740373</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-227.8484756981985</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.559200790171495e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8135065963305714</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>128.718</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5791012813129859</v>
+      </c>
+      <c r="D15" t="n">
+        <v>804.1256880832112</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.275671410111583</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.44787e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-77.145</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4318945232710127</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9512198184338075</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.52583069807508</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.439315529110092</v>
+      </c>
+      <c r="L15" t="n">
+        <v>16.90156311660557</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.2661129986185</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.07577321899202</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-6630.67046464207</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-234.3668950765035</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.341308952563464e-06</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8341125685920484</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>124.217</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5588513173049235</v>
+      </c>
+      <c r="D16" t="n">
+        <v>814.6462516431196</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.30544454889616</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.40734e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.616</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5233828772558503</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.015222101059186</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.529315879495205</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.172502424958999</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17.0237958747216</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.52379449953956</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12.77402588142602</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-6913.117957816235</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-251.8824368748429</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.215800879654981e-06</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8473687714558438</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>118.112</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5313849697667722</v>
+      </c>
+      <c r="D17" t="n">
+        <v>782.2409591848879</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.213737744006883</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.3773e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.964</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08498440621873239</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5545245022986216</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.54542455599606</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.390616830179318</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.46871805133745</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.52758181703794</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.78488725925079</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-6779.458745065738</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-231.4674499218453</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.13258003917621e-06</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8569422978983555</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>114.285</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5141673265188598</v>
+      </c>
+      <c r="D18" t="n">
+        <v>801.6651242013544</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.268708027444326</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.35741e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-78.289</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1254457280898007</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7588962091963971</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.430065130479381</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.416069223159731</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18.57612246421361</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.71854653558464</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.35740204621767</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-6985.424340662788</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-256.7510797507313</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.067916225075361e-06</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8650359142213063</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>112.262</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5050658652461848</v>
+      </c>
+      <c r="D19" t="n">
+        <v>913.2873578087826</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.584598353443879</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.34237e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-78.54600000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.763055379106334</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8076975056022773</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.539464313662918</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.182627006970885</v>
+      </c>
+      <c r="L19" t="n">
+        <v>19.22691353207595</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.92717248131648</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.044111147868</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-7262.25964341097</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-363.5161566211135</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.019854564218235e-06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8714067212329445</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>108.089</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4862915706881658</v>
+      </c>
+      <c r="D20" t="n">
+        <v>802.57363212065</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.271279100012259</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.33108e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.77500000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3509924758804119</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9763976557249112</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.61067014483494</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.698908343021163</v>
+      </c>
+      <c r="L20" t="n">
+        <v>20.66888514227622</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.98574501677405</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.24971761705974</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7258.901441500197</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-272.0200643912818</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.815714045508991e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8767422580128512</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104.666</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4708915202994528</v>
+      </c>
+      <c r="D21" t="n">
+        <v>801.0544551787253</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.266979837366043</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.32166e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.949</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3982951044651507</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8025505559272028</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.73252351030952</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.317778516365677</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.1485159166397</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.00640051918805</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.32366043472886</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-7197.159314864291</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-276.867590340141</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.532182013866964e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8808114597849536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
